--- a/grupos/6ASV - Estadisticos 20212.xlsx
+++ b/grupos/6ASV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="793" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="142">
   <si>
     <t>Materia</t>
   </si>
@@ -179,24 +179,24 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Ortega Valle Manuel</t>
+  </si>
+  <si>
+    <t>Duran Amezcua María Angélica</t>
+  </si>
+  <si>
+    <t>Medina Tolentino Elio</t>
+  </si>
+  <si>
+    <t>Hernández Mendoza Delfina</t>
+  </si>
+  <si>
     <t>Jiménez Nieto Enrique</t>
   </si>
   <si>
-    <t>Duran Amezcua María Angélica</t>
-  </si>
-  <si>
-    <t>Medina Tolentino Elio</t>
-  </si>
-  <si>
-    <t>Ortega Valle Manuel</t>
-  </si>
-  <si>
     <t>Pesce Bautista Victor Manuel</t>
   </si>
   <si>
-    <t>Hernández Mendoza Delfina</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -221,186 +221,213 @@
     <t>CISNEROS</t>
   </si>
   <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>LLAME</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MIXCOHUA</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>MONSALVO</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>ROMAN</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>SANTILLANA</t>
+  </si>
+  <si>
+    <t>LEYVA</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>PALMA</t>
+  </si>
+  <si>
+    <t>GERARDO</t>
+  </si>
+  <si>
+    <t>SERRANO</t>
+  </si>
+  <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>GALEOTE</t>
+  </si>
+  <si>
+    <t>SIERRA</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>TREJO</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>CASTELLANOS</t>
+  </si>
+  <si>
+    <t>QUINTERO</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>PINO</t>
+  </si>
+  <si>
+    <t>MOISES EFRAIN</t>
+  </si>
+  <si>
+    <t>JOSE EMMANUEL</t>
+  </si>
+  <si>
+    <t>BRANDON AXEL</t>
+  </si>
+  <si>
+    <t>GABRIEL MARTIN</t>
+  </si>
+  <si>
+    <t>VALERIA</t>
+  </si>
+  <si>
+    <t>JULIO GABRIEL</t>
+  </si>
+  <si>
+    <t>CRISTIAN</t>
+  </si>
+  <si>
+    <t>JAVIER FERNANDO</t>
+  </si>
+  <si>
+    <t>ALEXIS</t>
+  </si>
+  <si>
+    <t>DIEGO ABDEL JARIN</t>
+  </si>
+  <si>
+    <t>AIDA</t>
+  </si>
+  <si>
+    <t>CESAR</t>
+  </si>
+  <si>
+    <t>VALENTIN</t>
+  </si>
+  <si>
+    <t>ALFREDO</t>
+  </si>
+  <si>
+    <t>ANGEL GERARDO</t>
+  </si>
+  <si>
+    <t>EDUARDO ULISES</t>
+  </si>
+  <si>
+    <t>KARLA DENISSE</t>
+  </si>
+  <si>
+    <t>MONSERRAT</t>
+  </si>
+  <si>
+    <t>RICARDO ISIDRO</t>
+  </si>
+  <si>
+    <t>CESAR JAHIR</t>
+  </si>
+  <si>
+    <t>CESAR GAEL</t>
+  </si>
+  <si>
     <t>CORDOVA</t>
   </si>
   <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
     <t>GOMEZ</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>LLAME</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
     <t>MANI</t>
   </si>
   <si>
     <t>MENDOZA</t>
   </si>
   <si>
-    <t>MIXCOHUA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>MONSALVO</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
     <t>RIVERA</t>
   </si>
   <si>
     <t>ROJAS</t>
   </si>
   <si>
-    <t>ROMAN</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>SANTILLANA</t>
-  </si>
-  <si>
-    <t>TREJO</t>
-  </si>
-  <si>
-    <t>LEYVA</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>PALMA</t>
-  </si>
-  <si>
     <t>GUIZA</t>
   </si>
   <si>
-    <t>GERARDO</t>
-  </si>
-  <si>
-    <t>SERRANO</t>
-  </si>
-  <si>
     <t>CUAHUA</t>
   </si>
   <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>GALEOTE</t>
-  </si>
-  <si>
-    <t>SIERRA</t>
-  </si>
-  <si>
     <t>TZOMPAXTLE</t>
   </si>
   <si>
-    <t>VERA</t>
-  </si>
-  <si>
     <t>ZAPATA</t>
   </si>
   <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>CASTELLANOS</t>
-  </si>
-  <si>
-    <t>QUINTERO</t>
-  </si>
-  <si>
     <t>AGUILAR</t>
   </si>
   <si>
     <t>DIAZ</t>
   </si>
   <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>PINO</t>
-  </si>
-  <si>
     <t>LUENGAS</t>
   </si>
   <si>
-    <t>MOISES EFRAIN</t>
-  </si>
-  <si>
-    <t>JOSE EMMANUEL</t>
-  </si>
-  <si>
-    <t>BRANDON AXEL</t>
-  </si>
-  <si>
-    <t>GABRIEL MARTIN</t>
-  </si>
-  <si>
     <t>ANGELA ALESSANDRA</t>
   </si>
   <si>
-    <t>VALERIA</t>
-  </si>
-  <si>
-    <t>JULIO GABRIEL</t>
-  </si>
-  <si>
     <t>LUIS ANGEL</t>
   </si>
   <si>
-    <t>CRISTIAN</t>
-  </si>
-  <si>
     <t>ERICA</t>
   </si>
   <si>
     <t>ZAYRA JOSELIN</t>
   </si>
   <si>
-    <t>JAVIER FERNANDO</t>
-  </si>
-  <si>
-    <t>ALEXIS</t>
-  </si>
-  <si>
-    <t>DIEGO ABDEL JARIN</t>
-  </si>
-  <si>
     <t>WENDY</t>
   </si>
   <si>
-    <t>AIDA</t>
-  </si>
-  <si>
-    <t>CESAR</t>
-  </si>
-  <si>
     <t>JUAN CARLOS</t>
   </si>
   <si>
@@ -410,37 +437,10 @@
     <t>LETICIA</t>
   </si>
   <si>
-    <t>VALENTIN</t>
-  </si>
-  <si>
-    <t>ALFREDO</t>
-  </si>
-  <si>
-    <t>ANGEL GERARDO</t>
-  </si>
-  <si>
-    <t>EDUARDO ULISES</t>
-  </si>
-  <si>
     <t>JELIN JANET</t>
   </si>
   <si>
     <t>CESAR JOVANI</t>
-  </si>
-  <si>
-    <t>KARLA DENISSE</t>
-  </si>
-  <si>
-    <t>MONSERRAT</t>
-  </si>
-  <si>
-    <t>RICARDO ISIDRO</t>
-  </si>
-  <si>
-    <t>CESAR JAHIR</t>
-  </si>
-  <si>
-    <t>CESAR GAEL</t>
   </si>
   <si>
     <t>ELIZABETH</t>
@@ -929,7 +929,7 @@
         <v>12</v>
       </c>
       <c r="B4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C4">
         <v>6</v>
@@ -938,7 +938,7 @@
         <v>8</v>
       </c>
       <c r="E4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F4">
         <v>7</v>
@@ -983,7 +983,7 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U4">
         <v>6</v>
@@ -992,7 +992,7 @@
         <v>8</v>
       </c>
       <c r="W4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X4">
         <v>7</v>
@@ -1006,22 +1006,22 @@
         <v>13</v>
       </c>
       <c r="B5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C5">
         <v>-1</v>
       </c>
       <c r="D5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F5">
         <v>5</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H5">
         <v>-1</v>
@@ -1060,22 +1060,22 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U5">
         <v>-1</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X5">
         <v>5</v>
       </c>
       <c r="Y5">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1083,7 +1083,7 @@
         <v>14</v>
       </c>
       <c r="B6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C6">
         <v>6</v>
@@ -1092,7 +1092,7 @@
         <v>9</v>
       </c>
       <c r="E6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F6">
         <v>9</v>
@@ -1137,7 +1137,7 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U6">
         <v>6</v>
@@ -1146,7 +1146,7 @@
         <v>9</v>
       </c>
       <c r="W6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X6">
         <v>9</v>
@@ -1160,7 +1160,7 @@
         <v>15</v>
       </c>
       <c r="B7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C7">
         <v>7</v>
@@ -1169,7 +1169,7 @@
         <v>9</v>
       </c>
       <c r="E7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F7">
         <v>10</v>
@@ -1214,7 +1214,7 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U7">
         <v>7</v>
@@ -1223,7 +1223,7 @@
         <v>9</v>
       </c>
       <c r="W7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X7">
         <v>10</v>
@@ -1237,22 +1237,22 @@
         <v>16</v>
       </c>
       <c r="B8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C8">
         <v>8</v>
       </c>
       <c r="D8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F8">
         <v>9</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H8">
         <v>-1</v>
@@ -1291,22 +1291,22 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U8">
         <v>8</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X8">
         <v>9</v>
       </c>
       <c r="Y8">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1314,13 +1314,13 @@
         <v>17</v>
       </c>
       <c r="B9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C9">
         <v>-1</v>
       </c>
       <c r="D9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E9">
         <v>-1</v>
@@ -1368,13 +1368,13 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U9">
         <v>-1</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W9">
         <v>-1</v>
@@ -1391,7 +1391,7 @@
         <v>18</v>
       </c>
       <c r="B10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C10">
         <v>-1</v>
@@ -1445,7 +1445,7 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U10">
         <v>-1</v>
@@ -1468,7 +1468,7 @@
         <v>19</v>
       </c>
       <c r="B11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C11">
         <v>6</v>
@@ -1477,13 +1477,13 @@
         <v>8</v>
       </c>
       <c r="E11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F11">
         <v>10</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H11">
         <v>-1</v>
@@ -1522,7 +1522,7 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U11">
         <v>6</v>
@@ -1531,13 +1531,13 @@
         <v>8</v>
       </c>
       <c r="W11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X11">
         <v>10</v>
       </c>
       <c r="Y11">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1545,22 +1545,22 @@
         <v>20</v>
       </c>
       <c r="B12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C12">
         <v>-1</v>
       </c>
       <c r="D12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F12">
         <v>8</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H12">
         <v>-1</v>
@@ -1599,22 +1599,22 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U12">
         <v>-1</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X12">
         <v>8</v>
       </c>
       <c r="Y12">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1622,22 +1622,22 @@
         <v>21</v>
       </c>
       <c r="B13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C13">
         <v>6</v>
       </c>
       <c r="D13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F13">
         <v>6</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H13">
         <v>-1</v>
@@ -1676,22 +1676,22 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U13">
         <v>6</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X13">
         <v>6</v>
       </c>
       <c r="Y13">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1699,7 +1699,7 @@
         <v>22</v>
       </c>
       <c r="B14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C14">
         <v>8</v>
@@ -1708,13 +1708,13 @@
         <v>9</v>
       </c>
       <c r="E14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F14">
         <v>9</v>
       </c>
       <c r="G14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H14">
         <v>-1</v>
@@ -1753,7 +1753,7 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U14">
         <v>8</v>
@@ -1762,13 +1762,13 @@
         <v>9</v>
       </c>
       <c r="W14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X14">
         <v>9</v>
       </c>
       <c r="Y14">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1776,16 +1776,16 @@
         <v>23</v>
       </c>
       <c r="B15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C15">
         <v>-1</v>
       </c>
       <c r="D15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F15">
         <v>7</v>
@@ -1830,16 +1830,16 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U15">
         <v>-1</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X15">
         <v>7</v>
@@ -1853,7 +1853,7 @@
         <v>24</v>
       </c>
       <c r="B16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C16">
         <v>-1</v>
@@ -1862,13 +1862,13 @@
         <v>9</v>
       </c>
       <c r="E16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F16">
         <v>6</v>
       </c>
       <c r="G16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H16">
         <v>-1</v>
@@ -1907,7 +1907,7 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U16">
         <v>-1</v>
@@ -1916,13 +1916,13 @@
         <v>9</v>
       </c>
       <c r="W16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X16">
         <v>6</v>
       </c>
       <c r="Y16">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1930,7 +1930,7 @@
         <v>25</v>
       </c>
       <c r="B17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C17">
         <v>8</v>
@@ -1939,13 +1939,13 @@
         <v>9</v>
       </c>
       <c r="E17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F17">
         <v>8</v>
       </c>
       <c r="G17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H17">
         <v>-1</v>
@@ -1984,7 +1984,7 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U17">
         <v>8</v>
@@ -1993,13 +1993,13 @@
         <v>9</v>
       </c>
       <c r="W17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X17">
         <v>8</v>
       </c>
       <c r="Y17">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2007,7 +2007,7 @@
         <v>26</v>
       </c>
       <c r="B18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C18">
         <v>-1</v>
@@ -2061,7 +2061,7 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U18">
         <v>-1</v>
@@ -2084,7 +2084,7 @@
         <v>27</v>
       </c>
       <c r="B19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C19">
         <v>7</v>
@@ -2093,7 +2093,7 @@
         <v>9</v>
       </c>
       <c r="E19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F19">
         <v>9</v>
@@ -2138,7 +2138,7 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U19">
         <v>7</v>
@@ -2147,7 +2147,7 @@
         <v>9</v>
       </c>
       <c r="W19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X19">
         <v>9</v>
@@ -2161,7 +2161,7 @@
         <v>28</v>
       </c>
       <c r="B20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C20">
         <v>8</v>
@@ -2170,13 +2170,13 @@
         <v>8</v>
       </c>
       <c r="E20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F20">
         <v>8</v>
       </c>
       <c r="G20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H20">
         <v>-1</v>
@@ -2215,7 +2215,7 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U20">
         <v>8</v>
@@ -2224,13 +2224,13 @@
         <v>8</v>
       </c>
       <c r="W20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X20">
         <v>8</v>
       </c>
       <c r="Y20">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2238,7 +2238,7 @@
         <v>29</v>
       </c>
       <c r="B21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C21">
         <v>-1</v>
@@ -2247,7 +2247,7 @@
         <v>9</v>
       </c>
       <c r="E21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F21">
         <v>8</v>
@@ -2292,7 +2292,7 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U21">
         <v>-1</v>
@@ -2301,7 +2301,7 @@
         <v>9</v>
       </c>
       <c r="W21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X21">
         <v>8</v>
@@ -2315,7 +2315,7 @@
         <v>30</v>
       </c>
       <c r="B22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C22">
         <v>6</v>
@@ -2324,13 +2324,13 @@
         <v>9</v>
       </c>
       <c r="E22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F22">
         <v>6</v>
       </c>
       <c r="G22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H22">
         <v>-1</v>
@@ -2369,7 +2369,7 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U22">
         <v>6</v>
@@ -2378,13 +2378,13 @@
         <v>9</v>
       </c>
       <c r="W22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X22">
         <v>6</v>
       </c>
       <c r="Y22">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2392,7 +2392,7 @@
         <v>31</v>
       </c>
       <c r="B23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C23">
         <v>9</v>
@@ -2401,13 +2401,13 @@
         <v>9</v>
       </c>
       <c r="E23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F23">
         <v>10</v>
       </c>
       <c r="G23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H23">
         <v>-1</v>
@@ -2446,7 +2446,7 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U23">
         <v>9</v>
@@ -2455,13 +2455,13 @@
         <v>9</v>
       </c>
       <c r="W23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X23">
         <v>10</v>
       </c>
       <c r="Y23">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2469,7 +2469,7 @@
         <v>32</v>
       </c>
       <c r="B24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C24">
         <v>-1</v>
@@ -2478,13 +2478,13 @@
         <v>9</v>
       </c>
       <c r="E24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F24">
         <v>7</v>
       </c>
       <c r="G24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H24">
         <v>-1</v>
@@ -2523,7 +2523,7 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U24">
         <v>-1</v>
@@ -2532,13 +2532,13 @@
         <v>9</v>
       </c>
       <c r="W24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X24">
         <v>7</v>
       </c>
       <c r="Y24">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2546,7 +2546,7 @@
         <v>33</v>
       </c>
       <c r="B25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C25">
         <v>6</v>
@@ -2555,7 +2555,7 @@
         <v>9</v>
       </c>
       <c r="E25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F25">
         <v>7</v>
@@ -2600,7 +2600,7 @@
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U25">
         <v>6</v>
@@ -2609,7 +2609,7 @@
         <v>9</v>
       </c>
       <c r="W25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X25">
         <v>7</v>
@@ -2623,7 +2623,7 @@
         <v>34</v>
       </c>
       <c r="B26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C26">
         <v>6</v>
@@ -2632,7 +2632,7 @@
         <v>9</v>
       </c>
       <c r="E26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F26">
         <v>10</v>
@@ -2677,7 +2677,7 @@
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U26">
         <v>6</v>
@@ -2686,7 +2686,7 @@
         <v>9</v>
       </c>
       <c r="W26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X26">
         <v>10</v>
@@ -2700,13 +2700,13 @@
         <v>35</v>
       </c>
       <c r="B27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C27">
         <v>-1</v>
       </c>
       <c r="D27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E27">
         <v>-1</v>
@@ -2754,13 +2754,13 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U27">
         <v>-1</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W27">
         <v>-1</v>
@@ -2777,7 +2777,7 @@
         <v>36</v>
       </c>
       <c r="B28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C28">
         <v>8</v>
@@ -2786,13 +2786,13 @@
         <v>10</v>
       </c>
       <c r="E28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F28">
         <v>7</v>
       </c>
       <c r="G28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H28">
         <v>-1</v>
@@ -2831,7 +2831,7 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U28">
         <v>8</v>
@@ -2840,13 +2840,13 @@
         <v>10</v>
       </c>
       <c r="W28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X28">
         <v>7</v>
       </c>
       <c r="Y28">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2854,7 +2854,7 @@
         <v>37</v>
       </c>
       <c r="B29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C29">
         <v>6</v>
@@ -2863,13 +2863,13 @@
         <v>9</v>
       </c>
       <c r="E29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F29">
         <v>10</v>
       </c>
       <c r="G29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H29">
         <v>-1</v>
@@ -2908,7 +2908,7 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U29">
         <v>6</v>
@@ -2917,13 +2917,13 @@
         <v>9</v>
       </c>
       <c r="W29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X29">
         <v>10</v>
       </c>
       <c r="Y29">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2931,7 +2931,7 @@
         <v>38</v>
       </c>
       <c r="B30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C30">
         <v>-1</v>
@@ -2940,13 +2940,13 @@
         <v>10</v>
       </c>
       <c r="E30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F30">
         <v>10</v>
       </c>
       <c r="G30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H30">
         <v>-1</v>
@@ -2985,7 +2985,7 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U30">
         <v>-1</v>
@@ -2994,13 +2994,13 @@
         <v>10</v>
       </c>
       <c r="W30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X30">
         <v>10</v>
       </c>
       <c r="Y30">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -3008,7 +3008,7 @@
         <v>39</v>
       </c>
       <c r="B31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C31">
         <v>6</v>
@@ -3017,7 +3017,7 @@
         <v>9</v>
       </c>
       <c r="E31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F31">
         <v>7</v>
@@ -3062,7 +3062,7 @@
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U31">
         <v>6</v>
@@ -3071,7 +3071,7 @@
         <v>9</v>
       </c>
       <c r="W31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X31">
         <v>7</v>
@@ -3085,7 +3085,7 @@
         <v>40</v>
       </c>
       <c r="B32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C32">
         <v>-1</v>
@@ -3094,13 +3094,13 @@
         <v>9</v>
       </c>
       <c r="E32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F32">
         <v>6</v>
       </c>
       <c r="G32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H32">
         <v>-1</v>
@@ -3139,7 +3139,7 @@
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U32">
         <v>-1</v>
@@ -3148,13 +3148,13 @@
         <v>9</v>
       </c>
       <c r="W32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X32">
         <v>6</v>
       </c>
       <c r="Y32">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3162,7 +3162,7 @@
         <v>41</v>
       </c>
       <c r="B33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C33">
         <v>-1</v>
@@ -3171,13 +3171,13 @@
         <v>9</v>
       </c>
       <c r="E33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F33">
         <v>6</v>
       </c>
       <c r="G33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H33">
         <v>-1</v>
@@ -3216,7 +3216,7 @@
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U33">
         <v>-1</v>
@@ -3225,13 +3225,13 @@
         <v>9</v>
       </c>
       <c r="W33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X33">
         <v>6</v>
       </c>
       <c r="Y33">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3239,7 +3239,7 @@
         <v>42</v>
       </c>
       <c r="B34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C34">
         <v>-1</v>
@@ -3293,7 +3293,7 @@
         <v>-1</v>
       </c>
       <c r="T34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U34">
         <v>-1</v>
@@ -3316,7 +3316,7 @@
         <v>43</v>
       </c>
       <c r="B35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C35">
         <v>8</v>
@@ -3325,13 +3325,13 @@
         <v>9</v>
       </c>
       <c r="E35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F35">
         <v>9</v>
       </c>
       <c r="G35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H35">
         <v>-1</v>
@@ -3370,7 +3370,7 @@
         <v>-1</v>
       </c>
       <c r="T35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U35">
         <v>8</v>
@@ -3379,13 +3379,13 @@
         <v>9</v>
       </c>
       <c r="W35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X35">
         <v>9</v>
       </c>
       <c r="Y35">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -3441,7 +3441,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
         <v>53</v>
@@ -3450,22 +3450,25 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>56.25</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
+      <c r="H2">
+        <v>6.9</v>
+      </c>
       <c r="I2">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="J2">
-        <v>100</v>
+        <v>43.75</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -3479,22 +3482,25 @@
         <v>32</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>56.25</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
+      <c r="H3">
+        <v>6.4</v>
+      </c>
       <c r="I3">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="J3">
-        <v>100</v>
+        <v>43.75</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -3508,27 +3514,30 @@
         <v>32</v>
       </c>
       <c r="D4">
+        <v>24</v>
+      </c>
+      <c r="E4">
+        <v>8</v>
+      </c>
+      <c r="F4">
+        <v>75</v>
+      </c>
+      <c r="G4">
+        <v>25</v>
+      </c>
+      <c r="H4">
+        <v>6.6</v>
+      </c>
+      <c r="I4">
         <v>0</v>
       </c>
-      <c r="E4">
+      <c r="J4">
         <v>0</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>32</v>
-      </c>
-      <c r="J4">
-        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>56</v>
@@ -3537,30 +3546,30 @@
         <v>32</v>
       </c>
       <c r="D5">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="E5">
+        <v>6</v>
+      </c>
+      <c r="F5">
+        <v>81.25</v>
+      </c>
+      <c r="G5">
+        <v>18.75</v>
+      </c>
+      <c r="H5">
+        <v>7.5</v>
+      </c>
+      <c r="I5">
         <v>0</v>
       </c>
-      <c r="F5">
-        <v>56.25</v>
-      </c>
-      <c r="G5">
+      <c r="J5">
         <v>0</v>
-      </c>
-      <c r="H5">
-        <v>6.9</v>
-      </c>
-      <c r="I5">
-        <v>14</v>
-      </c>
-      <c r="J5">
-        <v>43.75</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>57</v>
@@ -3569,30 +3578,30 @@
         <v>32</v>
       </c>
       <c r="D6">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>71.88</v>
+        <v>84.38</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6">
-        <v>8.9</v>
+        <v>8.4</v>
       </c>
       <c r="I6">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J6">
-        <v>28.13</v>
+        <v>15.63</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
         <v>58</v>
@@ -3601,25 +3610,25 @@
         <v>32</v>
       </c>
       <c r="D7">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E7">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>81.25</v>
+        <v>93.75</v>
       </c>
       <c r="G7">
-        <v>18.75</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>7.5</v>
+        <v>8.6</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>6.25</v>
       </c>
     </row>
   </sheetData>
@@ -3629,7 +3638,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F120"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3664,153 +3673,153 @@
         <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="D2" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>19330051920246</v>
+        <v>19330051920247</v>
       </c>
       <c r="B3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C3" t="s">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="D3" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>19330051920246</v>
+        <v>19330051920248</v>
       </c>
       <c r="B4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="D4" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>19330051920247</v>
+        <v>19330051920249</v>
       </c>
       <c r="B5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C5" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="D5" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>19330051920247</v>
+        <v>19330051920251</v>
       </c>
       <c r="B6" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C6" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="D6" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>19330051920247</v>
+        <v>19330051920251</v>
       </c>
       <c r="B7" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C7" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="D7" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>19330051920247</v>
+        <v>19330051920251</v>
       </c>
       <c r="B8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C8" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="D8" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>19330051920247</v>
+        <v>19330051920252</v>
       </c>
       <c r="B9" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C9" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="D9" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="E9" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
         <v>57</v>
@@ -3818,19 +3827,19 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>19330051920248</v>
+        <v>19330051920252</v>
       </c>
       <c r="B10" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C10" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D10" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F10" t="s">
         <v>53</v>
@@ -3838,16 +3847,16 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>19330051920248</v>
+        <v>19330051920252</v>
       </c>
       <c r="B11" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C11" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D11" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
@@ -3858,39 +3867,39 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>19330051920248</v>
+        <v>19330051920433</v>
       </c>
       <c r="B12" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C12" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D12" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="E12" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F12" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>19330051920249</v>
+        <v>19330051920258</v>
       </c>
       <c r="B13" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C13" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D13" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="E13" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F13" t="s">
         <v>53</v>
@@ -3898,16 +3907,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>19330051920249</v>
+        <v>19330051920258</v>
       </c>
       <c r="B14" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C14" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D14" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="E14" t="s">
         <v>10</v>
@@ -3918,156 +3927,156 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>19330051920249</v>
+        <v>19330051920257</v>
       </c>
       <c r="B15" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C15" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D15" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="E15" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F15" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>19330051920250</v>
+        <v>19330051920259</v>
       </c>
       <c r="B16" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C16" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D16" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>19330051920250</v>
+        <v>19330051920259</v>
       </c>
       <c r="B17" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C17" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D17" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="E17" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F17" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>19330051920250</v>
+        <v>19330051920259</v>
       </c>
       <c r="B18" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C18" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D18" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="E18" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F18" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>19330051920250</v>
+        <v>19330051920259</v>
       </c>
       <c r="B19" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C19" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D19" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="E19" t="s">
         <v>7</v>
       </c>
       <c r="F19" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>19330051920251</v>
+        <v>19330051920260</v>
       </c>
       <c r="B20" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C20" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D20" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="E20" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F20" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>19330051920251</v>
+        <v>19330051920263</v>
       </c>
       <c r="B21" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C21" t="s">
         <v>91</v>
       </c>
       <c r="D21" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="E21" t="s">
         <v>6</v>
       </c>
       <c r="F21" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>19330051920251</v>
+        <v>19330051920263</v>
       </c>
       <c r="B22" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C22" t="s">
         <v>91</v>
       </c>
       <c r="D22" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="E22" t="s">
         <v>10</v>
@@ -4078,139 +4087,139 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>19330051920251</v>
+        <v>19330051920266</v>
       </c>
       <c r="B23" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C23" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D23" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="E23" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F23" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>19330051920251</v>
+        <v>19330051920402</v>
       </c>
       <c r="B24" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="C24" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D24" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="E24" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F24" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>19330051920252</v>
+        <v>19330051920400</v>
       </c>
       <c r="B25" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="C25" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D25" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="E25" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F25" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>19330051920252</v>
+        <v>19330051920403</v>
       </c>
       <c r="B26" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="C26" t="s">
-        <v>93</v>
+        <v>64</v>
       </c>
       <c r="D26" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="E26" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F26" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>19330051920252</v>
+        <v>19330051920403</v>
       </c>
       <c r="B27" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="C27" t="s">
-        <v>93</v>
+        <v>64</v>
       </c>
       <c r="D27" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="E27" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F27" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28">
-        <v>19330051920252</v>
+        <v>19330051920403</v>
       </c>
       <c r="B28" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="C28" t="s">
-        <v>93</v>
+        <v>64</v>
       </c>
       <c r="D28" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="E28" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F28" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29">
-        <v>19330051920253</v>
+        <v>19330051920406</v>
       </c>
       <c r="B29" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C29" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="D29" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="E29" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F29" t="s">
         <v>53</v>
@@ -4218,16 +4227,16 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30">
-        <v>19330051920253</v>
+        <v>19330051920407</v>
       </c>
       <c r="B30" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="C30" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D30" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E30" t="s">
         <v>10</v>
@@ -4238,39 +4247,39 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31">
-        <v>19330051920253</v>
+        <v>19330051920409</v>
       </c>
       <c r="B31" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C31" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D31" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E31" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F31" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32">
-        <v>19330051920433</v>
+        <v>19330051920411</v>
       </c>
       <c r="B32" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="C32" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D32" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E32" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F32" t="s">
         <v>53</v>
@@ -4278,1762 +4287,82 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33">
-        <v>19330051920433</v>
+        <v>19330051920412</v>
       </c>
       <c r="B33" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="C33" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="D33" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E33" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F33" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34">
-        <v>19330051920433</v>
+        <v>19330051920412</v>
       </c>
       <c r="B34" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="C34" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="D34" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E34" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F34" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35">
-        <v>19330051920433</v>
+        <v>19330051920412</v>
       </c>
       <c r="B35" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="C35" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="D35" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E35" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F35" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36">
-        <v>19330051920433</v>
+        <v>19330051920412</v>
       </c>
       <c r="B36" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="C36" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="D36" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E36" t="s">
         <v>7</v>
       </c>
       <c r="F36" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>19330051920256</v>
-      </c>
-      <c r="B37" t="s">
-        <v>72</v>
-      </c>
-      <c r="C37" t="s">
-        <v>95</v>
-      </c>
-      <c r="D37" t="s">
-        <v>119</v>
-      </c>
-      <c r="E37" t="s">
-        <v>8</v>
-      </c>
-      <c r="F37" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>19330051920256</v>
-      </c>
-      <c r="B38" t="s">
-        <v>72</v>
-      </c>
-      <c r="C38" t="s">
-        <v>95</v>
-      </c>
-      <c r="D38" t="s">
-        <v>119</v>
-      </c>
-      <c r="E38" t="s">
-        <v>10</v>
-      </c>
-      <c r="F38" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>19330051920256</v>
-      </c>
-      <c r="B39" t="s">
-        <v>72</v>
-      </c>
-      <c r="C39" t="s">
-        <v>95</v>
-      </c>
-      <c r="D39" t="s">
-        <v>119</v>
-      </c>
-      <c r="E39" t="s">
-        <v>5</v>
-      </c>
-      <c r="F39" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>19330051920254</v>
-      </c>
-      <c r="B40" t="s">
-        <v>72</v>
-      </c>
-      <c r="C40" t="s">
-        <v>68</v>
-      </c>
-      <c r="D40" t="s">
-        <v>120</v>
-      </c>
-      <c r="E40" t="s">
-        <v>8</v>
-      </c>
-      <c r="F40" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>19330051920254</v>
-      </c>
-      <c r="B41" t="s">
-        <v>72</v>
-      </c>
-      <c r="C41" t="s">
-        <v>68</v>
-      </c>
-      <c r="D41" t="s">
-        <v>120</v>
-      </c>
-      <c r="E41" t="s">
-        <v>10</v>
-      </c>
-      <c r="F41" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
-        <v>19330051920254</v>
-      </c>
-      <c r="B42" t="s">
-        <v>72</v>
-      </c>
-      <c r="C42" t="s">
-        <v>68</v>
-      </c>
-      <c r="D42" t="s">
-        <v>120</v>
-      </c>
-      <c r="E42" t="s">
-        <v>5</v>
-      </c>
-      <c r="F42" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43">
-        <v>19330051920254</v>
-      </c>
-      <c r="B43" t="s">
-        <v>72</v>
-      </c>
-      <c r="C43" t="s">
-        <v>68</v>
-      </c>
-      <c r="D43" t="s">
-        <v>120</v>
-      </c>
-      <c r="E43" t="s">
-        <v>7</v>
-      </c>
-      <c r="F43" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44">
-        <v>19330051920258</v>
-      </c>
-      <c r="B44" t="s">
-        <v>72</v>
-      </c>
-      <c r="C44" t="s">
-        <v>96</v>
-      </c>
-      <c r="D44" t="s">
-        <v>121</v>
-      </c>
-      <c r="E44" t="s">
-        <v>8</v>
-      </c>
-      <c r="F44" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45">
-        <v>19330051920258</v>
-      </c>
-      <c r="B45" t="s">
-        <v>72</v>
-      </c>
-      <c r="C45" t="s">
-        <v>96</v>
-      </c>
-      <c r="D45" t="s">
-        <v>121</v>
-      </c>
-      <c r="E45" t="s">
-        <v>6</v>
-      </c>
-      <c r="F45" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46">
-        <v>19330051920258</v>
-      </c>
-      <c r="B46" t="s">
-        <v>72</v>
-      </c>
-      <c r="C46" t="s">
-        <v>96</v>
-      </c>
-      <c r="D46" t="s">
-        <v>121</v>
-      </c>
-      <c r="E46" t="s">
-        <v>10</v>
-      </c>
-      <c r="F46" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47">
-        <v>19330051920258</v>
-      </c>
-      <c r="B47" t="s">
-        <v>72</v>
-      </c>
-      <c r="C47" t="s">
-        <v>96</v>
-      </c>
-      <c r="D47" t="s">
-        <v>121</v>
-      </c>
-      <c r="E47" t="s">
-        <v>5</v>
-      </c>
-      <c r="F47" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48">
-        <v>19330051920258</v>
-      </c>
-      <c r="B48" t="s">
-        <v>72</v>
-      </c>
-      <c r="C48" t="s">
-        <v>96</v>
-      </c>
-      <c r="D48" t="s">
-        <v>121</v>
-      </c>
-      <c r="E48" t="s">
-        <v>7</v>
-      </c>
-      <c r="F48" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49">
-        <v>19330051920257</v>
-      </c>
-      <c r="B49" t="s">
-        <v>72</v>
-      </c>
-      <c r="C49" t="s">
-        <v>97</v>
-      </c>
-      <c r="D49" t="s">
-        <v>122</v>
-      </c>
-      <c r="E49" t="s">
-        <v>8</v>
-      </c>
-      <c r="F49" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50">
-        <v>19330051920257</v>
-      </c>
-      <c r="B50" t="s">
-        <v>72</v>
-      </c>
-      <c r="C50" t="s">
-        <v>97</v>
-      </c>
-      <c r="D50" t="s">
-        <v>122</v>
-      </c>
-      <c r="E50" t="s">
-        <v>6</v>
-      </c>
-      <c r="F50" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51">
-        <v>19330051920257</v>
-      </c>
-      <c r="B51" t="s">
-        <v>72</v>
-      </c>
-      <c r="C51" t="s">
-        <v>97</v>
-      </c>
-      <c r="D51" t="s">
-        <v>122</v>
-      </c>
-      <c r="E51" t="s">
-        <v>10</v>
-      </c>
-      <c r="F51" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52">
-        <v>19330051920257</v>
-      </c>
-      <c r="B52" t="s">
-        <v>72</v>
-      </c>
-      <c r="C52" t="s">
-        <v>97</v>
-      </c>
-      <c r="D52" t="s">
-        <v>122</v>
-      </c>
-      <c r="E52" t="s">
-        <v>5</v>
-      </c>
-      <c r="F52" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53">
-        <v>19330051920259</v>
-      </c>
-      <c r="B53" t="s">
-        <v>73</v>
-      </c>
-      <c r="C53" t="s">
-        <v>98</v>
-      </c>
-      <c r="D53" t="s">
-        <v>123</v>
-      </c>
-      <c r="E53" t="s">
-        <v>8</v>
-      </c>
-      <c r="F53" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54">
-        <v>19330051920259</v>
-      </c>
-      <c r="B54" t="s">
-        <v>73</v>
-      </c>
-      <c r="C54" t="s">
-        <v>98</v>
-      </c>
-      <c r="D54" t="s">
-        <v>123</v>
-      </c>
-      <c r="E54" t="s">
-        <v>6</v>
-      </c>
-      <c r="F54" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55">
-        <v>19330051920259</v>
-      </c>
-      <c r="B55" t="s">
-        <v>73</v>
-      </c>
-      <c r="C55" t="s">
-        <v>98</v>
-      </c>
-      <c r="D55" t="s">
-        <v>123</v>
-      </c>
-      <c r="E55" t="s">
-        <v>10</v>
-      </c>
-      <c r="F55" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56">
-        <v>19330051920259</v>
-      </c>
-      <c r="B56" t="s">
-        <v>73</v>
-      </c>
-      <c r="C56" t="s">
-        <v>98</v>
-      </c>
-      <c r="D56" t="s">
-        <v>123</v>
-      </c>
-      <c r="E56" t="s">
-        <v>5</v>
-      </c>
-      <c r="F56" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57">
-        <v>19330051920259</v>
-      </c>
-      <c r="B57" t="s">
-        <v>73</v>
-      </c>
-      <c r="C57" t="s">
-        <v>98</v>
-      </c>
-      <c r="D57" t="s">
-        <v>123</v>
-      </c>
-      <c r="E57" t="s">
-        <v>7</v>
-      </c>
-      <c r="F57" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
-      <c r="A58">
-        <v>19330051920255</v>
-      </c>
-      <c r="B58" t="s">
-        <v>72</v>
-      </c>
-      <c r="C58" t="s">
-        <v>99</v>
-      </c>
-      <c r="D58" t="s">
-        <v>124</v>
-      </c>
-      <c r="E58" t="s">
-        <v>8</v>
-      </c>
-      <c r="F58" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
-      <c r="A59">
-        <v>19330051920255</v>
-      </c>
-      <c r="B59" t="s">
-        <v>72</v>
-      </c>
-      <c r="C59" t="s">
-        <v>99</v>
-      </c>
-      <c r="D59" t="s">
-        <v>124</v>
-      </c>
-      <c r="E59" t="s">
-        <v>10</v>
-      </c>
-      <c r="F59" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
-      <c r="A60">
-        <v>19330051920255</v>
-      </c>
-      <c r="B60" t="s">
-        <v>72</v>
-      </c>
-      <c r="C60" t="s">
-        <v>99</v>
-      </c>
-      <c r="D60" t="s">
-        <v>124</v>
-      </c>
-      <c r="E60" t="s">
-        <v>5</v>
-      </c>
-      <c r="F60" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
-      <c r="A61">
-        <v>19330051920260</v>
-      </c>
-      <c r="B61" t="s">
-        <v>74</v>
-      </c>
-      <c r="C61" t="s">
-        <v>100</v>
-      </c>
-      <c r="D61" t="s">
-        <v>125</v>
-      </c>
-      <c r="E61" t="s">
-        <v>8</v>
-      </c>
-      <c r="F61" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62">
-        <v>19330051920260</v>
-      </c>
-      <c r="B62" t="s">
-        <v>74</v>
-      </c>
-      <c r="C62" t="s">
-        <v>100</v>
-      </c>
-      <c r="D62" t="s">
-        <v>125</v>
-      </c>
-      <c r="E62" t="s">
-        <v>10</v>
-      </c>
-      <c r="F62" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
-      <c r="A63">
-        <v>19330051920260</v>
-      </c>
-      <c r="B63" t="s">
-        <v>74</v>
-      </c>
-      <c r="C63" t="s">
-        <v>100</v>
-      </c>
-      <c r="D63" t="s">
-        <v>125</v>
-      </c>
-      <c r="E63" t="s">
-        <v>5</v>
-      </c>
-      <c r="F63" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="A64">
-        <v>19330051920263</v>
-      </c>
-      <c r="B64" t="s">
-        <v>75</v>
-      </c>
-      <c r="C64" t="s">
-        <v>88</v>
-      </c>
-      <c r="D64" t="s">
-        <v>126</v>
-      </c>
-      <c r="E64" t="s">
-        <v>8</v>
-      </c>
-      <c r="F64" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
-      <c r="A65">
-        <v>19330051920263</v>
-      </c>
-      <c r="B65" t="s">
-        <v>75</v>
-      </c>
-      <c r="C65" t="s">
-        <v>88</v>
-      </c>
-      <c r="D65" t="s">
-        <v>126</v>
-      </c>
-      <c r="E65" t="s">
-        <v>6</v>
-      </c>
-      <c r="F65" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="A66">
-        <v>19330051920263</v>
-      </c>
-      <c r="B66" t="s">
-        <v>75</v>
-      </c>
-      <c r="C66" t="s">
-        <v>88</v>
-      </c>
-      <c r="D66" t="s">
-        <v>126</v>
-      </c>
-      <c r="E66" t="s">
-        <v>10</v>
-      </c>
-      <c r="F66" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67">
-        <v>19330051920263</v>
-      </c>
-      <c r="B67" t="s">
-        <v>75</v>
-      </c>
-      <c r="C67" t="s">
-        <v>88</v>
-      </c>
-      <c r="D67" t="s">
-        <v>126</v>
-      </c>
-      <c r="E67" t="s">
-        <v>5</v>
-      </c>
-      <c r="F67" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
-      <c r="A68">
-        <v>19330051920261</v>
-      </c>
-      <c r="B68" t="s">
-        <v>76</v>
-      </c>
-      <c r="C68" t="s">
-        <v>101</v>
-      </c>
-      <c r="D68" t="s">
-        <v>127</v>
-      </c>
-      <c r="E68" t="s">
-        <v>8</v>
-      </c>
-      <c r="F68" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="A69">
-        <v>19330051920261</v>
-      </c>
-      <c r="B69" t="s">
-        <v>76</v>
-      </c>
-      <c r="C69" t="s">
-        <v>101</v>
-      </c>
-      <c r="D69" t="s">
-        <v>127</v>
-      </c>
-      <c r="E69" t="s">
-        <v>10</v>
-      </c>
-      <c r="F69" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
-      <c r="A70">
-        <v>19330051920261</v>
-      </c>
-      <c r="B70" t="s">
-        <v>76</v>
-      </c>
-      <c r="C70" t="s">
-        <v>101</v>
-      </c>
-      <c r="D70" t="s">
-        <v>127</v>
-      </c>
-      <c r="E70" t="s">
-        <v>5</v>
-      </c>
-      <c r="F70" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="A71">
-        <v>19330051920265</v>
-      </c>
-      <c r="B71" t="s">
-        <v>77</v>
-      </c>
-      <c r="C71" t="s">
-        <v>71</v>
-      </c>
-      <c r="D71" t="s">
-        <v>128</v>
-      </c>
-      <c r="E71" t="s">
-        <v>8</v>
-      </c>
-      <c r="F71" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6">
-      <c r="A72">
-        <v>19330051920265</v>
-      </c>
-      <c r="B72" t="s">
-        <v>77</v>
-      </c>
-      <c r="C72" t="s">
-        <v>71</v>
-      </c>
-      <c r="D72" t="s">
-        <v>128</v>
-      </c>
-      <c r="E72" t="s">
-        <v>10</v>
-      </c>
-      <c r="F72" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6">
-      <c r="A73">
-        <v>19330051920265</v>
-      </c>
-      <c r="B73" t="s">
-        <v>77</v>
-      </c>
-      <c r="C73" t="s">
-        <v>71</v>
-      </c>
-      <c r="D73" t="s">
-        <v>128</v>
-      </c>
-      <c r="E73" t="s">
-        <v>5</v>
-      </c>
-      <c r="F73" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="A74">
-        <v>19330051920267</v>
-      </c>
-      <c r="B74" t="s">
-        <v>78</v>
-      </c>
-      <c r="C74" t="s">
-        <v>102</v>
-      </c>
-      <c r="D74" t="s">
-        <v>129</v>
-      </c>
-      <c r="E74" t="s">
-        <v>8</v>
-      </c>
-      <c r="F74" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
-      <c r="A75">
-        <v>19330051920267</v>
-      </c>
-      <c r="B75" t="s">
-        <v>78</v>
-      </c>
-      <c r="C75" t="s">
-        <v>102</v>
-      </c>
-      <c r="D75" t="s">
-        <v>129</v>
-      </c>
-      <c r="E75" t="s">
-        <v>10</v>
-      </c>
-      <c r="F75" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6">
-      <c r="A76">
-        <v>19330051920267</v>
-      </c>
-      <c r="B76" t="s">
-        <v>78</v>
-      </c>
-      <c r="C76" t="s">
-        <v>102</v>
-      </c>
-      <c r="D76" t="s">
-        <v>129</v>
-      </c>
-      <c r="E76" t="s">
-        <v>5</v>
-      </c>
-      <c r="F76" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6">
-      <c r="A77">
-        <v>19330051920266</v>
-      </c>
-      <c r="B77" t="s">
-        <v>78</v>
-      </c>
-      <c r="C77" t="s">
-        <v>102</v>
-      </c>
-      <c r="D77" t="s">
-        <v>130</v>
-      </c>
-      <c r="E77" t="s">
-        <v>8</v>
-      </c>
-      <c r="F77" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6">
-      <c r="A78">
-        <v>19330051920266</v>
-      </c>
-      <c r="B78" t="s">
-        <v>78</v>
-      </c>
-      <c r="C78" t="s">
-        <v>102</v>
-      </c>
-      <c r="D78" t="s">
-        <v>130</v>
-      </c>
-      <c r="E78" t="s">
-        <v>6</v>
-      </c>
-      <c r="F78" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6">
-      <c r="A79">
-        <v>19330051920266</v>
-      </c>
-      <c r="B79" t="s">
-        <v>78</v>
-      </c>
-      <c r="C79" t="s">
-        <v>102</v>
-      </c>
-      <c r="D79" t="s">
-        <v>130</v>
-      </c>
-      <c r="E79" t="s">
-        <v>10</v>
-      </c>
-      <c r="F79" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6">
-      <c r="A80">
-        <v>19330051920266</v>
-      </c>
-      <c r="B80" t="s">
-        <v>78</v>
-      </c>
-      <c r="C80" t="s">
-        <v>102</v>
-      </c>
-      <c r="D80" t="s">
-        <v>130</v>
-      </c>
-      <c r="E80" t="s">
-        <v>5</v>
-      </c>
-      <c r="F80" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6">
-      <c r="A81">
-        <v>19330051920402</v>
-      </c>
-      <c r="B81" t="s">
-        <v>79</v>
-      </c>
-      <c r="C81" t="s">
-        <v>103</v>
-      </c>
-      <c r="D81" t="s">
-        <v>131</v>
-      </c>
-      <c r="E81" t="s">
-        <v>8</v>
-      </c>
-      <c r="F81" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6">
-      <c r="A82">
-        <v>19330051920402</v>
-      </c>
-      <c r="B82" t="s">
-        <v>79</v>
-      </c>
-      <c r="C82" t="s">
-        <v>103</v>
-      </c>
-      <c r="D82" t="s">
-        <v>131</v>
-      </c>
-      <c r="E82" t="s">
-        <v>10</v>
-      </c>
-      <c r="F82" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6">
-      <c r="A83">
-        <v>19330051920402</v>
-      </c>
-      <c r="B83" t="s">
-        <v>79</v>
-      </c>
-      <c r="C83" t="s">
-        <v>103</v>
-      </c>
-      <c r="D83" t="s">
-        <v>131</v>
-      </c>
-      <c r="E83" t="s">
-        <v>5</v>
-      </c>
-      <c r="F83" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6">
-      <c r="A84">
-        <v>19330051920400</v>
-      </c>
-      <c r="B84" t="s">
-        <v>80</v>
-      </c>
-      <c r="C84" t="s">
-        <v>104</v>
-      </c>
-      <c r="D84" t="s">
-        <v>132</v>
-      </c>
-      <c r="E84" t="s">
-        <v>8</v>
-      </c>
-      <c r="F84" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6">
-      <c r="A85">
-        <v>19330051920400</v>
-      </c>
-      <c r="B85" t="s">
-        <v>80</v>
-      </c>
-      <c r="C85" t="s">
-        <v>104</v>
-      </c>
-      <c r="D85" t="s">
-        <v>132</v>
-      </c>
-      <c r="E85" t="s">
-        <v>10</v>
-      </c>
-      <c r="F85" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6">
-      <c r="A86">
-        <v>19330051920400</v>
-      </c>
-      <c r="B86" t="s">
-        <v>80</v>
-      </c>
-      <c r="C86" t="s">
-        <v>104</v>
-      </c>
-      <c r="D86" t="s">
-        <v>132</v>
-      </c>
-      <c r="E86" t="s">
-        <v>5</v>
-      </c>
-      <c r="F86" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6">
-      <c r="A87">
-        <v>19330051920403</v>
-      </c>
-      <c r="B87" t="s">
-        <v>81</v>
-      </c>
-      <c r="C87" t="s">
-        <v>64</v>
-      </c>
-      <c r="D87" t="s">
-        <v>133</v>
-      </c>
-      <c r="E87" t="s">
-        <v>8</v>
-      </c>
-      <c r="F87" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6">
-      <c r="A88">
-        <v>19330051920403</v>
-      </c>
-      <c r="B88" t="s">
-        <v>81</v>
-      </c>
-      <c r="C88" t="s">
-        <v>64</v>
-      </c>
-      <c r="D88" t="s">
-        <v>133</v>
-      </c>
-      <c r="E88" t="s">
-        <v>6</v>
-      </c>
-      <c r="F88" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6">
-      <c r="A89">
-        <v>19330051920403</v>
-      </c>
-      <c r="B89" t="s">
-        <v>81</v>
-      </c>
-      <c r="C89" t="s">
-        <v>64</v>
-      </c>
-      <c r="D89" t="s">
-        <v>133</v>
-      </c>
-      <c r="E89" t="s">
-        <v>10</v>
-      </c>
-      <c r="F89" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6">
-      <c r="A90">
-        <v>19330051920403</v>
-      </c>
-      <c r="B90" t="s">
-        <v>81</v>
-      </c>
-      <c r="C90" t="s">
-        <v>64</v>
-      </c>
-      <c r="D90" t="s">
-        <v>133</v>
-      </c>
-      <c r="E90" t="s">
-        <v>5</v>
-      </c>
-      <c r="F90" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6">
-      <c r="A91">
-        <v>19330051920403</v>
-      </c>
-      <c r="B91" t="s">
-        <v>81</v>
-      </c>
-      <c r="C91" t="s">
-        <v>64</v>
-      </c>
-      <c r="D91" t="s">
-        <v>133</v>
-      </c>
-      <c r="E91" t="s">
-        <v>7</v>
-      </c>
-      <c r="F91" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6">
-      <c r="A92">
-        <v>19330051920348</v>
-      </c>
-      <c r="B92" t="s">
-        <v>82</v>
-      </c>
-      <c r="C92" t="s">
-        <v>105</v>
-      </c>
-      <c r="D92" t="s">
-        <v>134</v>
-      </c>
-      <c r="E92" t="s">
-        <v>8</v>
-      </c>
-      <c r="F92" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6">
-      <c r="A93">
-        <v>19330051920348</v>
-      </c>
-      <c r="B93" t="s">
-        <v>82</v>
-      </c>
-      <c r="C93" t="s">
-        <v>105</v>
-      </c>
-      <c r="D93" t="s">
-        <v>134</v>
-      </c>
-      <c r="E93" t="s">
-        <v>10</v>
-      </c>
-      <c r="F93" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6">
-      <c r="A94">
-        <v>19330051920348</v>
-      </c>
-      <c r="B94" t="s">
-        <v>82</v>
-      </c>
-      <c r="C94" t="s">
-        <v>105</v>
-      </c>
-      <c r="D94" t="s">
-        <v>134</v>
-      </c>
-      <c r="E94" t="s">
-        <v>5</v>
-      </c>
-      <c r="F94" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6">
-      <c r="A95">
-        <v>19330051920405</v>
-      </c>
-      <c r="B95" t="s">
-        <v>83</v>
-      </c>
-      <c r="C95" t="s">
-        <v>106</v>
-      </c>
-      <c r="D95" t="s">
-        <v>135</v>
-      </c>
-      <c r="E95" t="s">
-        <v>8</v>
-      </c>
-      <c r="F95" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6">
-      <c r="A96">
-        <v>19330051920405</v>
-      </c>
-      <c r="B96" t="s">
-        <v>83</v>
-      </c>
-      <c r="C96" t="s">
-        <v>106</v>
-      </c>
-      <c r="D96" t="s">
-        <v>135</v>
-      </c>
-      <c r="E96" t="s">
-        <v>10</v>
-      </c>
-      <c r="F96" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6">
-      <c r="A97">
-        <v>19330051920405</v>
-      </c>
-      <c r="B97" t="s">
-        <v>83</v>
-      </c>
-      <c r="C97" t="s">
-        <v>106</v>
-      </c>
-      <c r="D97" t="s">
-        <v>135</v>
-      </c>
-      <c r="E97" t="s">
-        <v>5</v>
-      </c>
-      <c r="F97" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6">
-      <c r="A98">
-        <v>19330051920406</v>
-      </c>
-      <c r="B98" t="s">
-        <v>84</v>
-      </c>
-      <c r="C98" t="s">
-        <v>107</v>
-      </c>
-      <c r="D98" t="s">
-        <v>136</v>
-      </c>
-      <c r="E98" t="s">
-        <v>8</v>
-      </c>
-      <c r="F98" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6">
-      <c r="A99">
-        <v>19330051920406</v>
-      </c>
-      <c r="B99" t="s">
-        <v>84</v>
-      </c>
-      <c r="C99" t="s">
-        <v>107</v>
-      </c>
-      <c r="D99" t="s">
-        <v>136</v>
-      </c>
-      <c r="E99" t="s">
-        <v>6</v>
-      </c>
-      <c r="F99" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6">
-      <c r="A100">
-        <v>19330051920406</v>
-      </c>
-      <c r="B100" t="s">
-        <v>84</v>
-      </c>
-      <c r="C100" t="s">
-        <v>107</v>
-      </c>
-      <c r="D100" t="s">
-        <v>136</v>
-      </c>
-      <c r="E100" t="s">
-        <v>10</v>
-      </c>
-      <c r="F100" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6">
-      <c r="A101">
-        <v>19330051920406</v>
-      </c>
-      <c r="B101" t="s">
-        <v>84</v>
-      </c>
-      <c r="C101" t="s">
-        <v>107</v>
-      </c>
-      <c r="D101" t="s">
-        <v>136</v>
-      </c>
-      <c r="E101" t="s">
-        <v>5</v>
-      </c>
-      <c r="F101" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6">
-      <c r="A102">
-        <v>19330051920407</v>
-      </c>
-      <c r="B102" t="s">
-        <v>85</v>
-      </c>
-      <c r="C102" t="s">
-        <v>86</v>
-      </c>
-      <c r="D102" t="s">
-        <v>137</v>
-      </c>
-      <c r="E102" t="s">
-        <v>8</v>
-      </c>
-      <c r="F102" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6">
-      <c r="A103">
-        <v>19330051920407</v>
-      </c>
-      <c r="B103" t="s">
-        <v>85</v>
-      </c>
-      <c r="C103" t="s">
-        <v>86</v>
-      </c>
-      <c r="D103" t="s">
-        <v>137</v>
-      </c>
-      <c r="E103" t="s">
-        <v>10</v>
-      </c>
-      <c r="F103" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6">
-      <c r="A104">
-        <v>19330051920407</v>
-      </c>
-      <c r="B104" t="s">
-        <v>85</v>
-      </c>
-      <c r="C104" t="s">
-        <v>86</v>
-      </c>
-      <c r="D104" t="s">
-        <v>137</v>
-      </c>
-      <c r="E104" t="s">
-        <v>5</v>
-      </c>
-      <c r="F104" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6">
-      <c r="A105">
-        <v>19330051920409</v>
-      </c>
-      <c r="B105" t="s">
-        <v>86</v>
-      </c>
-      <c r="C105" t="s">
-        <v>90</v>
-      </c>
-      <c r="D105" t="s">
-        <v>138</v>
-      </c>
-      <c r="E105" t="s">
-        <v>8</v>
-      </c>
-      <c r="F105" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6">
-      <c r="A106">
-        <v>19330051920409</v>
-      </c>
-      <c r="B106" t="s">
-        <v>86</v>
-      </c>
-      <c r="C106" t="s">
-        <v>90</v>
-      </c>
-      <c r="D106" t="s">
-        <v>138</v>
-      </c>
-      <c r="E106" t="s">
-        <v>6</v>
-      </c>
-      <c r="F106" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6">
-      <c r="A107">
-        <v>19330051920409</v>
-      </c>
-      <c r="B107" t="s">
-        <v>86</v>
-      </c>
-      <c r="C107" t="s">
-        <v>90</v>
-      </c>
-      <c r="D107" t="s">
-        <v>138</v>
-      </c>
-      <c r="E107" t="s">
-        <v>10</v>
-      </c>
-      <c r="F107" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6">
-      <c r="A108">
-        <v>19330051920409</v>
-      </c>
-      <c r="B108" t="s">
-        <v>86</v>
-      </c>
-      <c r="C108" t="s">
-        <v>90</v>
-      </c>
-      <c r="D108" t="s">
-        <v>138</v>
-      </c>
-      <c r="E108" t="s">
-        <v>5</v>
-      </c>
-      <c r="F108" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6">
-      <c r="A109">
-        <v>19330051920411</v>
-      </c>
-      <c r="B109" t="s">
-        <v>86</v>
-      </c>
-      <c r="C109" t="s">
-        <v>108</v>
-      </c>
-      <c r="D109" t="s">
-        <v>139</v>
-      </c>
-      <c r="E109" t="s">
-        <v>8</v>
-      </c>
-      <c r="F109" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6">
-      <c r="A110">
-        <v>19330051920411</v>
-      </c>
-      <c r="B110" t="s">
-        <v>86</v>
-      </c>
-      <c r="C110" t="s">
-        <v>108</v>
-      </c>
-      <c r="D110" t="s">
-        <v>139</v>
-      </c>
-      <c r="E110" t="s">
-        <v>6</v>
-      </c>
-      <c r="F110" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6">
-      <c r="A111">
-        <v>19330051920411</v>
-      </c>
-      <c r="B111" t="s">
-        <v>86</v>
-      </c>
-      <c r="C111" t="s">
-        <v>108</v>
-      </c>
-      <c r="D111" t="s">
-        <v>139</v>
-      </c>
-      <c r="E111" t="s">
-        <v>10</v>
-      </c>
-      <c r="F111" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6">
-      <c r="A112">
-        <v>19330051920411</v>
-      </c>
-      <c r="B112" t="s">
-        <v>86</v>
-      </c>
-      <c r="C112" t="s">
-        <v>108</v>
-      </c>
-      <c r="D112" t="s">
-        <v>139</v>
-      </c>
-      <c r="E112" t="s">
-        <v>5</v>
-      </c>
-      <c r="F112" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6">
-      <c r="A113">
-        <v>19330051920412</v>
-      </c>
-      <c r="B113" t="s">
-        <v>87</v>
-      </c>
-      <c r="C113" t="s">
-        <v>86</v>
-      </c>
-      <c r="D113" t="s">
-        <v>140</v>
-      </c>
-      <c r="E113" t="s">
-        <v>8</v>
-      </c>
-      <c r="F113" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6">
-      <c r="A114">
-        <v>19330051920412</v>
-      </c>
-      <c r="B114" t="s">
-        <v>87</v>
-      </c>
-      <c r="C114" t="s">
-        <v>86</v>
-      </c>
-      <c r="D114" t="s">
-        <v>140</v>
-      </c>
-      <c r="E114" t="s">
-        <v>6</v>
-      </c>
-      <c r="F114" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6">
-      <c r="A115">
-        <v>19330051920412</v>
-      </c>
-      <c r="B115" t="s">
-        <v>87</v>
-      </c>
-      <c r="C115" t="s">
-        <v>86</v>
-      </c>
-      <c r="D115" t="s">
-        <v>140</v>
-      </c>
-      <c r="E115" t="s">
-        <v>10</v>
-      </c>
-      <c r="F115" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6">
-      <c r="A116">
-        <v>19330051920412</v>
-      </c>
-      <c r="B116" t="s">
-        <v>87</v>
-      </c>
-      <c r="C116" t="s">
-        <v>86</v>
-      </c>
-      <c r="D116" t="s">
-        <v>140</v>
-      </c>
-      <c r="E116" t="s">
-        <v>5</v>
-      </c>
-      <c r="F116" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6">
-      <c r="A117">
-        <v>19330051920412</v>
-      </c>
-      <c r="B117" t="s">
-        <v>87</v>
-      </c>
-      <c r="C117" t="s">
-        <v>86</v>
-      </c>
-      <c r="D117" t="s">
-        <v>140</v>
-      </c>
-      <c r="E117" t="s">
-        <v>7</v>
-      </c>
-      <c r="F117" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6">
-      <c r="A118">
-        <v>19330051920414</v>
-      </c>
-      <c r="B118" t="s">
-        <v>88</v>
-      </c>
-      <c r="C118" t="s">
-        <v>109</v>
-      </c>
-      <c r="D118" t="s">
-        <v>141</v>
-      </c>
-      <c r="E118" t="s">
-        <v>8</v>
-      </c>
-      <c r="F118" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6">
-      <c r="A119">
-        <v>19330051920414</v>
-      </c>
-      <c r="B119" t="s">
-        <v>88</v>
-      </c>
-      <c r="C119" t="s">
-        <v>109</v>
-      </c>
-      <c r="D119" t="s">
-        <v>141</v>
-      </c>
-      <c r="E119" t="s">
-        <v>10</v>
-      </c>
-      <c r="F119" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6">
-      <c r="A120">
-        <v>19330051920414</v>
-      </c>
-      <c r="B120" t="s">
-        <v>88</v>
-      </c>
-      <c r="C120" t="s">
-        <v>109</v>
-      </c>
-      <c r="D120" t="s">
-        <v>141</v>
-      </c>
-      <c r="E120" t="s">
-        <v>5</v>
-      </c>
-      <c r="F120" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -6069,529 +4398,529 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>19330051920247</v>
+        <v>19330051920259</v>
       </c>
       <c r="B2" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="D2" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>19330051920251</v>
+        <v>19330051920412</v>
       </c>
       <c r="B3" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="C3" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="D3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>19330051920433</v>
+        <v>19330051920251</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="D4" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>19330051920258</v>
+        <v>19330051920252</v>
       </c>
       <c r="B5" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C5" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="D5" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>19330051920259</v>
+        <v>19330051920403</v>
       </c>
       <c r="B6" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C6" t="s">
-        <v>98</v>
+        <v>64</v>
       </c>
       <c r="D6" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>19330051920403</v>
+        <v>19330051920258</v>
       </c>
       <c r="B7" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>64</v>
+        <v>87</v>
       </c>
       <c r="D7" t="s">
-        <v>133</v>
+        <v>104</v>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>19330051920412</v>
+        <v>19330051920263</v>
       </c>
       <c r="B8" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="C8" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D8" t="s">
-        <v>140</v>
+        <v>108</v>
       </c>
       <c r="E8">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>19330051920250</v>
+        <v>19330051920246</v>
       </c>
       <c r="B9" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C9" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="D9" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="E9">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>19330051920252</v>
+        <v>19330051920247</v>
       </c>
       <c r="B10" t="s">
+        <v>64</v>
+      </c>
+      <c r="C10" t="s">
         <v>69</v>
       </c>
-      <c r="C10" t="s">
-        <v>93</v>
-      </c>
       <c r="D10" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="E10">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>19330051920254</v>
+        <v>19330051920248</v>
       </c>
       <c r="B11" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="C11" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="D11" t="s">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="E11">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>19330051920257</v>
+        <v>19330051920249</v>
       </c>
       <c r="B12" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="C12" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="D12" t="s">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="E12">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>19330051920263</v>
+        <v>19330051920433</v>
       </c>
       <c r="B13" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="C13" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D13" t="s">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="E13">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>19330051920266</v>
+        <v>19330051920257</v>
       </c>
       <c r="B14" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="C14" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="D14" t="s">
-        <v>130</v>
+        <v>105</v>
       </c>
       <c r="E14">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>19330051920406</v>
+        <v>19330051920260</v>
       </c>
       <c r="B15" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="C15" t="s">
+        <v>90</v>
+      </c>
+      <c r="D15" t="s">
         <v>107</v>
       </c>
-      <c r="D15" t="s">
-        <v>136</v>
-      </c>
       <c r="E15">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>19330051920409</v>
+        <v>19330051920266</v>
       </c>
       <c r="B16" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="C16" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D16" t="s">
-        <v>138</v>
+        <v>109</v>
       </c>
       <c r="E16">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>19330051920411</v>
+        <v>19330051920402</v>
       </c>
       <c r="B17" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="C17" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="D17" t="s">
-        <v>139</v>
+        <v>110</v>
       </c>
       <c r="E17">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>19330051920246</v>
+        <v>19330051920400</v>
       </c>
       <c r="B18" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="C18" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D18" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E18">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>19330051920248</v>
+        <v>19330051920406</v>
       </c>
       <c r="B19" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="C19" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D19" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E19">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>19330051920249</v>
+        <v>19330051920407</v>
       </c>
       <c r="B20" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="C20" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="D20" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E20">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>19330051920253</v>
+        <v>19330051920409</v>
       </c>
       <c r="B21" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C21" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D21" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E21">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>19330051920256</v>
+        <v>19330051920411</v>
       </c>
       <c r="B22" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="C22" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D22" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E22">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>19330051920255</v>
+        <v>19330051920250</v>
       </c>
       <c r="B23" t="s">
-        <v>72</v>
+        <v>118</v>
       </c>
       <c r="C23" t="s">
-        <v>99</v>
+        <v>124</v>
       </c>
       <c r="D23" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="E23">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>19330051920260</v>
+        <v>19330051920253</v>
       </c>
       <c r="B24" t="s">
-        <v>74</v>
+        <v>119</v>
       </c>
       <c r="C24" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="D24" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="E24">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>19330051920261</v>
+        <v>19330051920256</v>
       </c>
       <c r="B25" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="C25" t="s">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="D25" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="E25">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>19330051920265</v>
+        <v>19330051920254</v>
       </c>
       <c r="B26" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="C26" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D26" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="E26">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>19330051920267</v>
+        <v>19330051920255</v>
       </c>
       <c r="B27" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="C27" t="s">
-        <v>102</v>
+        <v>126</v>
       </c>
       <c r="D27" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="E27">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>19330051920402</v>
+        <v>19330051920261</v>
       </c>
       <c r="B28" t="s">
-        <v>79</v>
+        <v>120</v>
       </c>
       <c r="C28" t="s">
-        <v>103</v>
+        <v>127</v>
       </c>
       <c r="D28" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="E28">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>19330051920400</v>
+        <v>19330051920265</v>
       </c>
       <c r="B29" t="s">
-        <v>80</v>
+        <v>121</v>
       </c>
       <c r="C29" t="s">
-        <v>104</v>
+        <v>69</v>
       </c>
       <c r="D29" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="E29">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>19330051920348</v>
+        <v>19330051920267</v>
       </c>
       <c r="B30" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="C30" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="D30" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E30">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>19330051920405</v>
+        <v>19330051920348</v>
       </c>
       <c r="B31" t="s">
-        <v>83</v>
+        <v>122</v>
       </c>
       <c r="C31" t="s">
-        <v>106</v>
+        <v>128</v>
       </c>
       <c r="D31" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E31">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>19330051920407</v>
+        <v>19330051920405</v>
       </c>
       <c r="B32" t="s">
-        <v>85</v>
+        <v>123</v>
       </c>
       <c r="C32" t="s">
-        <v>86</v>
+        <v>129</v>
       </c>
       <c r="D32" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E32">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -6599,16 +4928,16 @@
         <v>19330051920414</v>
       </c>
       <c r="B33" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C33" t="s">
-        <v>109</v>
+        <v>130</v>
       </c>
       <c r="D33" t="s">
         <v>141</v>
       </c>
       <c r="E33">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -6618,7 +4947,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6648,6 +4977,374 @@
         <v>4</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>19330051920263</v>
+      </c>
+      <c r="B2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>19330051920263</v>
+      </c>
+      <c r="B3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D3" t="s">
+        <v>108</v>
+      </c>
+      <c r="E3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>19330051920246</v>
+      </c>
+      <c r="B4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C4" t="s">
+        <v>82</v>
+      </c>
+      <c r="D4" t="s">
+        <v>97</v>
+      </c>
+      <c r="E4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G4">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>19330051920248</v>
+      </c>
+      <c r="B5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C5" t="s">
+        <v>83</v>
+      </c>
+      <c r="D5" t="s">
+        <v>99</v>
+      </c>
+      <c r="E5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" t="s">
+        <v>54</v>
+      </c>
+      <c r="G5">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>19330051920249</v>
+      </c>
+      <c r="B6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" t="s">
+        <v>84</v>
+      </c>
+      <c r="D6" t="s">
+        <v>100</v>
+      </c>
+      <c r="E6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" t="s">
+        <v>54</v>
+      </c>
+      <c r="G6">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>19330051920433</v>
+      </c>
+      <c r="B7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C7" t="s">
+        <v>86</v>
+      </c>
+      <c r="D7" t="s">
+        <v>103</v>
+      </c>
+      <c r="E7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F7" t="s">
+        <v>53</v>
+      </c>
+      <c r="G7">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>19330051920257</v>
+      </c>
+      <c r="B8" t="s">
+        <v>70</v>
+      </c>
+      <c r="C8" t="s">
+        <v>88</v>
+      </c>
+      <c r="D8" t="s">
+        <v>105</v>
+      </c>
+      <c r="E8" t="s">
+        <v>6</v>
+      </c>
+      <c r="F8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G8">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>19330051920260</v>
+      </c>
+      <c r="B9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9" t="s">
+        <v>90</v>
+      </c>
+      <c r="D9" t="s">
+        <v>107</v>
+      </c>
+      <c r="E9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" t="s">
+        <v>54</v>
+      </c>
+      <c r="G9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>19330051920261</v>
+      </c>
+      <c r="B10" t="s">
+        <v>120</v>
+      </c>
+      <c r="C10" t="s">
+        <v>127</v>
+      </c>
+      <c r="D10" t="s">
+        <v>136</v>
+      </c>
+      <c r="E10" t="s">
+        <v>5</v>
+      </c>
+      <c r="F10" t="s">
+        <v>55</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>19330051920266</v>
+      </c>
+      <c r="B11" t="s">
+        <v>74</v>
+      </c>
+      <c r="C11" t="s">
+        <v>92</v>
+      </c>
+      <c r="D11" t="s">
+        <v>109</v>
+      </c>
+      <c r="E11" t="s">
+        <v>6</v>
+      </c>
+      <c r="F11" t="s">
+        <v>53</v>
+      </c>
+      <c r="G11">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>19330051920402</v>
+      </c>
+      <c r="B12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C12" t="s">
+        <v>93</v>
+      </c>
+      <c r="D12" t="s">
+        <v>110</v>
+      </c>
+      <c r="E12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" t="s">
+        <v>54</v>
+      </c>
+      <c r="G12">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>19330051920400</v>
+      </c>
+      <c r="B13" t="s">
+        <v>76</v>
+      </c>
+      <c r="C13" t="s">
+        <v>94</v>
+      </c>
+      <c r="D13" t="s">
+        <v>111</v>
+      </c>
+      <c r="E13" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" t="s">
+        <v>54</v>
+      </c>
+      <c r="G13">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>19330051920406</v>
+      </c>
+      <c r="B14" t="s">
+        <v>78</v>
+      </c>
+      <c r="C14" t="s">
+        <v>95</v>
+      </c>
+      <c r="D14" t="s">
+        <v>113</v>
+      </c>
+      <c r="E14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F14" t="s">
+        <v>53</v>
+      </c>
+      <c r="G14">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>19330051920407</v>
+      </c>
+      <c r="B15" t="s">
+        <v>79</v>
+      </c>
+      <c r="C15" t="s">
+        <v>80</v>
+      </c>
+      <c r="D15" t="s">
+        <v>114</v>
+      </c>
+      <c r="E15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G15">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>19330051920409</v>
+      </c>
+      <c r="B16" t="s">
+        <v>80</v>
+      </c>
+      <c r="C16" t="s">
+        <v>83</v>
+      </c>
+      <c r="D16" t="s">
+        <v>115</v>
+      </c>
+      <c r="E16" t="s">
+        <v>6</v>
+      </c>
+      <c r="F16" t="s">
+        <v>53</v>
+      </c>
+      <c r="G16">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>19330051920411</v>
+      </c>
+      <c r="B17" t="s">
+        <v>80</v>
+      </c>
+      <c r="C17" t="s">
+        <v>96</v>
+      </c>
+      <c r="D17" t="s">
+        <v>116</v>
+      </c>
+      <c r="E17" t="s">
+        <v>6</v>
+      </c>
+      <c r="F17" t="s">
+        <v>53</v>
+      </c>
+      <c r="G17">
+        <v>-1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/grupos/6ASV - Estadisticos 20212.xlsx
+++ b/grupos/6ASV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="142">
   <si>
     <t>Materia</t>
   </si>
@@ -245,58 +245,151 @@
     <t>MIXCOHUA</t>
   </si>
   <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>ROMAN</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>SANTILLANA</t>
+  </si>
+  <si>
+    <t>LEYVA</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>PALMA</t>
+  </si>
+  <si>
+    <t>GERARDO</t>
+  </si>
+  <si>
+    <t>SERRANO</t>
+  </si>
+  <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>GALEOTE</t>
+  </si>
+  <si>
+    <t>SIERRA</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>TREJO</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>PINO</t>
+  </si>
+  <si>
+    <t>MOISES EFRAIN</t>
+  </si>
+  <si>
+    <t>JOSE EMMANUEL</t>
+  </si>
+  <si>
+    <t>BRANDON AXEL</t>
+  </si>
+  <si>
+    <t>GABRIEL MARTIN</t>
+  </si>
+  <si>
+    <t>VALERIA</t>
+  </si>
+  <si>
+    <t>JULIO GABRIEL</t>
+  </si>
+  <si>
+    <t>CRISTIAN</t>
+  </si>
+  <si>
+    <t>JAVIER FERNANDO</t>
+  </si>
+  <si>
+    <t>ALEXIS</t>
+  </si>
+  <si>
+    <t>DIEGO ABDEL JARIN</t>
+  </si>
+  <si>
+    <t>AIDA</t>
+  </si>
+  <si>
+    <t>CESAR</t>
+  </si>
+  <si>
+    <t>VALENTIN</t>
+  </si>
+  <si>
+    <t>EDUARDO ULISES</t>
+  </si>
+  <si>
+    <t>KARLA DENISSE</t>
+  </si>
+  <si>
+    <t>MONSERRAT</t>
+  </si>
+  <si>
+    <t>RICARDO ISIDRO</t>
+  </si>
+  <si>
+    <t>CESAR JAHIR</t>
+  </si>
+  <si>
+    <t>CESAR GAEL</t>
+  </si>
+  <si>
+    <t>CORDOVA</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>MANI</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
     <t>MORALES</t>
   </si>
   <si>
     <t>MONSALVO</t>
   </si>
   <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>ROMAN</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>SANTILLANA</t>
-  </si>
-  <si>
-    <t>LEYVA</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>PALMA</t>
-  </si>
-  <si>
-    <t>GERARDO</t>
-  </si>
-  <si>
-    <t>SERRANO</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>GALEOTE</t>
-  </si>
-  <si>
-    <t>SIERRA</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>TREJO</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>GUIZA</t>
+  </si>
+  <si>
+    <t>CUAHUA</t>
+  </si>
+  <si>
+    <t>TZOMPAXTLE</t>
+  </si>
+  <si>
+    <t>ZAPATA</t>
   </si>
   <si>
     <t>CASTELLANOS</t>
@@ -305,136 +398,43 @@
     <t>QUINTERO</t>
   </si>
   <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>PINO</t>
-  </si>
-  <si>
-    <t>MOISES EFRAIN</t>
-  </si>
-  <si>
-    <t>JOSE EMMANUEL</t>
-  </si>
-  <si>
-    <t>BRANDON AXEL</t>
-  </si>
-  <si>
-    <t>GABRIEL MARTIN</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
-  </si>
-  <si>
-    <t>JULIO GABRIEL</t>
-  </si>
-  <si>
-    <t>CRISTIAN</t>
-  </si>
-  <si>
-    <t>JAVIER FERNANDO</t>
-  </si>
-  <si>
-    <t>ALEXIS</t>
-  </si>
-  <si>
-    <t>DIEGO ABDEL JARIN</t>
-  </si>
-  <si>
-    <t>AIDA</t>
-  </si>
-  <si>
-    <t>CESAR</t>
-  </si>
-  <si>
-    <t>VALENTIN</t>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>LUENGAS</t>
+  </si>
+  <si>
+    <t>ANGELA ALESSANDRA</t>
+  </si>
+  <si>
+    <t>LUIS ANGEL</t>
+  </si>
+  <si>
+    <t>ERICA</t>
+  </si>
+  <si>
+    <t>ZAYRA JOSELIN</t>
+  </si>
+  <si>
+    <t>WENDY</t>
+  </si>
+  <si>
+    <t>JUAN CARLOS</t>
+  </si>
+  <si>
+    <t>KARLA</t>
+  </si>
+  <si>
+    <t>LETICIA</t>
   </si>
   <si>
     <t>ALFREDO</t>
   </si>
   <si>
     <t>ANGEL GERARDO</t>
-  </si>
-  <si>
-    <t>EDUARDO ULISES</t>
-  </si>
-  <si>
-    <t>KARLA DENISSE</t>
-  </si>
-  <si>
-    <t>MONSERRAT</t>
-  </si>
-  <si>
-    <t>RICARDO ISIDRO</t>
-  </si>
-  <si>
-    <t>CESAR JAHIR</t>
-  </si>
-  <si>
-    <t>CESAR GAEL</t>
-  </si>
-  <si>
-    <t>CORDOVA</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>MANI</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>GUIZA</t>
-  </si>
-  <si>
-    <t>CUAHUA</t>
-  </si>
-  <si>
-    <t>TZOMPAXTLE</t>
-  </si>
-  <si>
-    <t>ZAPATA</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>LUENGAS</t>
-  </si>
-  <si>
-    <t>ANGELA ALESSANDRA</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
-  </si>
-  <si>
-    <t>ERICA</t>
-  </si>
-  <si>
-    <t>ZAYRA JOSELIN</t>
-  </si>
-  <si>
-    <t>WENDY</t>
-  </si>
-  <si>
-    <t>JUAN CARLOS</t>
-  </si>
-  <si>
-    <t>KARLA</t>
-  </si>
-  <si>
-    <t>LETICIA</t>
   </si>
   <si>
     <t>JELIN JANET</t>
@@ -1791,7 +1791,7 @@
         <v>7</v>
       </c>
       <c r="G15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H15">
         <v>-1</v>
@@ -1845,7 +1845,7 @@
         <v>7</v>
       </c>
       <c r="Y15">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -2253,7 +2253,7 @@
         <v>8</v>
       </c>
       <c r="G21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H21">
         <v>-1</v>
@@ -2307,7 +2307,7 @@
         <v>8</v>
       </c>
       <c r="Y21">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2561,7 +2561,7 @@
         <v>7</v>
       </c>
       <c r="G25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H25">
         <v>-1</v>
@@ -2615,7 +2615,7 @@
         <v>7</v>
       </c>
       <c r="Y25">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2638,7 +2638,7 @@
         <v>10</v>
       </c>
       <c r="G26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H26">
         <v>-1</v>
@@ -2692,7 +2692,7 @@
         <v>10</v>
       </c>
       <c r="Y26">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2715,7 +2715,7 @@
         <v>5</v>
       </c>
       <c r="G27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H27">
         <v>-1</v>
@@ -2769,7 +2769,7 @@
         <v>5</v>
       </c>
       <c r="Y27">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -3482,25 +3482,25 @@
         <v>32</v>
       </c>
       <c r="D3">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>56.25</v>
+        <v>71.88</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="I3">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J3">
-        <v>43.75</v>
+        <v>28.13</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -3638,7 +3638,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3673,10 +3673,10 @@
         <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D2" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
@@ -3696,7 +3696,7 @@
         <v>69</v>
       </c>
       <c r="D3" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E3" t="s">
         <v>6</v>
@@ -3713,10 +3713,10 @@
         <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D4" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
@@ -3733,10 +3733,10 @@
         <v>66</v>
       </c>
       <c r="C5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D5" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -3753,10 +3753,10 @@
         <v>67</v>
       </c>
       <c r="C6" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D6" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -3773,10 +3773,10 @@
         <v>67</v>
       </c>
       <c r="C7" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D7" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="E7" t="s">
         <v>6</v>
@@ -3793,10 +3793,10 @@
         <v>67</v>
       </c>
       <c r="C8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D8" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="E8" t="s">
         <v>10</v>
@@ -3813,10 +3813,10 @@
         <v>68</v>
       </c>
       <c r="C9" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D9" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -3833,10 +3833,10 @@
         <v>68</v>
       </c>
       <c r="C10" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D10" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
@@ -3853,10 +3853,10 @@
         <v>68</v>
       </c>
       <c r="C11" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D11" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
@@ -3873,10 +3873,10 @@
         <v>69</v>
       </c>
       <c r="C12" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D12" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E12" t="s">
         <v>6</v>
@@ -3893,10 +3893,10 @@
         <v>70</v>
       </c>
       <c r="C13" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D13" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="E13" t="s">
         <v>6</v>
@@ -3907,42 +3907,42 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>19330051920258</v>
+        <v>19330051920257</v>
       </c>
       <c r="B14" t="s">
         <v>70</v>
       </c>
       <c r="C14" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D14" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E14" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F14" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>19330051920257</v>
+        <v>19330051920259</v>
       </c>
       <c r="B15" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C15" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D15" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E15" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -3953,16 +3953,16 @@
         <v>71</v>
       </c>
       <c r="C16" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D16" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E16" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F16" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -3973,16 +3973,16 @@
         <v>71</v>
       </c>
       <c r="C17" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D17" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E17" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F17" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -3993,70 +3993,70 @@
         <v>71</v>
       </c>
       <c r="C18" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D18" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E18" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F18" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>19330051920259</v>
+        <v>19330051920260</v>
       </c>
       <c r="B19" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D19" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E19" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F19" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>19330051920260</v>
+        <v>19330051920263</v>
       </c>
       <c r="B20" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D20" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E20" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F20" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>19330051920263</v>
+        <v>19330051920266</v>
       </c>
       <c r="B21" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C21" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D21" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E21" t="s">
         <v>6</v>
@@ -4067,36 +4067,36 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>19330051920263</v>
+        <v>19330051920403</v>
       </c>
       <c r="B22" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C22" t="s">
-        <v>91</v>
+        <v>64</v>
       </c>
       <c r="D22" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E22" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F22" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>19330051920266</v>
+        <v>19330051920403</v>
       </c>
       <c r="B23" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C23" t="s">
-        <v>92</v>
+        <v>64</v>
       </c>
       <c r="D23" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E23" t="s">
         <v>6</v>
@@ -4107,36 +4107,36 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>19330051920402</v>
+        <v>19330051920406</v>
       </c>
       <c r="B24" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C24" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D24" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E24" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F24" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>19330051920400</v>
+        <v>19330051920407</v>
       </c>
       <c r="B25" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C25" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="D25" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E25" t="s">
         <v>10</v>
@@ -4147,36 +4147,36 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>19330051920403</v>
+        <v>19330051920409</v>
       </c>
       <c r="B26" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C26" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="D26" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E26" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F26" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>19330051920403</v>
+        <v>19330051920411</v>
       </c>
       <c r="B27" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C27" t="s">
-        <v>64</v>
+        <v>92</v>
       </c>
       <c r="D27" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E27" t="s">
         <v>6</v>
@@ -4187,36 +4187,36 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28">
-        <v>19330051920403</v>
+        <v>19330051920412</v>
       </c>
       <c r="B28" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C28" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="D28" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E28" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F28" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29">
-        <v>19330051920406</v>
+        <v>19330051920412</v>
       </c>
       <c r="B29" t="s">
+        <v>79</v>
+      </c>
+      <c r="C29" t="s">
         <v>78</v>
       </c>
-      <c r="C29" t="s">
-        <v>95</v>
-      </c>
       <c r="D29" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E29" t="s">
         <v>6</v>
@@ -4227,16 +4227,16 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30">
-        <v>19330051920407</v>
+        <v>19330051920412</v>
       </c>
       <c r="B30" t="s">
         <v>79</v>
       </c>
       <c r="C30" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D30" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E30" t="s">
         <v>10</v>
@@ -4247,121 +4247,21 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31">
-        <v>19330051920409</v>
+        <v>19330051920412</v>
       </c>
       <c r="B31" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C31" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="D31" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="E31" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F31" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>19330051920411</v>
-      </c>
-      <c r="B32" t="s">
-        <v>80</v>
-      </c>
-      <c r="C32" t="s">
-        <v>96</v>
-      </c>
-      <c r="D32" t="s">
-        <v>116</v>
-      </c>
-      <c r="E32" t="s">
-        <v>6</v>
-      </c>
-      <c r="F32" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>19330051920412</v>
-      </c>
-      <c r="B33" t="s">
-        <v>81</v>
-      </c>
-      <c r="C33" t="s">
-        <v>80</v>
-      </c>
-      <c r="D33" t="s">
-        <v>117</v>
-      </c>
-      <c r="E33" t="s">
-        <v>8</v>
-      </c>
-      <c r="F33" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>19330051920412</v>
-      </c>
-      <c r="B34" t="s">
-        <v>81</v>
-      </c>
-      <c r="C34" t="s">
-        <v>80</v>
-      </c>
-      <c r="D34" t="s">
-        <v>117</v>
-      </c>
-      <c r="E34" t="s">
-        <v>6</v>
-      </c>
-      <c r="F34" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>19330051920412</v>
-      </c>
-      <c r="B35" t="s">
-        <v>81</v>
-      </c>
-      <c r="C35" t="s">
-        <v>80</v>
-      </c>
-      <c r="D35" t="s">
-        <v>117</v>
-      </c>
-      <c r="E35" t="s">
-        <v>10</v>
-      </c>
-      <c r="F35" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>19330051920412</v>
-      </c>
-      <c r="B36" t="s">
-        <v>81</v>
-      </c>
-      <c r="C36" t="s">
-        <v>80</v>
-      </c>
-      <c r="D36" t="s">
-        <v>117</v>
-      </c>
-      <c r="E36" t="s">
-        <v>7</v>
-      </c>
-      <c r="F36" t="s">
         <v>58</v>
       </c>
     </row>
@@ -4404,10 +4304,10 @@
         <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E2">
         <v>4</v>
@@ -4418,13 +4318,13 @@
         <v>19330051920412</v>
       </c>
       <c r="B3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D3" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="E3">
         <v>4</v>
@@ -4438,10 +4338,10 @@
         <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D4" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -4455,10 +4355,10 @@
         <v>68</v>
       </c>
       <c r="C5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D5" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -4469,64 +4369,64 @@
         <v>19330051920403</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C6" t="s">
         <v>64</v>
       </c>
       <c r="D6" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>19330051920258</v>
+        <v>19330051920246</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="C7" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="D7" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>19330051920263</v>
+        <v>19330051920247</v>
       </c>
       <c r="B8" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="C8" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="D8" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>19330051920246</v>
+        <v>19330051920248</v>
       </c>
       <c r="B9" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D9" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -4534,16 +4434,16 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>19330051920247</v>
+        <v>19330051920249</v>
       </c>
       <c r="B10" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C10" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="D10" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -4551,13 +4451,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>19330051920248</v>
+        <v>19330051920433</v>
       </c>
       <c r="B11" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D11" t="s">
         <v>99</v>
@@ -4568,13 +4468,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>19330051920249</v>
+        <v>19330051920258</v>
       </c>
       <c r="B12" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C12" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D12" t="s">
         <v>100</v>
@@ -4585,16 +4485,16 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>19330051920433</v>
+        <v>19330051920257</v>
       </c>
       <c r="B13" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C13" t="s">
         <v>86</v>
       </c>
       <c r="D13" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -4602,16 +4502,16 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>19330051920257</v>
+        <v>19330051920260</v>
       </c>
       <c r="B14" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C14" t="s">
         <v>88</v>
       </c>
       <c r="D14" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -4619,16 +4519,16 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>19330051920260</v>
+        <v>19330051920263</v>
       </c>
       <c r="B15" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C15" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D15" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -4642,10 +4542,10 @@
         <v>74</v>
       </c>
       <c r="C16" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D16" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="E16">
         <v>1</v>
@@ -4653,16 +4553,16 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>19330051920402</v>
+        <v>19330051920406</v>
       </c>
       <c r="B17" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D17" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -4670,16 +4570,16 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>19330051920400</v>
+        <v>19330051920407</v>
       </c>
       <c r="B18" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C18" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="D18" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -4687,16 +4587,16 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>19330051920406</v>
+        <v>19330051920409</v>
       </c>
       <c r="B19" t="s">
         <v>78</v>
       </c>
       <c r="C19" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="D19" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E19">
         <v>1</v>
@@ -4704,16 +4604,16 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>19330051920407</v>
+        <v>19330051920411</v>
       </c>
       <c r="B20" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C20" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="D20" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E20">
         <v>1</v>
@@ -4721,47 +4621,47 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>19330051920409</v>
+        <v>19330051920250</v>
       </c>
       <c r="B21" t="s">
-        <v>80</v>
+        <v>112</v>
       </c>
       <c r="C21" t="s">
-        <v>83</v>
+        <v>120</v>
       </c>
       <c r="D21" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>19330051920411</v>
+        <v>19330051920253</v>
       </c>
       <c r="B22" t="s">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="C22" t="s">
-        <v>96</v>
+        <v>118</v>
       </c>
       <c r="D22" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>19330051920250</v>
+        <v>19330051920256</v>
       </c>
       <c r="B23" t="s">
-        <v>118</v>
+        <v>70</v>
       </c>
       <c r="C23" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D23" t="s">
         <v>131</v>
@@ -4772,13 +4672,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>19330051920253</v>
+        <v>19330051920254</v>
       </c>
       <c r="B24" t="s">
-        <v>119</v>
+        <v>70</v>
       </c>
       <c r="C24" t="s">
-        <v>122</v>
+        <v>67</v>
       </c>
       <c r="D24" t="s">
         <v>132</v>
@@ -4789,13 +4689,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>19330051920256</v>
+        <v>19330051920255</v>
       </c>
       <c r="B25" t="s">
         <v>70</v>
       </c>
       <c r="C25" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D25" t="s">
         <v>133</v>
@@ -4806,13 +4706,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>19330051920254</v>
+        <v>19330051920261</v>
       </c>
       <c r="B26" t="s">
-        <v>70</v>
+        <v>114</v>
       </c>
       <c r="C26" t="s">
-        <v>67</v>
+        <v>123</v>
       </c>
       <c r="D26" t="s">
         <v>134</v>
@@ -4823,13 +4723,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>19330051920255</v>
+        <v>19330051920265</v>
       </c>
       <c r="B27" t="s">
-        <v>70</v>
+        <v>115</v>
       </c>
       <c r="C27" t="s">
-        <v>126</v>
+        <v>69</v>
       </c>
       <c r="D27" t="s">
         <v>135</v>
@@ -4840,13 +4740,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>19330051920261</v>
+        <v>19330051920267</v>
       </c>
       <c r="B28" t="s">
-        <v>120</v>
+        <v>74</v>
       </c>
       <c r="C28" t="s">
-        <v>127</v>
+        <v>90</v>
       </c>
       <c r="D28" t="s">
         <v>136</v>
@@ -4857,13 +4757,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>19330051920265</v>
+        <v>19330051920402</v>
       </c>
       <c r="B29" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C29" t="s">
-        <v>69</v>
+        <v>124</v>
       </c>
       <c r="D29" t="s">
         <v>137</v>
@@ -4874,13 +4774,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>19330051920267</v>
+        <v>19330051920400</v>
       </c>
       <c r="B30" t="s">
-        <v>74</v>
+        <v>117</v>
       </c>
       <c r="C30" t="s">
-        <v>92</v>
+        <v>125</v>
       </c>
       <c r="D30" t="s">
         <v>138</v>
@@ -4894,10 +4794,10 @@
         <v>19330051920348</v>
       </c>
       <c r="B31" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C31" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D31" t="s">
         <v>139</v>
@@ -4911,10 +4811,10 @@
         <v>19330051920405</v>
       </c>
       <c r="B32" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C32" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D32" t="s">
         <v>140</v>
@@ -4928,10 +4828,10 @@
         <v>19330051920414</v>
       </c>
       <c r="B33" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C33" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D33" t="s">
         <v>141</v>
@@ -4947,7 +4847,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4979,45 +4879,45 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920263</v>
+        <v>19330051920258</v>
       </c>
       <c r="B2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C2" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D2" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920263</v>
+        <v>19330051920258</v>
       </c>
       <c r="B3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C3" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D3" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G3">
         <v>-1</v>
@@ -5031,10 +4931,10 @@
         <v>63</v>
       </c>
       <c r="C4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D4" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
@@ -5054,10 +4954,10 @@
         <v>65</v>
       </c>
       <c r="C5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D5" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -5077,10 +4977,10 @@
         <v>66</v>
       </c>
       <c r="C6" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D6" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
@@ -5100,10 +5000,10 @@
         <v>69</v>
       </c>
       <c r="C7" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D7" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E7" t="s">
         <v>6</v>
@@ -5123,10 +5023,10 @@
         <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D8" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
@@ -5146,10 +5046,10 @@
         <v>72</v>
       </c>
       <c r="C9" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D9" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
@@ -5163,68 +5063,68 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>19330051920261</v>
+        <v>19330051920263</v>
       </c>
       <c r="B10" t="s">
-        <v>120</v>
+        <v>73</v>
       </c>
       <c r="C10" t="s">
-        <v>127</v>
+        <v>89</v>
       </c>
       <c r="D10" t="s">
-        <v>136</v>
+        <v>104</v>
       </c>
       <c r="E10" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G10">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>19330051920266</v>
+        <v>19330051920261</v>
       </c>
       <c r="B11" t="s">
-        <v>74</v>
+        <v>114</v>
       </c>
       <c r="C11" t="s">
-        <v>92</v>
+        <v>123</v>
       </c>
       <c r="D11" t="s">
-        <v>109</v>
+        <v>134</v>
       </c>
       <c r="E11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F11" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>19330051920402</v>
+        <v>19330051920266</v>
       </c>
       <c r="B12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C12" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D12" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="E12" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G12">
         <v>-1</v>
@@ -5232,22 +5132,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>19330051920400</v>
+        <v>19330051920406</v>
       </c>
       <c r="B13" t="s">
         <v>76</v>
       </c>
       <c r="C13" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D13" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E13" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F13" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G13">
         <v>-1</v>
@@ -5255,22 +5155,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>19330051920406</v>
+        <v>19330051920407</v>
       </c>
       <c r="B14" t="s">
+        <v>77</v>
+      </c>
+      <c r="C14" t="s">
         <v>78</v>
       </c>
-      <c r="C14" t="s">
-        <v>95</v>
-      </c>
       <c r="D14" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="E14" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G14">
         <v>-1</v>
@@ -5278,22 +5178,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>19330051920407</v>
+        <v>19330051920409</v>
       </c>
       <c r="B15" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C15" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D15" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="E15" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F15" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G15">
         <v>-1</v>
@@ -5301,16 +5201,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>19330051920409</v>
+        <v>19330051920411</v>
       </c>
       <c r="B16" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C16" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="D16" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="E16" t="s">
         <v>6</v>
@@ -5319,29 +5219,6 @@
         <v>53</v>
       </c>
       <c r="G16">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>19330051920411</v>
-      </c>
-      <c r="B17" t="s">
-        <v>80</v>
-      </c>
-      <c r="C17" t="s">
-        <v>96</v>
-      </c>
-      <c r="D17" t="s">
-        <v>116</v>
-      </c>
-      <c r="E17" t="s">
-        <v>6</v>
-      </c>
-      <c r="F17" t="s">
-        <v>53</v>
-      </c>
-      <c r="G17">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/6ASV - Estadisticos 20212.xlsx
+++ b/grupos/6ASV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="142">
   <si>
     <t>Materia</t>
   </si>
@@ -179,21 +179,21 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Duran Amezcua María Angélica</t>
+  </si>
+  <si>
     <t>Ortega Valle Manuel</t>
   </si>
   <si>
-    <t>Duran Amezcua María Angélica</t>
-  </si>
-  <si>
     <t>Medina Tolentino Elio</t>
   </si>
   <si>
+    <t>Jiménez Nieto Enrique</t>
+  </si>
+  <si>
     <t>Hernández Mendoza Delfina</t>
   </si>
   <si>
-    <t>Jiménez Nieto Enrique</t>
-  </si>
-  <si>
     <t>Pesce Bautista Victor Manuel</t>
   </si>
   <si>
@@ -209,22 +209,64 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>SANTILLANA</t>
+  </si>
+  <si>
+    <t>PALMA</t>
+  </si>
+  <si>
+    <t>GERARDO</t>
+  </si>
+  <si>
+    <t>SIERRA</t>
+  </si>
+  <si>
+    <t>BONILLA</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>VALERIA</t>
+  </si>
+  <si>
+    <t>JULIO GABRIEL</t>
+  </si>
+  <si>
+    <t>DIEGO ABDEL JARIN</t>
+  </si>
+  <si>
+    <t>EDUARDO ULISES</t>
+  </si>
+  <si>
+    <t>CESAR GAEL</t>
+  </si>
+  <si>
     <t>ALCANTARA</t>
   </si>
   <si>
-    <t>BONILLA</t>
-  </si>
-  <si>
     <t>CASTILLO</t>
   </si>
   <si>
     <t>CISNEROS</t>
   </si>
   <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
+    <t>CORDOVA</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
   </si>
   <si>
     <t>GONZALEZ</t>
@@ -233,19 +275,31 @@
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
     <t>LLAME</t>
   </si>
   <si>
     <t>MARTINEZ</t>
   </si>
   <si>
+    <t>MANI</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
     <t>MIXCOHUA</t>
   </si>
   <si>
-    <t>PEREZ</t>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>MONSALVO</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
   </si>
   <si>
     <t>ROMAN</t>
@@ -254,10 +308,7 @@
     <t>ROSAS</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>SANTILLANA</t>
+    <t>TREJO</t>
   </si>
   <si>
     <t>LEYVA</t>
@@ -266,39 +317,54 @@
     <t>GARCIA</t>
   </si>
   <si>
-    <t>PALMA</t>
-  </si>
-  <si>
-    <t>GERARDO</t>
+    <t>GUIZA</t>
   </si>
   <si>
     <t>SERRANO</t>
   </si>
   <si>
+    <t>CUAHUA</t>
+  </si>
+  <si>
     <t>DOMINGUEZ</t>
   </si>
   <si>
     <t>GALEOTE</t>
   </si>
   <si>
-    <t>SIERRA</t>
+    <t>TZOMPAXTLE</t>
   </si>
   <si>
     <t>VERA</t>
   </si>
   <si>
-    <t>TREJO</t>
+    <t>ZAPATA</t>
   </si>
   <si>
     <t>IXMATLAHUA</t>
   </si>
   <si>
+    <t>CASTELLANOS</t>
+  </si>
+  <si>
+    <t>QUINTERO</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
     <t>JUAREZ</t>
   </si>
   <si>
     <t>PINO</t>
   </si>
   <si>
+    <t>LUENGAS</t>
+  </si>
+  <si>
     <t>MOISES EFRAIN</t>
   </si>
   <si>
@@ -311,22 +377,28 @@
     <t>GABRIEL MARTIN</t>
   </si>
   <si>
-    <t>VALERIA</t>
-  </si>
-  <si>
-    <t>JULIO GABRIEL</t>
+    <t>ANGELA ALESSANDRA</t>
+  </si>
+  <si>
+    <t>LUIS ANGEL</t>
   </si>
   <si>
     <t>CRISTIAN</t>
   </si>
   <si>
+    <t>ERICA</t>
+  </si>
+  <si>
+    <t>ZAYRA JOSELIN</t>
+  </si>
+  <si>
     <t>JAVIER FERNANDO</t>
   </si>
   <si>
     <t>ALEXIS</t>
   </si>
   <si>
-    <t>DIEGO ABDEL JARIN</t>
+    <t>WENDY</t>
   </si>
   <si>
     <t>AIDA</t>
@@ -335,10 +407,28 @@
     <t>CESAR</t>
   </si>
   <si>
+    <t>JUAN CARLOS</t>
+  </si>
+  <si>
+    <t>KARLA</t>
+  </si>
+  <si>
+    <t>LETICIA</t>
+  </si>
+  <si>
     <t>VALENTIN</t>
   </si>
   <si>
-    <t>EDUARDO ULISES</t>
+    <t>ALFREDO</t>
+  </si>
+  <si>
+    <t>ANGEL GERARDO</t>
+  </si>
+  <si>
+    <t>JELIN JANET</t>
+  </si>
+  <si>
+    <t>CESAR JOVANI</t>
   </si>
   <si>
     <t>KARLA DENISSE</t>
@@ -351,96 +441,6 @@
   </si>
   <si>
     <t>CESAR JAHIR</t>
-  </si>
-  <si>
-    <t>CESAR GAEL</t>
-  </si>
-  <si>
-    <t>CORDOVA</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>MANI</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>MONSALVO</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>GUIZA</t>
-  </si>
-  <si>
-    <t>CUAHUA</t>
-  </si>
-  <si>
-    <t>TZOMPAXTLE</t>
-  </si>
-  <si>
-    <t>ZAPATA</t>
-  </si>
-  <si>
-    <t>CASTELLANOS</t>
-  </si>
-  <si>
-    <t>QUINTERO</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>LUENGAS</t>
-  </si>
-  <si>
-    <t>ANGELA ALESSANDRA</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
-  </si>
-  <si>
-    <t>ERICA</t>
-  </si>
-  <si>
-    <t>ZAYRA JOSELIN</t>
-  </si>
-  <si>
-    <t>WENDY</t>
-  </si>
-  <si>
-    <t>JUAN CARLOS</t>
-  </si>
-  <si>
-    <t>KARLA</t>
-  </si>
-  <si>
-    <t>LETICIA</t>
-  </si>
-  <si>
-    <t>ALFREDO</t>
-  </si>
-  <si>
-    <t>ANGEL GERARDO</t>
-  </si>
-  <si>
-    <t>JELIN JANET</t>
-  </si>
-  <si>
-    <t>CESAR JOVANI</t>
   </si>
   <si>
     <t>ELIZABETH</t>
@@ -944,25 +944,25 @@
         <v>7</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H4">
         <v>-1</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K4">
         <v>-1</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -998,7 +998,7 @@
         <v>7</v>
       </c>
       <c r="Y4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1009,7 +1009,7 @@
         <v>5</v>
       </c>
       <c r="C5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D5">
         <v>7</v>
@@ -1027,16 +1027,16 @@
         <v>-1</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K5">
         <v>-1</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M5">
         <v>-1</v>
@@ -1063,10 +1063,10 @@
         <v>5</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W5">
         <v>6</v>
@@ -1098,25 +1098,25 @@
         <v>9</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H6">
         <v>-1</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K6">
         <v>-1</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1149,10 +1149,10 @@
         <v>10</v>
       </c>
       <c r="X6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1175,25 +1175,25 @@
         <v>10</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H7">
         <v>-1</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K7">
         <v>-1</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1229,7 +1229,7 @@
         <v>10</v>
       </c>
       <c r="Y7">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1258,19 +1258,19 @@
         <v>-1</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K8">
         <v>-1</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1303,10 +1303,10 @@
         <v>10</v>
       </c>
       <c r="X8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y8">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1317,7 +1317,7 @@
         <v>5</v>
       </c>
       <c r="C9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D9">
         <v>6</v>
@@ -1329,25 +1329,25 @@
         <v>5</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H9">
         <v>-1</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K9">
         <v>-1</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1371,19 +1371,19 @@
         <v>5</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W9">
         <v>-1</v>
       </c>
       <c r="X9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y9">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1394,7 +1394,7 @@
         <v>5</v>
       </c>
       <c r="C10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D10">
         <v>8</v>
@@ -1406,25 +1406,25 @@
         <v>5</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H10">
         <v>-1</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K10">
         <v>-1</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1448,7 +1448,7 @@
         <v>5</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V10">
         <v>8</v>
@@ -1460,7 +1460,7 @@
         <v>5</v>
       </c>
       <c r="Y10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1489,19 +1489,19 @@
         <v>-1</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K11">
         <v>-1</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1528,16 +1528,16 @@
         <v>6</v>
       </c>
       <c r="V11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W11">
         <v>8</v>
       </c>
       <c r="X11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y11">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1548,7 +1548,7 @@
         <v>6</v>
       </c>
       <c r="C12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D12">
         <v>8</v>
@@ -1566,19 +1566,19 @@
         <v>-1</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K12">
         <v>-1</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1602,10 +1602,10 @@
         <v>6</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W12">
         <v>7</v>
@@ -1614,7 +1614,7 @@
         <v>8</v>
       </c>
       <c r="Y12">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1643,19 +1643,19 @@
         <v>-1</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K13">
         <v>-1</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1691,7 +1691,7 @@
         <v>6</v>
       </c>
       <c r="Y13">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1720,16 +1720,16 @@
         <v>-1</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K14">
         <v>-1</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M14">
         <v>-1</v>
@@ -1779,7 +1779,7 @@
         <v>5</v>
       </c>
       <c r="C15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D15">
         <v>7</v>
@@ -1797,19 +1797,19 @@
         <v>-1</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K15">
         <v>-1</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1833,10 +1833,10 @@
         <v>5</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W15">
         <v>9</v>
@@ -1845,7 +1845,7 @@
         <v>7</v>
       </c>
       <c r="Y15">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1856,7 +1856,7 @@
         <v>6</v>
       </c>
       <c r="C16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D16">
         <v>9</v>
@@ -1874,19 +1874,19 @@
         <v>-1</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K16">
         <v>-1</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1910,10 +1910,10 @@
         <v>6</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W16">
         <v>8</v>
@@ -1922,7 +1922,7 @@
         <v>6</v>
       </c>
       <c r="Y16">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1951,19 +1951,19 @@
         <v>-1</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K17">
         <v>-1</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -1990,16 +1990,16 @@
         <v>8</v>
       </c>
       <c r="V17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W17">
         <v>9</v>
       </c>
       <c r="X17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y17">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2010,10 +2010,10 @@
         <v>5</v>
       </c>
       <c r="C18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E18">
         <v>-1</v>
@@ -2022,13 +2022,13 @@
         <v>5</v>
       </c>
       <c r="G18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H18">
         <v>-1</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J18">
         <v>-1</v>
@@ -2037,10 +2037,10 @@
         <v>-1</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2064,10 +2064,10 @@
         <v>5</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W18">
         <v>-1</v>
@@ -2076,7 +2076,7 @@
         <v>5</v>
       </c>
       <c r="Y18">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2099,25 +2099,25 @@
         <v>9</v>
       </c>
       <c r="G19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H19">
         <v>-1</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K19">
         <v>-1</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2150,10 +2150,10 @@
         <v>9</v>
       </c>
       <c r="X19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y19">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2182,19 +2182,19 @@
         <v>-1</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K20">
         <v>-1</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2218,10 +2218,10 @@
         <v>5</v>
       </c>
       <c r="U20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W20">
         <v>7</v>
@@ -2241,7 +2241,7 @@
         <v>7</v>
       </c>
       <c r="C21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D21">
         <v>9</v>
@@ -2259,19 +2259,19 @@
         <v>-1</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K21">
         <v>-1</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2295,7 +2295,7 @@
         <v>7</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V21">
         <v>9</v>
@@ -2336,19 +2336,19 @@
         <v>-1</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K22">
         <v>-1</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2384,7 +2384,7 @@
         <v>6</v>
       </c>
       <c r="Y22">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2413,19 +2413,19 @@
         <v>-1</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K23">
         <v>-1</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2461,7 +2461,7 @@
         <v>10</v>
       </c>
       <c r="Y23">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2472,7 +2472,7 @@
         <v>8</v>
       </c>
       <c r="C24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D24">
         <v>9</v>
@@ -2490,19 +2490,19 @@
         <v>-1</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K24">
         <v>-1</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2526,7 +2526,7 @@
         <v>8</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V24">
         <v>9</v>
@@ -2538,7 +2538,7 @@
         <v>7</v>
       </c>
       <c r="Y24">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2567,19 +2567,19 @@
         <v>-1</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K25">
         <v>-1</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2603,7 +2603,7 @@
         <v>8</v>
       </c>
       <c r="U25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V25">
         <v>9</v>
@@ -2612,10 +2612,10 @@
         <v>9</v>
       </c>
       <c r="X25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y25">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2644,19 +2644,19 @@
         <v>-1</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K26">
         <v>-1</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2692,7 +2692,7 @@
         <v>10</v>
       </c>
       <c r="Y26">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2703,7 +2703,7 @@
         <v>5</v>
       </c>
       <c r="C27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D27">
         <v>6</v>
@@ -2721,19 +2721,19 @@
         <v>-1</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K27">
         <v>-1</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2757,7 +2757,7 @@
         <v>5</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V27">
         <v>6</v>
@@ -2766,10 +2766,10 @@
         <v>-1</v>
       </c>
       <c r="X27">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y27">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2798,19 +2798,19 @@
         <v>-1</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K28">
         <v>-1</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2875,19 +2875,19 @@
         <v>-1</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K29">
         <v>-1</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2934,7 +2934,7 @@
         <v>7</v>
       </c>
       <c r="C30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D30">
         <v>10</v>
@@ -2952,19 +2952,19 @@
         <v>-1</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K30">
         <v>-1</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -2988,7 +2988,7 @@
         <v>7</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V30">
         <v>10</v>
@@ -3000,7 +3000,7 @@
         <v>10</v>
       </c>
       <c r="Y30">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -3023,25 +3023,25 @@
         <v>7</v>
       </c>
       <c r="G31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H31">
         <v>-1</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K31">
         <v>-1</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -3065,7 +3065,7 @@
         <v>8</v>
       </c>
       <c r="U31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V31">
         <v>9</v>
@@ -3077,7 +3077,7 @@
         <v>7</v>
       </c>
       <c r="Y31">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -3088,7 +3088,7 @@
         <v>6</v>
       </c>
       <c r="C32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D32">
         <v>9</v>
@@ -3106,19 +3106,19 @@
         <v>-1</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K32">
         <v>-1</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3142,7 +3142,7 @@
         <v>6</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V32">
         <v>9</v>
@@ -3154,7 +3154,7 @@
         <v>6</v>
       </c>
       <c r="Y32">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3165,7 +3165,7 @@
         <v>6</v>
       </c>
       <c r="C33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D33">
         <v>9</v>
@@ -3183,16 +3183,16 @@
         <v>-1</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K33">
         <v>-1</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M33">
         <v>-1</v>
@@ -3219,7 +3219,7 @@
         <v>6</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V33">
         <v>9</v>
@@ -3242,10 +3242,10 @@
         <v>5</v>
       </c>
       <c r="C34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E34">
         <v>-1</v>
@@ -3254,25 +3254,25 @@
         <v>5</v>
       </c>
       <c r="G34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H34">
         <v>-1</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K34">
         <v>-1</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3296,10 +3296,10 @@
         <v>5</v>
       </c>
       <c r="U34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W34">
         <v>-1</v>
@@ -3308,7 +3308,7 @@
         <v>5</v>
       </c>
       <c r="Y34">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3337,19 +3337,19 @@
         <v>-1</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K35">
         <v>-1</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3373,7 +3373,7 @@
         <v>8</v>
       </c>
       <c r="U35">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V35">
         <v>9</v>
@@ -3382,10 +3382,10 @@
         <v>7</v>
       </c>
       <c r="X35">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y35">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -3441,7 +3441,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>53</v>
@@ -3450,30 +3450,30 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E2">
+        <v>15</v>
+      </c>
+      <c r="F2">
+        <v>53.13</v>
+      </c>
+      <c r="G2">
+        <v>46.88</v>
+      </c>
+      <c r="H2">
+        <v>6</v>
+      </c>
+      <c r="I2">
         <v>0</v>
       </c>
-      <c r="F2">
-        <v>56.25</v>
-      </c>
-      <c r="G2">
+      <c r="J2">
         <v>0</v>
-      </c>
-      <c r="H2">
-        <v>6.9</v>
-      </c>
-      <c r="I2">
-        <v>14</v>
-      </c>
-      <c r="J2">
-        <v>43.75</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>54</v>
@@ -3482,25 +3482,25 @@
         <v>32</v>
       </c>
       <c r="D3">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F3">
-        <v>71.88</v>
+        <v>62.5</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="H3">
         <v>6.3</v>
       </c>
       <c r="I3">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>28.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -3537,7 +3537,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>56</v>
@@ -3546,30 +3546,30 @@
         <v>32</v>
       </c>
       <c r="D5">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>81.25</v>
+        <v>84.38</v>
       </c>
       <c r="G5">
-        <v>18.75</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>7.5</v>
+        <v>8.4</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>15.63</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>57</v>
@@ -3578,25 +3578,25 @@
         <v>32</v>
       </c>
       <c r="D6">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E6">
+        <v>4</v>
+      </c>
+      <c r="F6">
+        <v>87.5</v>
+      </c>
+      <c r="G6">
+        <v>12.5</v>
+      </c>
+      <c r="H6">
+        <v>7.5</v>
+      </c>
+      <c r="I6">
         <v>0</v>
       </c>
-      <c r="F6">
-        <v>84.38</v>
-      </c>
-      <c r="G6">
+      <c r="J6">
         <v>0</v>
-      </c>
-      <c r="H6">
-        <v>8.4</v>
-      </c>
-      <c r="I6">
-        <v>5</v>
-      </c>
-      <c r="J6">
-        <v>15.63</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -3610,25 +3610,25 @@
         <v>32</v>
       </c>
       <c r="D7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>96.88</v>
+      </c>
+      <c r="G7">
+        <v>3.13</v>
+      </c>
+      <c r="H7">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="I7">
         <v>0</v>
       </c>
-      <c r="F7">
-        <v>93.75</v>
-      </c>
-      <c r="G7">
+      <c r="J7">
         <v>0</v>
-      </c>
-      <c r="H7">
-        <v>8.6</v>
-      </c>
-      <c r="I7">
-        <v>2</v>
-      </c>
-      <c r="J7">
-        <v>6.25</v>
       </c>
     </row>
   </sheetData>
@@ -3638,7 +3638,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3667,27 +3667,27 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>19330051920246</v>
+        <v>19330051920251</v>
       </c>
       <c r="B2" t="s">
         <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="D2" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>19330051920247</v>
+        <v>19330051920252</v>
       </c>
       <c r="B3" t="s">
         <v>64</v>
@@ -3696,573 +3696,73 @@
         <v>69</v>
       </c>
       <c r="D3" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="E3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>19330051920248</v>
+        <v>19330051920259</v>
       </c>
       <c r="B4" t="s">
         <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="D4" t="s">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>19330051920249</v>
+        <v>19330051920403</v>
       </c>
       <c r="B5" t="s">
         <v>66</v>
       </c>
       <c r="C5" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="D5" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>19330051920251</v>
+        <v>19330051920412</v>
       </c>
       <c r="B6" t="s">
         <v>67</v>
       </c>
       <c r="C6" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="D6" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>19330051920251</v>
-      </c>
-      <c r="B7" t="s">
-        <v>67</v>
-      </c>
-      <c r="C7" t="s">
-        <v>82</v>
-      </c>
-      <c r="D7" t="s">
-        <v>97</v>
-      </c>
-      <c r="E7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F7" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>19330051920251</v>
-      </c>
-      <c r="B8" t="s">
-        <v>67</v>
-      </c>
-      <c r="C8" t="s">
-        <v>82</v>
-      </c>
-      <c r="D8" t="s">
-        <v>97</v>
-      </c>
-      <c r="E8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>19330051920252</v>
-      </c>
-      <c r="B9" t="s">
-        <v>68</v>
-      </c>
-      <c r="C9" t="s">
-        <v>83</v>
-      </c>
-      <c r="D9" t="s">
-        <v>98</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>19330051920252</v>
-      </c>
-      <c r="B10" t="s">
-        <v>68</v>
-      </c>
-      <c r="C10" t="s">
-        <v>83</v>
-      </c>
-      <c r="D10" t="s">
-        <v>98</v>
-      </c>
-      <c r="E10" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>19330051920252</v>
-      </c>
-      <c r="B11" t="s">
-        <v>68</v>
-      </c>
-      <c r="C11" t="s">
-        <v>83</v>
-      </c>
-      <c r="D11" t="s">
-        <v>98</v>
-      </c>
-      <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>19330051920433</v>
-      </c>
-      <c r="B12" t="s">
-        <v>69</v>
-      </c>
-      <c r="C12" t="s">
-        <v>84</v>
-      </c>
-      <c r="D12" t="s">
-        <v>99</v>
-      </c>
-      <c r="E12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>19330051920258</v>
-      </c>
-      <c r="B13" t="s">
-        <v>70</v>
-      </c>
-      <c r="C13" t="s">
-        <v>85</v>
-      </c>
-      <c r="D13" t="s">
-        <v>100</v>
-      </c>
-      <c r="E13" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>19330051920257</v>
-      </c>
-      <c r="B14" t="s">
-        <v>70</v>
-      </c>
-      <c r="C14" t="s">
-        <v>86</v>
-      </c>
-      <c r="D14" t="s">
-        <v>101</v>
-      </c>
-      <c r="E14" t="s">
-        <v>6</v>
-      </c>
-      <c r="F14" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>19330051920259</v>
-      </c>
-      <c r="B15" t="s">
-        <v>71</v>
-      </c>
-      <c r="C15" t="s">
-        <v>87</v>
-      </c>
-      <c r="D15" t="s">
-        <v>102</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>19330051920259</v>
-      </c>
-      <c r="B16" t="s">
-        <v>71</v>
-      </c>
-      <c r="C16" t="s">
-        <v>87</v>
-      </c>
-      <c r="D16" t="s">
-        <v>102</v>
-      </c>
-      <c r="E16" t="s">
-        <v>6</v>
-      </c>
-      <c r="F16" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>19330051920259</v>
-      </c>
-      <c r="B17" t="s">
-        <v>71</v>
-      </c>
-      <c r="C17" t="s">
-        <v>87</v>
-      </c>
-      <c r="D17" t="s">
-        <v>102</v>
-      </c>
-      <c r="E17" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>19330051920259</v>
-      </c>
-      <c r="B18" t="s">
-        <v>71</v>
-      </c>
-      <c r="C18" t="s">
-        <v>87</v>
-      </c>
-      <c r="D18" t="s">
-        <v>102</v>
-      </c>
-      <c r="E18" t="s">
-        <v>7</v>
-      </c>
-      <c r="F18" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>19330051920260</v>
-      </c>
-      <c r="B19" t="s">
-        <v>72</v>
-      </c>
-      <c r="C19" t="s">
-        <v>88</v>
-      </c>
-      <c r="D19" t="s">
-        <v>103</v>
-      </c>
-      <c r="E19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F19" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>19330051920263</v>
-      </c>
-      <c r="B20" t="s">
-        <v>73</v>
-      </c>
-      <c r="C20" t="s">
-        <v>89</v>
-      </c>
-      <c r="D20" t="s">
-        <v>104</v>
-      </c>
-      <c r="E20" t="s">
-        <v>6</v>
-      </c>
-      <c r="F20" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>19330051920266</v>
-      </c>
-      <c r="B21" t="s">
-        <v>74</v>
-      </c>
-      <c r="C21" t="s">
-        <v>90</v>
-      </c>
-      <c r="D21" t="s">
-        <v>105</v>
-      </c>
-      <c r="E21" t="s">
-        <v>6</v>
-      </c>
-      <c r="F21" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>19330051920403</v>
-      </c>
-      <c r="B22" t="s">
-        <v>75</v>
-      </c>
-      <c r="C22" t="s">
-        <v>64</v>
-      </c>
-      <c r="D22" t="s">
-        <v>106</v>
-      </c>
-      <c r="E22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>19330051920403</v>
-      </c>
-      <c r="B23" t="s">
-        <v>75</v>
-      </c>
-      <c r="C23" t="s">
-        <v>64</v>
-      </c>
-      <c r="D23" t="s">
-        <v>106</v>
-      </c>
-      <c r="E23" t="s">
-        <v>6</v>
-      </c>
-      <c r="F23" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>19330051920406</v>
-      </c>
-      <c r="B24" t="s">
-        <v>76</v>
-      </c>
-      <c r="C24" t="s">
-        <v>91</v>
-      </c>
-      <c r="D24" t="s">
-        <v>107</v>
-      </c>
-      <c r="E24" t="s">
-        <v>6</v>
-      </c>
-      <c r="F24" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>19330051920407</v>
-      </c>
-      <c r="B25" t="s">
-        <v>77</v>
-      </c>
-      <c r="C25" t="s">
-        <v>78</v>
-      </c>
-      <c r="D25" t="s">
-        <v>108</v>
-      </c>
-      <c r="E25" t="s">
-        <v>10</v>
-      </c>
-      <c r="F25" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>19330051920409</v>
-      </c>
-      <c r="B26" t="s">
-        <v>78</v>
-      </c>
-      <c r="C26" t="s">
-        <v>81</v>
-      </c>
-      <c r="D26" t="s">
-        <v>109</v>
-      </c>
-      <c r="E26" t="s">
-        <v>6</v>
-      </c>
-      <c r="F26" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>19330051920411</v>
-      </c>
-      <c r="B27" t="s">
-        <v>78</v>
-      </c>
-      <c r="C27" t="s">
-        <v>92</v>
-      </c>
-      <c r="D27" t="s">
-        <v>110</v>
-      </c>
-      <c r="E27" t="s">
-        <v>6</v>
-      </c>
-      <c r="F27" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>19330051920412</v>
-      </c>
-      <c r="B28" t="s">
-        <v>79</v>
-      </c>
-      <c r="C28" t="s">
-        <v>78</v>
-      </c>
-      <c r="D28" t="s">
-        <v>111</v>
-      </c>
-      <c r="E28" t="s">
-        <v>8</v>
-      </c>
-      <c r="F28" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>19330051920412</v>
-      </c>
-      <c r="B29" t="s">
-        <v>79</v>
-      </c>
-      <c r="C29" t="s">
-        <v>78</v>
-      </c>
-      <c r="D29" t="s">
-        <v>111</v>
-      </c>
-      <c r="E29" t="s">
-        <v>6</v>
-      </c>
-      <c r="F29" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>19330051920412</v>
-      </c>
-      <c r="B30" t="s">
-        <v>79</v>
-      </c>
-      <c r="C30" t="s">
-        <v>78</v>
-      </c>
-      <c r="D30" t="s">
-        <v>111</v>
-      </c>
-      <c r="E30" t="s">
-        <v>10</v>
-      </c>
-      <c r="F30" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>19330051920412</v>
-      </c>
-      <c r="B31" t="s">
-        <v>79</v>
-      </c>
-      <c r="C31" t="s">
-        <v>78</v>
-      </c>
-      <c r="D31" t="s">
-        <v>111</v>
-      </c>
-      <c r="E31" t="s">
-        <v>7</v>
-      </c>
-      <c r="F31" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -4298,87 +3798,87 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>19330051920259</v>
+        <v>19330051920251</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>87</v>
+        <v>68</v>
       </c>
       <c r="D2" t="s">
-        <v>102</v>
+        <v>73</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>19330051920412</v>
+        <v>19330051920252</v>
       </c>
       <c r="B3" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="C3" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D3" t="s">
-        <v>111</v>
+        <v>74</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>19330051920251</v>
+        <v>19330051920259</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="D4" t="s">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>19330051920252</v>
+        <v>19330051920403</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C5" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="D5" t="s">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>19330051920403</v>
+        <v>19330051920412</v>
       </c>
       <c r="B6" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="C6" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="D6" t="s">
-        <v>106</v>
+        <v>77</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -4386,16 +3886,16 @@
         <v>19330051920246</v>
       </c>
       <c r="B7" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="C7" t="s">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="D7" t="s">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -4403,16 +3903,16 @@
         <v>19330051920247</v>
       </c>
       <c r="B8" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="C8" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="D8" t="s">
-        <v>94</v>
+        <v>116</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -4420,16 +3920,16 @@
         <v>19330051920248</v>
       </c>
       <c r="B9" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="C9" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="D9" t="s">
-        <v>95</v>
+        <v>117</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -4437,197 +3937,197 @@
         <v>19330051920249</v>
       </c>
       <c r="B10" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="C10" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="D10" t="s">
-        <v>96</v>
+        <v>118</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>19330051920433</v>
+        <v>19330051920250</v>
       </c>
       <c r="B11" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="C11" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="D11" t="s">
-        <v>99</v>
+        <v>119</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>19330051920258</v>
+        <v>19330051920253</v>
       </c>
       <c r="B12" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="C12" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="D12" t="s">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>19330051920257</v>
+        <v>19330051920433</v>
       </c>
       <c r="B13" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="C13" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="D13" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>19330051920260</v>
+        <v>19330051920256</v>
       </c>
       <c r="B14" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="C14" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="D14" t="s">
-        <v>103</v>
+        <v>122</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>19330051920263</v>
+        <v>19330051920254</v>
       </c>
       <c r="B15" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="C15" t="s">
-        <v>89</v>
+        <v>63</v>
       </c>
       <c r="D15" t="s">
-        <v>104</v>
+        <v>123</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>19330051920266</v>
+        <v>19330051920258</v>
       </c>
       <c r="B16" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="C16" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="D16" t="s">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>19330051920406</v>
+        <v>19330051920257</v>
       </c>
       <c r="B17" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="C17" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="D17" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>19330051920407</v>
+        <v>19330051920255</v>
       </c>
       <c r="B18" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C18" t="s">
-        <v>78</v>
+        <v>104</v>
       </c>
       <c r="D18" t="s">
-        <v>108</v>
+        <v>126</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>19330051920409</v>
+        <v>19330051920260</v>
       </c>
       <c r="B19" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="C19" t="s">
-        <v>81</v>
+        <v>105</v>
       </c>
       <c r="D19" t="s">
-        <v>109</v>
+        <v>127</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>19330051920411</v>
+        <v>19330051920263</v>
       </c>
       <c r="B20" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="C20" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D20" t="s">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>19330051920250</v>
+        <v>19330051920261</v>
       </c>
       <c r="B21" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="C21" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="D21" t="s">
         <v>129</v>
@@ -4638,13 +4138,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>19330051920253</v>
+        <v>19330051920265</v>
       </c>
       <c r="B22" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="C22" t="s">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="D22" t="s">
         <v>130</v>
@@ -4655,13 +4155,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>19330051920256</v>
+        <v>19330051920267</v>
       </c>
       <c r="B23" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="C23" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="D23" t="s">
         <v>131</v>
@@ -4672,13 +4172,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>19330051920254</v>
+        <v>19330051920266</v>
       </c>
       <c r="B24" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="C24" t="s">
-        <v>67</v>
+        <v>107</v>
       </c>
       <c r="D24" t="s">
         <v>132</v>
@@ -4689,13 +4189,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>19330051920255</v>
+        <v>19330051920402</v>
       </c>
       <c r="B25" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="C25" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="D25" t="s">
         <v>133</v>
@@ -4706,13 +4206,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>19330051920261</v>
+        <v>19330051920400</v>
       </c>
       <c r="B26" t="s">
-        <v>114</v>
+        <v>91</v>
       </c>
       <c r="C26" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="D26" t="s">
         <v>134</v>
@@ -4723,13 +4223,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>19330051920265</v>
+        <v>19330051920348</v>
       </c>
       <c r="B27" t="s">
-        <v>115</v>
+        <v>92</v>
       </c>
       <c r="C27" t="s">
-        <v>69</v>
+        <v>110</v>
       </c>
       <c r="D27" t="s">
         <v>135</v>
@@ -4740,13 +4240,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>19330051920267</v>
+        <v>19330051920405</v>
       </c>
       <c r="B28" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="C28" t="s">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="D28" t="s">
         <v>136</v>
@@ -4757,13 +4257,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>19330051920402</v>
+        <v>19330051920406</v>
       </c>
       <c r="B29" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="C29" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="D29" t="s">
         <v>137</v>
@@ -4774,13 +4274,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>19330051920400</v>
+        <v>19330051920407</v>
       </c>
       <c r="B30" t="s">
-        <v>117</v>
+        <v>95</v>
       </c>
       <c r="C30" t="s">
-        <v>125</v>
+        <v>72</v>
       </c>
       <c r="D30" t="s">
         <v>138</v>
@@ -4791,13 +4291,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>19330051920348</v>
+        <v>19330051920409</v>
       </c>
       <c r="B31" t="s">
-        <v>118</v>
+        <v>72</v>
       </c>
       <c r="C31" t="s">
-        <v>126</v>
+        <v>98</v>
       </c>
       <c r="D31" t="s">
         <v>139</v>
@@ -4808,13 +4308,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>19330051920405</v>
+        <v>19330051920411</v>
       </c>
       <c r="B32" t="s">
-        <v>119</v>
+        <v>72</v>
       </c>
       <c r="C32" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="D32" t="s">
         <v>140</v>
@@ -4828,10 +4328,10 @@
         <v>19330051920414</v>
       </c>
       <c r="B33" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="C33" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D33" t="s">
         <v>141</v>
@@ -4847,7 +4347,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4879,22 +4379,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920258</v>
+        <v>19330051920400</v>
       </c>
       <c r="B2" t="s">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="C2" t="s">
-        <v>85</v>
+        <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>100</v>
+        <v>134</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4902,206 +4402,206 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920258</v>
+        <v>19330051920400</v>
       </c>
       <c r="B3" t="s">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="C3" t="s">
-        <v>85</v>
+        <v>109</v>
       </c>
       <c r="D3" t="s">
-        <v>100</v>
+        <v>134</v>
       </c>
       <c r="E3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
         <v>53</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920246</v>
+        <v>19330051920409</v>
       </c>
       <c r="B4" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="C4" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="D4" t="s">
-        <v>93</v>
+        <v>139</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
         <v>54</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920248</v>
+        <v>19330051920409</v>
       </c>
       <c r="B5" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="C5" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="D5" t="s">
-        <v>95</v>
+        <v>139</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920249</v>
+        <v>19330051920246</v>
       </c>
       <c r="B6" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="C6" t="s">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="D6" t="s">
-        <v>96</v>
+        <v>115</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920433</v>
+        <v>19330051920248</v>
       </c>
       <c r="B7" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="C7" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="D7" t="s">
-        <v>99</v>
+        <v>117</v>
       </c>
       <c r="E7" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
         <v>53</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920257</v>
+        <v>19330051920250</v>
       </c>
       <c r="B8" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="C8" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="D8" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
         <v>53</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330051920260</v>
+        <v>19330051920433</v>
       </c>
       <c r="B9" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="C9" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="D9" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F9" t="s">
         <v>54</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>19330051920263</v>
+        <v>19330051920254</v>
       </c>
       <c r="B10" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="C10" t="s">
-        <v>89</v>
+        <v>63</v>
       </c>
       <c r="D10" t="s">
-        <v>104</v>
+        <v>123</v>
       </c>
       <c r="E10" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
         <v>53</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>19330051920261</v>
+        <v>19330051920257</v>
       </c>
       <c r="B11" t="s">
-        <v>114</v>
+        <v>84</v>
       </c>
       <c r="C11" t="s">
-        <v>123</v>
+        <v>103</v>
       </c>
       <c r="D11" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="E11" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -5109,94 +4609,94 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>19330051920266</v>
+        <v>19330051920261</v>
       </c>
       <c r="B12" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="C12" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="D12" t="s">
-        <v>105</v>
+        <v>129</v>
       </c>
       <c r="E12" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F12" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>19330051920406</v>
+        <v>19330051920265</v>
       </c>
       <c r="B13" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="C13" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="D13" t="s">
-        <v>107</v>
+        <v>130</v>
       </c>
       <c r="E13" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F13" t="s">
         <v>53</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>19330051920407</v>
+        <v>19330051920402</v>
       </c>
       <c r="B14" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="C14" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="D14" t="s">
-        <v>108</v>
+        <v>133</v>
       </c>
       <c r="E14" t="s">
         <v>10</v>
       </c>
       <c r="F14" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G14">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>19330051920409</v>
+        <v>19330051920407</v>
       </c>
       <c r="B15" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="C15" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="D15" t="s">
-        <v>109</v>
+        <v>138</v>
       </c>
       <c r="E15" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F15" t="s">
         <v>53</v>
       </c>
       <c r="G15">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -5204,22 +4704,45 @@
         <v>19330051920411</v>
       </c>
       <c r="B16" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C16" t="s">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="D16" t="s">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="E16" t="s">
         <v>6</v>
       </c>
       <c r="F16" t="s">
+        <v>54</v>
+      </c>
+      <c r="G16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>19330051920414</v>
+      </c>
+      <c r="B17" t="s">
+        <v>96</v>
+      </c>
+      <c r="C17" t="s">
+        <v>114</v>
+      </c>
+      <c r="D17" t="s">
+        <v>141</v>
+      </c>
+      <c r="E17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F17" t="s">
         <v>53</v>
       </c>
-      <c r="G16">
-        <v>-1</v>
+      <c r="G17">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/6ASV - Estadisticos 20212.xlsx
+++ b/grupos/6ASV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="142">
   <si>
     <t>Materia</t>
   </si>
@@ -179,21 +179,21 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Medina Tolentino Elio</t>
+  </si>
+  <si>
     <t>Duran Amezcua María Angélica</t>
   </si>
   <si>
     <t>Ortega Valle Manuel</t>
   </si>
   <si>
-    <t>Medina Tolentino Elio</t>
+    <t>Hernández Mendoza Delfina</t>
   </si>
   <si>
     <t>Jiménez Nieto Enrique</t>
   </si>
   <si>
-    <t>Hernández Mendoza Delfina</t>
-  </si>
-  <si>
     <t>Pesce Bautista Victor Manuel</t>
   </si>
   <si>
@@ -209,175 +209,175 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>SANTILLANA</t>
+  </si>
+  <si>
+    <t>GERARDO</t>
+  </si>
+  <si>
+    <t>SIERRA</t>
+  </si>
+  <si>
+    <t>BONILLA</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>JULIO GABRIEL</t>
+  </si>
+  <si>
+    <t>DIEGO ABDEL JARIN</t>
+  </si>
+  <si>
+    <t>EDUARDO ULISES</t>
+  </si>
+  <si>
+    <t>CESAR GAEL</t>
+  </si>
+  <si>
+    <t>ALCANTARA</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>CISNEROS</t>
+  </si>
+  <si>
+    <t>CORDOVA</t>
+  </si>
+  <si>
     <t>CRUZ</t>
   </si>
   <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>SANTILLANA</t>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>LLAME</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MANI</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>MIXCOHUA</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>MONSALVO</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>ROMAN</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>TREJO</t>
+  </si>
+  <si>
+    <t>LEYVA</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
   </si>
   <si>
     <t>PALMA</t>
   </si>
   <si>
-    <t>GERARDO</t>
-  </si>
-  <si>
-    <t>SIERRA</t>
-  </si>
-  <si>
-    <t>BONILLA</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
+    <t>GUIZA</t>
+  </si>
+  <si>
+    <t>SERRANO</t>
+  </si>
+  <si>
+    <t>CUAHUA</t>
+  </si>
+  <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>GALEOTE</t>
+  </si>
+  <si>
+    <t>TZOMPAXTLE</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>ZAPATA</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>CASTELLANOS</t>
+  </si>
+  <si>
+    <t>QUINTERO</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>PINO</t>
+  </si>
+  <si>
+    <t>LUENGAS</t>
+  </si>
+  <si>
+    <t>MOISES EFRAIN</t>
+  </si>
+  <si>
+    <t>JOSE EMMANUEL</t>
+  </si>
+  <si>
+    <t>BRANDON AXEL</t>
+  </si>
+  <si>
+    <t>GABRIEL MARTIN</t>
+  </si>
+  <si>
+    <t>ANGELA ALESSANDRA</t>
   </si>
   <si>
     <t>VALERIA</t>
-  </si>
-  <si>
-    <t>JULIO GABRIEL</t>
-  </si>
-  <si>
-    <t>DIEGO ABDEL JARIN</t>
-  </si>
-  <si>
-    <t>EDUARDO ULISES</t>
-  </si>
-  <si>
-    <t>CESAR GAEL</t>
-  </si>
-  <si>
-    <t>ALCANTARA</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>CISNEROS</t>
-  </si>
-  <si>
-    <t>CORDOVA</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>LLAME</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MANI</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>MIXCOHUA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>MONSALVO</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>ROMAN</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>TREJO</t>
-  </si>
-  <si>
-    <t>LEYVA</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GUIZA</t>
-  </si>
-  <si>
-    <t>SERRANO</t>
-  </si>
-  <si>
-    <t>CUAHUA</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>GALEOTE</t>
-  </si>
-  <si>
-    <t>TZOMPAXTLE</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>ZAPATA</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>CASTELLANOS</t>
-  </si>
-  <si>
-    <t>QUINTERO</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>PINO</t>
-  </si>
-  <si>
-    <t>LUENGAS</t>
-  </si>
-  <si>
-    <t>MOISES EFRAIN</t>
-  </si>
-  <si>
-    <t>JOSE EMMANUEL</t>
-  </si>
-  <si>
-    <t>BRANDON AXEL</t>
-  </si>
-  <si>
-    <t>GABRIEL MARTIN</t>
-  </si>
-  <si>
-    <t>ANGELA ALESSANDRA</t>
   </si>
   <si>
     <t>LUIS ANGEL</t>
@@ -947,7 +947,7 @@
         <v>6</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I4">
         <v>6</v>
@@ -956,7 +956,7 @@
         <v>8</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L4">
         <v>7</v>
@@ -983,7 +983,7 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U4">
         <v>6</v>
@@ -992,7 +992,7 @@
         <v>8</v>
       </c>
       <c r="W4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X4">
         <v>7</v>
@@ -1024,7 +1024,7 @@
         <v>6</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I5">
         <v>5</v>
@@ -1101,7 +1101,7 @@
         <v>6</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I6">
         <v>6</v>
@@ -1110,7 +1110,7 @@
         <v>9</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L6">
         <v>7</v>
@@ -1137,7 +1137,7 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U6">
         <v>6</v>
@@ -1178,7 +1178,7 @@
         <v>6</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I7">
         <v>7</v>
@@ -1187,7 +1187,7 @@
         <v>9</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L7">
         <v>10</v>
@@ -1214,7 +1214,7 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U7">
         <v>7</v>
@@ -1255,7 +1255,7 @@
         <v>6</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I8">
         <v>7</v>
@@ -1264,7 +1264,7 @@
         <v>10</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L8">
         <v>6</v>
@@ -1291,7 +1291,7 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U8">
         <v>8</v>
@@ -1323,7 +1323,7 @@
         <v>6</v>
       </c>
       <c r="E9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -1332,7 +1332,7 @@
         <v>5</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I9">
         <v>6</v>
@@ -1341,7 +1341,7 @@
         <v>8</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L9">
         <v>7</v>
@@ -1377,7 +1377,7 @@
         <v>7</v>
       </c>
       <c r="W9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X9">
         <v>6</v>
@@ -1409,7 +1409,7 @@
         <v>6</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I10">
         <v>5</v>
@@ -1486,7 +1486,7 @@
         <v>9</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I11">
         <v>6</v>
@@ -1495,7 +1495,7 @@
         <v>9</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L11">
         <v>7</v>
@@ -1522,7 +1522,7 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U11">
         <v>6</v>
@@ -1563,7 +1563,7 @@
         <v>6</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I12">
         <v>6</v>
@@ -1572,7 +1572,7 @@
         <v>9</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L12">
         <v>7</v>
@@ -1599,7 +1599,7 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U12">
         <v>5</v>
@@ -1608,7 +1608,7 @@
         <v>9</v>
       </c>
       <c r="W12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X12">
         <v>8</v>
@@ -1640,7 +1640,7 @@
         <v>6</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I13">
         <v>6</v>
@@ -1649,7 +1649,7 @@
         <v>10</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L13">
         <v>6</v>
@@ -1676,7 +1676,7 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U13">
         <v>6</v>
@@ -1717,7 +1717,7 @@
         <v>6</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I14">
         <v>8</v>
@@ -1726,7 +1726,7 @@
         <v>9</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L14">
         <v>9</v>
@@ -1753,7 +1753,7 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U14">
         <v>8</v>
@@ -1794,7 +1794,7 @@
         <v>6</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I15">
         <v>5</v>
@@ -1803,7 +1803,7 @@
         <v>8</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L15">
         <v>6</v>
@@ -1871,7 +1871,7 @@
         <v>6</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I16">
         <v>5</v>
@@ -1880,7 +1880,7 @@
         <v>10</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L16">
         <v>6</v>
@@ -1907,7 +1907,7 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U16">
         <v>5</v>
@@ -1948,7 +1948,7 @@
         <v>6</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I17">
         <v>7</v>
@@ -1957,7 +1957,7 @@
         <v>10</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L17">
         <v>9</v>
@@ -1984,7 +1984,7 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U17">
         <v>8</v>
@@ -1993,7 +1993,7 @@
         <v>10</v>
       </c>
       <c r="W17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X17">
         <v>9</v>
@@ -2025,13 +2025,13 @@
         <v>5</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I18">
         <v>5</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K18">
         <v>-1</v>
@@ -2067,7 +2067,7 @@
         <v>5</v>
       </c>
       <c r="V18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W18">
         <v>-1</v>
@@ -2102,7 +2102,7 @@
         <v>6</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I19">
         <v>7</v>
@@ -2111,7 +2111,7 @@
         <v>9</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L19">
         <v>10</v>
@@ -2138,7 +2138,7 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U19">
         <v>7</v>
@@ -2179,7 +2179,7 @@
         <v>7</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I20">
         <v>6</v>
@@ -2256,7 +2256,7 @@
         <v>6</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I21">
         <v>6</v>
@@ -2265,7 +2265,7 @@
         <v>9</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L21">
         <v>8</v>
@@ -2292,7 +2292,7 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U21">
         <v>7</v>
@@ -2333,7 +2333,7 @@
         <v>6</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I22">
         <v>6</v>
@@ -2342,7 +2342,7 @@
         <v>9</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L22">
         <v>6</v>
@@ -2369,7 +2369,7 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U22">
         <v>6</v>
@@ -2378,7 +2378,7 @@
         <v>9</v>
       </c>
       <c r="W22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X22">
         <v>6</v>
@@ -2410,7 +2410,7 @@
         <v>6</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I23">
         <v>9</v>
@@ -2419,7 +2419,7 @@
         <v>9</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L23">
         <v>10</v>
@@ -2446,7 +2446,7 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U23">
         <v>9</v>
@@ -2487,7 +2487,7 @@
         <v>6</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I24">
         <v>9</v>
@@ -2496,7 +2496,7 @@
         <v>9</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L24">
         <v>7</v>
@@ -2523,7 +2523,7 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U24">
         <v>9</v>
@@ -2532,7 +2532,7 @@
         <v>9</v>
       </c>
       <c r="W24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X24">
         <v>7</v>
@@ -2564,7 +2564,7 @@
         <v>6</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I25">
         <v>5</v>
@@ -2573,7 +2573,7 @@
         <v>9</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L25">
         <v>5</v>
@@ -2600,7 +2600,7 @@
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U25">
         <v>5</v>
@@ -2609,7 +2609,7 @@
         <v>9</v>
       </c>
       <c r="W25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X25">
         <v>6</v>
@@ -2641,7 +2641,7 @@
         <v>6</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I26">
         <v>6</v>
@@ -2650,7 +2650,7 @@
         <v>9</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L26">
         <v>10</v>
@@ -2677,7 +2677,7 @@
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U26">
         <v>6</v>
@@ -2718,7 +2718,7 @@
         <v>6</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I27">
         <v>6</v>
@@ -2795,7 +2795,7 @@
         <v>7</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I28">
         <v>7</v>
@@ -2804,7 +2804,7 @@
         <v>10</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L28">
         <v>7</v>
@@ -2831,7 +2831,7 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U28">
         <v>8</v>
@@ -2872,7 +2872,7 @@
         <v>7</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I29">
         <v>6</v>
@@ -2881,7 +2881,7 @@
         <v>9</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L29">
         <v>9</v>
@@ -2908,7 +2908,7 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U29">
         <v>6</v>
@@ -2917,7 +2917,7 @@
         <v>9</v>
       </c>
       <c r="W29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X29">
         <v>10</v>
@@ -2949,7 +2949,7 @@
         <v>7</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I30">
         <v>6</v>
@@ -2958,7 +2958,7 @@
         <v>10</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L30">
         <v>10</v>
@@ -2985,7 +2985,7 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U30">
         <v>7</v>
@@ -3026,7 +3026,7 @@
         <v>6</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I31">
         <v>7</v>
@@ -3035,7 +3035,7 @@
         <v>9</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L31">
         <v>6</v>
@@ -3062,7 +3062,7 @@
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U31">
         <v>7</v>
@@ -3071,7 +3071,7 @@
         <v>9</v>
       </c>
       <c r="W31">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X31">
         <v>7</v>
@@ -3103,7 +3103,7 @@
         <v>6</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I32">
         <v>5</v>
@@ -3112,7 +3112,7 @@
         <v>9</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L32">
         <v>6</v>
@@ -3139,7 +3139,7 @@
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U32">
         <v>5</v>
@@ -3148,7 +3148,7 @@
         <v>9</v>
       </c>
       <c r="W32">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X32">
         <v>6</v>
@@ -3180,7 +3180,7 @@
         <v>6</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I33">
         <v>6</v>
@@ -3216,7 +3216,7 @@
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U33">
         <v>5</v>
@@ -3257,7 +3257,7 @@
         <v>6</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I34">
         <v>5</v>
@@ -3334,7 +3334,7 @@
         <v>6</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I35">
         <v>6</v>
@@ -3343,7 +3343,7 @@
         <v>9</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L35">
         <v>6</v>
@@ -3370,7 +3370,7 @@
         <v>-1</v>
       </c>
       <c r="T35">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U35">
         <v>7</v>
@@ -3379,7 +3379,7 @@
         <v>9</v>
       </c>
       <c r="W35">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X35">
         <v>8</v>
@@ -3441,7 +3441,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>53</v>
@@ -3450,19 +3450,19 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F2">
-        <v>53.13</v>
+        <v>50</v>
       </c>
       <c r="G2">
-        <v>46.88</v>
+        <v>50</v>
       </c>
       <c r="H2">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3473,7 +3473,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>54</v>
@@ -3482,19 +3482,19 @@
         <v>32</v>
       </c>
       <c r="D3">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E3">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F3">
-        <v>62.5</v>
+        <v>53.13</v>
       </c>
       <c r="G3">
-        <v>37.5</v>
+        <v>46.88</v>
       </c>
       <c r="H3">
-        <v>6.3</v>
+        <v>6</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3505,7 +3505,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>55</v>
@@ -3514,19 +3514,19 @@
         <v>32</v>
       </c>
       <c r="D4">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E4">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F4">
-        <v>75</v>
+        <v>62.5</v>
       </c>
       <c r="G4">
-        <v>25</v>
+        <v>37.5</v>
       </c>
       <c r="H4">
-        <v>6.6</v>
+        <v>6.3</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3537,7 +3537,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>56</v>
@@ -3546,30 +3546,30 @@
         <v>32</v>
       </c>
       <c r="D5">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5">
+        <v>87.5</v>
+      </c>
+      <c r="G5">
+        <v>12.5</v>
+      </c>
+      <c r="H5">
+        <v>7.5</v>
+      </c>
+      <c r="I5">
         <v>0</v>
       </c>
-      <c r="F5">
-        <v>84.38</v>
-      </c>
-      <c r="G5">
+      <c r="J5">
         <v>0</v>
-      </c>
-      <c r="H5">
-        <v>8.4</v>
-      </c>
-      <c r="I5">
-        <v>5</v>
-      </c>
-      <c r="J5">
-        <v>15.63</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>57</v>
@@ -3581,22 +3581,22 @@
         <v>28</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F6">
         <v>87.5</v>
       </c>
       <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="I6">
+        <v>4</v>
+      </c>
+      <c r="J6">
         <v>12.5</v>
-      </c>
-      <c r="H6">
-        <v>7.5</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -3610,16 +3610,16 @@
         <v>32</v>
       </c>
       <c r="D7">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>96.88</v>
+        <v>100</v>
       </c>
       <c r="G7">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="H7">
         <v>8.800000000000001</v>
@@ -3638,7 +3638,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3667,102 +3667,82 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>19330051920251</v>
+        <v>19330051920252</v>
       </c>
       <c r="B2" t="s">
         <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>19330051920252</v>
+        <v>19330051920259</v>
       </c>
       <c r="B3" t="s">
         <v>64</v>
       </c>
       <c r="C3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>19330051920259</v>
+        <v>19330051920403</v>
       </c>
       <c r="B4" t="s">
         <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>19330051920403</v>
+        <v>19330051920412</v>
       </c>
       <c r="B5" t="s">
         <v>66</v>
       </c>
       <c r="C5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>19330051920412</v>
-      </c>
-      <c r="B6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C6" t="s">
-        <v>72</v>
-      </c>
-      <c r="D6" t="s">
-        <v>77</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -3798,16 +3778,16 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>19330051920251</v>
+        <v>19330051920252</v>
       </c>
       <c r="B2" t="s">
         <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -3815,16 +3795,16 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>19330051920252</v>
+        <v>19330051920259</v>
       </c>
       <c r="B3" t="s">
         <v>64</v>
       </c>
       <c r="C3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -3832,16 +3812,16 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>19330051920259</v>
+        <v>19330051920403</v>
       </c>
       <c r="B4" t="s">
         <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -3849,16 +3829,16 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>19330051920403</v>
+        <v>19330051920412</v>
       </c>
       <c r="B5" t="s">
         <v>66</v>
       </c>
       <c r="C5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -3866,30 +3846,30 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>19330051920412</v>
+        <v>19330051920246</v>
       </c>
       <c r="B6" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="D6" t="s">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>19330051920246</v>
+        <v>19330051920247</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="C7" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="D7" t="s">
         <v>115</v>
@@ -3900,13 +3880,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>19330051920247</v>
+        <v>19330051920248</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C8" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="D8" t="s">
         <v>116</v>
@@ -3917,13 +3897,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>19330051920248</v>
+        <v>19330051920249</v>
       </c>
       <c r="B9" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D9" t="s">
         <v>117</v>
@@ -3934,13 +3914,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>19330051920249</v>
+        <v>19330051920250</v>
       </c>
       <c r="B10" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C10" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="D10" t="s">
         <v>118</v>
@@ -3951,13 +3931,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>19330051920250</v>
+        <v>19330051920251</v>
       </c>
       <c r="B11" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C11" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D11" t="s">
         <v>119</v>
@@ -3971,10 +3951,10 @@
         <v>19330051920253</v>
       </c>
       <c r="B12" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C12" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D12" t="s">
         <v>120</v>
@@ -3988,10 +3968,10 @@
         <v>19330051920433</v>
       </c>
       <c r="B13" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C13" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D13" t="s">
         <v>121</v>
@@ -4005,10 +3985,10 @@
         <v>19330051920256</v>
       </c>
       <c r="B14" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C14" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D14" t="s">
         <v>122</v>
@@ -4022,10 +4002,10 @@
         <v>19330051920254</v>
       </c>
       <c r="B15" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C15" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="D15" t="s">
         <v>123</v>
@@ -4039,10 +4019,10 @@
         <v>19330051920258</v>
       </c>
       <c r="B16" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C16" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D16" t="s">
         <v>124</v>
@@ -4056,10 +4036,10 @@
         <v>19330051920257</v>
       </c>
       <c r="B17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C17" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D17" t="s">
         <v>125</v>
@@ -4073,10 +4053,10 @@
         <v>19330051920255</v>
       </c>
       <c r="B18" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C18" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D18" t="s">
         <v>126</v>
@@ -4090,10 +4070,10 @@
         <v>19330051920260</v>
       </c>
       <c r="B19" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C19" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D19" t="s">
         <v>127</v>
@@ -4107,10 +4087,10 @@
         <v>19330051920263</v>
       </c>
       <c r="B20" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C20" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D20" t="s">
         <v>128</v>
@@ -4124,10 +4104,10 @@
         <v>19330051920261</v>
       </c>
       <c r="B21" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C21" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D21" t="s">
         <v>129</v>
@@ -4141,10 +4121,10 @@
         <v>19330051920265</v>
       </c>
       <c r="B22" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C22" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D22" t="s">
         <v>130</v>
@@ -4158,10 +4138,10 @@
         <v>19330051920267</v>
       </c>
       <c r="B23" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C23" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D23" t="s">
         <v>131</v>
@@ -4175,10 +4155,10 @@
         <v>19330051920266</v>
       </c>
       <c r="B24" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C24" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D24" t="s">
         <v>132</v>
@@ -4192,10 +4172,10 @@
         <v>19330051920402</v>
       </c>
       <c r="B25" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D25" t="s">
         <v>133</v>
@@ -4209,10 +4189,10 @@
         <v>19330051920400</v>
       </c>
       <c r="B26" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C26" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D26" t="s">
         <v>134</v>
@@ -4226,10 +4206,10 @@
         <v>19330051920348</v>
       </c>
       <c r="B27" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C27" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D27" t="s">
         <v>135</v>
@@ -4243,10 +4223,10 @@
         <v>19330051920405</v>
       </c>
       <c r="B28" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C28" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D28" t="s">
         <v>136</v>
@@ -4260,10 +4240,10 @@
         <v>19330051920406</v>
       </c>
       <c r="B29" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C29" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D29" t="s">
         <v>137</v>
@@ -4277,10 +4257,10 @@
         <v>19330051920407</v>
       </c>
       <c r="B30" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C30" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D30" t="s">
         <v>138</v>
@@ -4294,10 +4274,10 @@
         <v>19330051920409</v>
       </c>
       <c r="B31" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C31" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D31" t="s">
         <v>139</v>
@@ -4311,10 +4291,10 @@
         <v>19330051920411</v>
       </c>
       <c r="B32" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C32" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D32" t="s">
         <v>140</v>
@@ -4328,10 +4308,10 @@
         <v>19330051920414</v>
       </c>
       <c r="B33" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C33" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D33" t="s">
         <v>141</v>
@@ -4347,7 +4327,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4379,22 +4359,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920400</v>
+        <v>19330051920251</v>
       </c>
       <c r="B2" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="C2" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="D2" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4402,22 +4382,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920400</v>
+        <v>19330051920251</v>
       </c>
       <c r="B3" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="C3" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="D3" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4425,22 +4405,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920409</v>
+        <v>19330051920433</v>
       </c>
       <c r="B4" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="C4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D4" t="s">
-        <v>139</v>
+        <v>121</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4448,22 +4428,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920409</v>
+        <v>19330051920433</v>
       </c>
       <c r="B5" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="C5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D5" t="s">
-        <v>139</v>
+        <v>121</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -4471,19 +4451,19 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920246</v>
+        <v>19330051920257</v>
       </c>
       <c r="B6" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C6" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D6" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
         <v>53</v>
@@ -4494,22 +4474,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920248</v>
+        <v>19330051920257</v>
       </c>
       <c r="B7" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C7" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D7" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -4517,19 +4497,19 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920250</v>
+        <v>19330051920402</v>
       </c>
       <c r="B8" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="C8" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="D8" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
         <v>53</v>
@@ -4540,19 +4520,19 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330051920433</v>
+        <v>19330051920402</v>
       </c>
       <c r="B9" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C9" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="D9" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="E9" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
         <v>54</v>
@@ -4563,22 +4543,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>19330051920254</v>
+        <v>19330051920400</v>
       </c>
       <c r="B10" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C10" t="s">
-        <v>63</v>
+        <v>108</v>
       </c>
       <c r="D10" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -4586,19 +4566,19 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>19330051920257</v>
+        <v>19330051920400</v>
       </c>
       <c r="B11" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C11" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="D11" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="E11" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F11" t="s">
         <v>54</v>
@@ -4609,22 +4589,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>19330051920261</v>
+        <v>19330051920411</v>
       </c>
       <c r="B12" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="C12" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="D12" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="E12" t="s">
         <v>5</v>
       </c>
       <c r="F12" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -4632,22 +4612,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>19330051920265</v>
+        <v>19330051920411</v>
       </c>
       <c r="B13" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="C13" t="s">
-        <v>83</v>
+        <v>112</v>
       </c>
       <c r="D13" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="E13" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F13" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -4655,22 +4635,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>19330051920402</v>
+        <v>19330051920246</v>
       </c>
       <c r="B14" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="C14" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="D14" t="s">
-        <v>133</v>
+        <v>114</v>
       </c>
       <c r="E14" t="s">
         <v>10</v>
       </c>
       <c r="F14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -4678,22 +4658,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>19330051920407</v>
+        <v>19330051920248</v>
       </c>
       <c r="B15" t="s">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="C15" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="D15" t="s">
-        <v>138</v>
+        <v>116</v>
       </c>
       <c r="E15" t="s">
         <v>10</v>
       </c>
       <c r="F15" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -4701,19 +4681,19 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>19330051920411</v>
+        <v>19330051920250</v>
       </c>
       <c r="B16" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C16" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="D16" t="s">
-        <v>140</v>
+        <v>118</v>
       </c>
       <c r="E16" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F16" t="s">
         <v>54</v>
@@ -4724,24 +4704,185 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>19330051920414</v>
+        <v>19330051920256</v>
       </c>
       <c r="B17" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="C17" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="D17" t="s">
-        <v>141</v>
+        <v>122</v>
       </c>
       <c r="E17" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F17" t="s">
         <v>53</v>
       </c>
       <c r="G17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>19330051920254</v>
+      </c>
+      <c r="B18" t="s">
+        <v>82</v>
+      </c>
+      <c r="C18" t="s">
+        <v>79</v>
+      </c>
+      <c r="D18" t="s">
+        <v>123</v>
+      </c>
+      <c r="E18" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18" t="s">
+        <v>54</v>
+      </c>
+      <c r="G18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>19330051920255</v>
+      </c>
+      <c r="B19" t="s">
+        <v>82</v>
+      </c>
+      <c r="C19" t="s">
+        <v>103</v>
+      </c>
+      <c r="D19" t="s">
+        <v>126</v>
+      </c>
+      <c r="E19" t="s">
+        <v>5</v>
+      </c>
+      <c r="F19" t="s">
+        <v>53</v>
+      </c>
+      <c r="G19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>19330051920261</v>
+      </c>
+      <c r="B20" t="s">
+        <v>85</v>
+      </c>
+      <c r="C20" t="s">
+        <v>105</v>
+      </c>
+      <c r="D20" t="s">
+        <v>129</v>
+      </c>
+      <c r="E20" t="s">
+        <v>5</v>
+      </c>
+      <c r="F20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G20">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>19330051920265</v>
+      </c>
+      <c r="B21" t="s">
+        <v>86</v>
+      </c>
+      <c r="C21" t="s">
+        <v>81</v>
+      </c>
+      <c r="D21" t="s">
+        <v>130</v>
+      </c>
+      <c r="E21" t="s">
+        <v>10</v>
+      </c>
+      <c r="F21" t="s">
+        <v>54</v>
+      </c>
+      <c r="G21">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>19330051920405</v>
+      </c>
+      <c r="B22" t="s">
+        <v>91</v>
+      </c>
+      <c r="C22" t="s">
+        <v>110</v>
+      </c>
+      <c r="D22" t="s">
+        <v>136</v>
+      </c>
+      <c r="E22" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" t="s">
+        <v>53</v>
+      </c>
+      <c r="G22">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>19330051920407</v>
+      </c>
+      <c r="B23" t="s">
+        <v>93</v>
+      </c>
+      <c r="C23" t="s">
+        <v>70</v>
+      </c>
+      <c r="D23" t="s">
+        <v>138</v>
+      </c>
+      <c r="E23" t="s">
+        <v>10</v>
+      </c>
+      <c r="F23" t="s">
+        <v>54</v>
+      </c>
+      <c r="G23">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>19330051920414</v>
+      </c>
+      <c r="B24" t="s">
+        <v>94</v>
+      </c>
+      <c r="C24" t="s">
+        <v>113</v>
+      </c>
+      <c r="D24" t="s">
+        <v>141</v>
+      </c>
+      <c r="E24" t="s">
+        <v>10</v>
+      </c>
+      <c r="F24" t="s">
+        <v>54</v>
+      </c>
+      <c r="G24">
         <v>5</v>
       </c>
     </row>

--- a/grupos/6ASV - Estadisticos 20212.xlsx
+++ b/grupos/6ASV - Estadisticos 20212.xlsx
@@ -1732,7 +1732,7 @@
         <v>9</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1768,7 +1768,7 @@
         <v>9</v>
       </c>
       <c r="Y14">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:25">

--- a/grupos/6ASV - Estadisticos 20212.xlsx
+++ b/grupos/6ASV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="142">
   <si>
     <t>Materia</t>
   </si>
@@ -179,19 +179,19 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Duran Amezcua María Angélica</t>
+  </si>
+  <si>
+    <t>Hernández Mendoza Delfina</t>
+  </si>
+  <si>
+    <t>Ortega Valle Manuel</t>
+  </si>
+  <si>
+    <t>Jiménez Nieto Enrique</t>
+  </si>
+  <si>
     <t>Medina Tolentino Elio</t>
-  </si>
-  <si>
-    <t>Duran Amezcua María Angélica</t>
-  </si>
-  <si>
-    <t>Ortega Valle Manuel</t>
-  </si>
-  <si>
-    <t>Hernández Mendoza Delfina</t>
-  </si>
-  <si>
-    <t>Jiménez Nieto Enrique</t>
   </si>
   <si>
     <t>Pesce Bautista Victor Manuel</t>
@@ -947,7 +947,7 @@
         <v>6</v>
       </c>
       <c r="H4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I4">
         <v>6</v>
@@ -968,22 +968,22 @@
         <v>-1</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q4">
         <v>-1</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S4">
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="U4">
         <v>6</v>
@@ -995,7 +995,7 @@
         <v>8</v>
       </c>
       <c r="X4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y4">
         <v>5</v>
@@ -1024,7 +1024,7 @@
         <v>6</v>
       </c>
       <c r="H5">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I5">
         <v>5</v>
@@ -1045,28 +1045,28 @@
         <v>-1</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q5">
         <v>-1</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S5">
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U5">
         <v>5</v>
       </c>
       <c r="V5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W5">
         <v>6</v>
@@ -1101,7 +1101,7 @@
         <v>6</v>
       </c>
       <c r="H6">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I6">
         <v>6</v>
@@ -1122,22 +1122,22 @@
         <v>-1</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q6">
         <v>-1</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S6">
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="U6">
         <v>6</v>
@@ -1149,7 +1149,7 @@
         <v>10</v>
       </c>
       <c r="X6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y6">
         <v>5</v>
@@ -1178,7 +1178,7 @@
         <v>6</v>
       </c>
       <c r="H7">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I7">
         <v>7</v>
@@ -1199,22 +1199,22 @@
         <v>-1</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q7">
         <v>-1</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S7">
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U7">
         <v>7</v>
@@ -1255,7 +1255,7 @@
         <v>6</v>
       </c>
       <c r="H8">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I8">
         <v>7</v>
@@ -1276,25 +1276,25 @@
         <v>-1</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q8">
         <v>-1</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S8">
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V8">
         <v>10</v>
@@ -1303,7 +1303,7 @@
         <v>10</v>
       </c>
       <c r="X8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y8">
         <v>5</v>
@@ -1332,7 +1332,7 @@
         <v>5</v>
       </c>
       <c r="H9">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I9">
         <v>6</v>
@@ -1353,25 +1353,25 @@
         <v>-1</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q9">
         <v>-1</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S9">
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V9">
         <v>7</v>
@@ -1380,7 +1380,7 @@
         <v>9</v>
       </c>
       <c r="X9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y9">
         <v>6</v>
@@ -1409,7 +1409,7 @@
         <v>6</v>
       </c>
       <c r="H10">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I10">
         <v>5</v>
@@ -1430,22 +1430,22 @@
         <v>-1</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q10">
         <v>-1</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S10">
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U10">
         <v>5</v>
@@ -1486,7 +1486,7 @@
         <v>9</v>
       </c>
       <c r="H11">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I11">
         <v>6</v>
@@ -1507,28 +1507,28 @@
         <v>-1</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q11">
         <v>-1</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S11">
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="U11">
         <v>6</v>
       </c>
       <c r="V11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W11">
         <v>8</v>
@@ -1563,7 +1563,7 @@
         <v>6</v>
       </c>
       <c r="H12">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I12">
         <v>6</v>
@@ -1584,28 +1584,28 @@
         <v>-1</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q12">
         <v>-1</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S12">
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W12">
         <v>8</v>
@@ -1640,7 +1640,7 @@
         <v>6</v>
       </c>
       <c r="H13">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I13">
         <v>6</v>
@@ -1661,22 +1661,22 @@
         <v>-1</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q13">
         <v>-1</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S13">
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="U13">
         <v>6</v>
@@ -1717,7 +1717,7 @@
         <v>6</v>
       </c>
       <c r="H14">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I14">
         <v>8</v>
@@ -1738,22 +1738,22 @@
         <v>-1</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q14">
         <v>-1</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S14">
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U14">
         <v>8</v>
@@ -1794,7 +1794,7 @@
         <v>6</v>
       </c>
       <c r="H15">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I15">
         <v>5</v>
@@ -1815,25 +1815,25 @@
         <v>-1</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q15">
         <v>-1</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S15">
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V15">
         <v>8</v>
@@ -1871,7 +1871,7 @@
         <v>6</v>
       </c>
       <c r="H16">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I16">
         <v>5</v>
@@ -1892,34 +1892,34 @@
         <v>-1</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q16">
         <v>-1</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S16">
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W16">
         <v>8</v>
       </c>
       <c r="X16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y16">
         <v>7</v>
@@ -1948,7 +1948,7 @@
         <v>6</v>
       </c>
       <c r="H17">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I17">
         <v>7</v>
@@ -1969,28 +1969,28 @@
         <v>-1</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q17">
         <v>-1</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S17">
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W17">
         <v>10</v>
@@ -2025,7 +2025,7 @@
         <v>5</v>
       </c>
       <c r="H18">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I18">
         <v>5</v>
@@ -2046,22 +2046,22 @@
         <v>-1</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q18">
         <v>-1</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S18">
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U18">
         <v>5</v>
@@ -2102,7 +2102,7 @@
         <v>6</v>
       </c>
       <c r="H19">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I19">
         <v>7</v>
@@ -2123,22 +2123,22 @@
         <v>-1</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q19">
         <v>-1</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S19">
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="U19">
         <v>7</v>
@@ -2179,7 +2179,7 @@
         <v>7</v>
       </c>
       <c r="H20">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I20">
         <v>6</v>
@@ -2200,28 +2200,28 @@
         <v>-1</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q20">
         <v>-1</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S20">
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W20">
         <v>7</v>
@@ -2256,7 +2256,7 @@
         <v>6</v>
       </c>
       <c r="H21">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I21">
         <v>6</v>
@@ -2277,22 +2277,22 @@
         <v>-1</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q21">
         <v>-1</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S21">
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="U21">
         <v>7</v>
@@ -2333,7 +2333,7 @@
         <v>6</v>
       </c>
       <c r="H22">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I22">
         <v>6</v>
@@ -2354,25 +2354,25 @@
         <v>-1</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q22">
         <v>-1</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S22">
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V22">
         <v>9</v>
@@ -2410,7 +2410,7 @@
         <v>6</v>
       </c>
       <c r="H23">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I23">
         <v>9</v>
@@ -2431,22 +2431,22 @@
         <v>-1</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q23">
         <v>-1</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S23">
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U23">
         <v>9</v>
@@ -2487,7 +2487,7 @@
         <v>6</v>
       </c>
       <c r="H24">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I24">
         <v>9</v>
@@ -2508,22 +2508,22 @@
         <v>-1</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q24">
         <v>-1</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S24">
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U24">
         <v>9</v>
@@ -2535,7 +2535,7 @@
         <v>9</v>
       </c>
       <c r="X24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y24">
         <v>8</v>
@@ -2564,7 +2564,7 @@
         <v>6</v>
       </c>
       <c r="H25">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I25">
         <v>5</v>
@@ -2585,25 +2585,25 @@
         <v>-1</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q25">
         <v>-1</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S25">
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V25">
         <v>9</v>
@@ -2612,7 +2612,7 @@
         <v>10</v>
       </c>
       <c r="X25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y25">
         <v>5</v>
@@ -2641,7 +2641,7 @@
         <v>6</v>
       </c>
       <c r="H26">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I26">
         <v>6</v>
@@ -2662,22 +2662,22 @@
         <v>-1</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q26">
         <v>-1</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S26">
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U26">
         <v>6</v>
@@ -2718,7 +2718,7 @@
         <v>6</v>
       </c>
       <c r="H27">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I27">
         <v>6</v>
@@ -2739,25 +2739,25 @@
         <v>-1</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q27">
         <v>-1</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S27">
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V27">
         <v>6</v>
@@ -2766,7 +2766,7 @@
         <v>-1</v>
       </c>
       <c r="X27">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y27">
         <v>5</v>
@@ -2795,7 +2795,7 @@
         <v>7</v>
       </c>
       <c r="H28">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I28">
         <v>7</v>
@@ -2816,25 +2816,25 @@
         <v>-1</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q28">
         <v>-1</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S28">
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V28">
         <v>10</v>
@@ -2843,7 +2843,7 @@
         <v>10</v>
       </c>
       <c r="X28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y28">
         <v>7</v>
@@ -2872,7 +2872,7 @@
         <v>7</v>
       </c>
       <c r="H29">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I29">
         <v>6</v>
@@ -2893,22 +2893,22 @@
         <v>-1</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q29">
         <v>-1</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S29">
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U29">
         <v>6</v>
@@ -2920,7 +2920,7 @@
         <v>10</v>
       </c>
       <c r="X29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y29">
         <v>7</v>
@@ -2949,7 +2949,7 @@
         <v>7</v>
       </c>
       <c r="H30">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I30">
         <v>6</v>
@@ -2970,22 +2970,22 @@
         <v>-1</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q30">
         <v>-1</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S30">
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="U30">
         <v>7</v>
@@ -3026,7 +3026,7 @@
         <v>6</v>
       </c>
       <c r="H31">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I31">
         <v>7</v>
@@ -3047,25 +3047,25 @@
         <v>-1</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q31">
         <v>-1</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S31">
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U31">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V31">
         <v>9</v>
@@ -3103,7 +3103,7 @@
         <v>6</v>
       </c>
       <c r="H32">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I32">
         <v>5</v>
@@ -3124,25 +3124,25 @@
         <v>-1</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q32">
         <v>-1</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S32">
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V32">
         <v>9</v>
@@ -3180,7 +3180,7 @@
         <v>6</v>
       </c>
       <c r="H33">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I33">
         <v>6</v>
@@ -3201,25 +3201,25 @@
         <v>-1</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q33">
         <v>-1</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S33">
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V33">
         <v>9</v>
@@ -3257,7 +3257,7 @@
         <v>6</v>
       </c>
       <c r="H34">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I34">
         <v>5</v>
@@ -3278,28 +3278,28 @@
         <v>-1</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q34">
         <v>-1</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S34">
         <v>-1</v>
       </c>
       <c r="T34">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U34">
         <v>5</v>
       </c>
       <c r="V34">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W34">
         <v>-1</v>
@@ -3334,7 +3334,7 @@
         <v>6</v>
       </c>
       <c r="H35">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I35">
         <v>6</v>
@@ -3355,22 +3355,22 @@
         <v>-1</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q35">
         <v>-1</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S35">
         <v>-1</v>
       </c>
       <c r="T35">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U35">
         <v>7</v>
@@ -3441,7 +3441,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>53</v>
@@ -3450,19 +3450,19 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F2">
-        <v>50</v>
+        <v>53.13</v>
       </c>
       <c r="G2">
-        <v>50</v>
+        <v>46.88</v>
       </c>
       <c r="H2">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3473,7 +3473,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
         <v>54</v>
@@ -3482,19 +3482,19 @@
         <v>32</v>
       </c>
       <c r="D3">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E3">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>53.13</v>
+        <v>81.25</v>
       </c>
       <c r="G3">
-        <v>46.88</v>
+        <v>18.75</v>
       </c>
       <c r="H3">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3514,16 +3514,16 @@
         <v>32</v>
       </c>
       <c r="D4">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="E4">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>62.5</v>
+        <v>84.38</v>
       </c>
       <c r="G4">
-        <v>37.5</v>
+        <v>15.63</v>
       </c>
       <c r="H4">
         <v>6.3</v>
@@ -3537,7 +3537,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>56</v>
@@ -3549,27 +3549,27 @@
         <v>28</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F5">
         <v>87.5</v>
       </c>
       <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="I5">
+        <v>4</v>
+      </c>
+      <c r="J5">
         <v>12.5</v>
-      </c>
-      <c r="H5">
-        <v>7.5</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>57</v>
@@ -3578,25 +3578,25 @@
         <v>32</v>
       </c>
       <c r="D6">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>87.5</v>
+        <v>100</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="I6">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>12.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -3622,7 +3622,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -3682,7 +3682,7 @@
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3702,7 +3702,7 @@
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3722,7 +3722,7 @@
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -3742,7 +3742,7 @@
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -4327,7 +4327,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4359,22 +4359,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920251</v>
+        <v>19330051920247</v>
       </c>
       <c r="B2" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="C2" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="D2" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4382,22 +4382,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920251</v>
+        <v>19330051920247</v>
       </c>
       <c r="B3" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="C3" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="D3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E3" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4405,22 +4405,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920433</v>
+        <v>19330051920265</v>
       </c>
       <c r="B4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C4" t="s">
         <v>81</v>
       </c>
-      <c r="C4" t="s">
-        <v>99</v>
-      </c>
       <c r="D4" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4428,22 +4428,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920433</v>
+        <v>19330051920265</v>
       </c>
       <c r="B5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C5" t="s">
         <v>81</v>
       </c>
-      <c r="C5" t="s">
-        <v>99</v>
-      </c>
       <c r="D5" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="E5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -4451,19 +4451,19 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920257</v>
+        <v>19330051920246</v>
       </c>
       <c r="B6" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="D6" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
         <v>53</v>
@@ -4474,22 +4474,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920257</v>
+        <v>19330051920248</v>
       </c>
       <c r="B7" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="C7" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="D7" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="E7" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -4497,19 +4497,19 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920402</v>
+        <v>19330051920250</v>
       </c>
       <c r="B8" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="C8" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="D8" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
         <v>53</v>
@@ -4520,19 +4520,19 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330051920402</v>
+        <v>19330051920251</v>
       </c>
       <c r="B9" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="C9" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="D9" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
         <v>54</v>
@@ -4543,22 +4543,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>19330051920400</v>
+        <v>19330051920254</v>
       </c>
       <c r="B10" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C10" t="s">
-        <v>108</v>
+        <v>79</v>
       </c>
       <c r="D10" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="E10" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -4566,22 +4566,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>19330051920400</v>
+        <v>19330051920258</v>
       </c>
       <c r="B11" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C11" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="D11" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -4589,19 +4589,19 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>19330051920411</v>
+        <v>19330051920402</v>
       </c>
       <c r="B12" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="C12" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="D12" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="E12" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F12" t="s">
         <v>53</v>
@@ -4612,22 +4612,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>19330051920411</v>
+        <v>19330051920400</v>
       </c>
       <c r="B13" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="C13" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D13" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="E13" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F13" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -4635,22 +4635,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>19330051920246</v>
+        <v>19330051920407</v>
       </c>
       <c r="B14" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="C14" t="s">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="D14" t="s">
-        <v>114</v>
+        <v>138</v>
       </c>
       <c r="E14" t="s">
         <v>10</v>
       </c>
       <c r="F14" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -4658,22 +4658,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>19330051920248</v>
+        <v>19330051920409</v>
       </c>
       <c r="B15" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="C15" t="s">
         <v>96</v>
       </c>
       <c r="D15" t="s">
-        <v>116</v>
+        <v>139</v>
       </c>
       <c r="E15" t="s">
         <v>10</v>
       </c>
       <c r="F15" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -4681,208 +4681,24 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>19330051920250</v>
+        <v>19330051920414</v>
       </c>
       <c r="B16" t="s">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="C16" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="D16" t="s">
-        <v>118</v>
+        <v>141</v>
       </c>
       <c r="E16" t="s">
         <v>10</v>
       </c>
       <c r="F16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>19330051920256</v>
-      </c>
-      <c r="B17" t="s">
-        <v>82</v>
-      </c>
-      <c r="C17" t="s">
-        <v>100</v>
-      </c>
-      <c r="D17" t="s">
-        <v>122</v>
-      </c>
-      <c r="E17" t="s">
-        <v>5</v>
-      </c>
-      <c r="F17" t="s">
-        <v>53</v>
-      </c>
-      <c r="G17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>19330051920254</v>
-      </c>
-      <c r="B18" t="s">
-        <v>82</v>
-      </c>
-      <c r="C18" t="s">
-        <v>79</v>
-      </c>
-      <c r="D18" t="s">
-        <v>123</v>
-      </c>
-      <c r="E18" t="s">
-        <v>10</v>
-      </c>
-      <c r="F18" t="s">
-        <v>54</v>
-      </c>
-      <c r="G18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>19330051920255</v>
-      </c>
-      <c r="B19" t="s">
-        <v>82</v>
-      </c>
-      <c r="C19" t="s">
-        <v>103</v>
-      </c>
-      <c r="D19" t="s">
-        <v>126</v>
-      </c>
-      <c r="E19" t="s">
-        <v>5</v>
-      </c>
-      <c r="F19" t="s">
-        <v>53</v>
-      </c>
-      <c r="G19">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>19330051920261</v>
-      </c>
-      <c r="B20" t="s">
-        <v>85</v>
-      </c>
-      <c r="C20" t="s">
-        <v>105</v>
-      </c>
-      <c r="D20" t="s">
-        <v>129</v>
-      </c>
-      <c r="E20" t="s">
-        <v>5</v>
-      </c>
-      <c r="F20" t="s">
-        <v>53</v>
-      </c>
-      <c r="G20">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>19330051920265</v>
-      </c>
-      <c r="B21" t="s">
-        <v>86</v>
-      </c>
-      <c r="C21" t="s">
-        <v>81</v>
-      </c>
-      <c r="D21" t="s">
-        <v>130</v>
-      </c>
-      <c r="E21" t="s">
-        <v>10</v>
-      </c>
-      <c r="F21" t="s">
-        <v>54</v>
-      </c>
-      <c r="G21">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>19330051920405</v>
-      </c>
-      <c r="B22" t="s">
-        <v>91</v>
-      </c>
-      <c r="C22" t="s">
-        <v>110</v>
-      </c>
-      <c r="D22" t="s">
-        <v>136</v>
-      </c>
-      <c r="E22" t="s">
-        <v>5</v>
-      </c>
-      <c r="F22" t="s">
-        <v>53</v>
-      </c>
-      <c r="G22">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>19330051920407</v>
-      </c>
-      <c r="B23" t="s">
-        <v>93</v>
-      </c>
-      <c r="C23" t="s">
-        <v>70</v>
-      </c>
-      <c r="D23" t="s">
-        <v>138</v>
-      </c>
-      <c r="E23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F23" t="s">
-        <v>54</v>
-      </c>
-      <c r="G23">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>19330051920414</v>
-      </c>
-      <c r="B24" t="s">
-        <v>94</v>
-      </c>
-      <c r="C24" t="s">
-        <v>113</v>
-      </c>
-      <c r="D24" t="s">
-        <v>141</v>
-      </c>
-      <c r="E24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F24" t="s">
-        <v>54</v>
-      </c>
-      <c r="G24">
         <v>5</v>
       </c>
     </row>

--- a/grupos/6ASV - Estadisticos 20212.xlsx
+++ b/grupos/6ASV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="142">
   <si>
     <t>Materia</t>
   </si>
@@ -179,15 +179,15 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Hernández Mendoza Delfina</t>
+  </si>
+  <si>
+    <t>Ortega Valle Manuel</t>
+  </si>
+  <si>
     <t>Duran Amezcua María Angélica</t>
   </si>
   <si>
-    <t>Hernández Mendoza Delfina</t>
-  </si>
-  <si>
-    <t>Ortega Valle Manuel</t>
-  </si>
-  <si>
     <t>Jiménez Nieto Enrique</t>
   </si>
   <si>
@@ -209,238 +209,238 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>ALCANTARA</t>
+  </si>
+  <si>
+    <t>BONILLA</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>CISNEROS</t>
+  </si>
+  <si>
+    <t>CORDOVA</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
     <t>FLORES</t>
   </si>
   <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>HERRERA</t>
   </si>
   <si>
+    <t>LLAME</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MANI</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>MIXCOHUA</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>MONSALVO</t>
+  </si>
+  <si>
     <t>PEREZ</t>
   </si>
   <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>ROMAN</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
     <t>SANTILLANA</t>
   </si>
   <si>
+    <t>TREJO</t>
+  </si>
+  <si>
+    <t>LEYVA</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>PALMA</t>
+  </si>
+  <si>
+    <t>GUIZA</t>
+  </si>
+  <si>
     <t>GERARDO</t>
   </si>
   <si>
+    <t>SERRANO</t>
+  </si>
+  <si>
+    <t>CUAHUA</t>
+  </si>
+  <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>GALEOTE</t>
+  </si>
+  <si>
     <t>SIERRA</t>
   </si>
   <si>
-    <t>BONILLA</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
+    <t>TZOMPAXTLE</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>ZAPATA</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>CASTELLANOS</t>
+  </si>
+  <si>
+    <t>QUINTERO</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>PINO</t>
+  </si>
+  <si>
+    <t>LUENGAS</t>
+  </si>
+  <si>
+    <t>MOISES EFRAIN</t>
+  </si>
+  <si>
+    <t>JOSE EMMANUEL</t>
+  </si>
+  <si>
+    <t>BRANDON AXEL</t>
+  </si>
+  <si>
+    <t>GABRIEL MARTIN</t>
+  </si>
+  <si>
+    <t>ANGELA ALESSANDRA</t>
+  </si>
+  <si>
+    <t>VALERIA</t>
   </si>
   <si>
     <t>JULIO GABRIEL</t>
   </si>
   <si>
+    <t>LUIS ANGEL</t>
+  </si>
+  <si>
+    <t>CRISTIAN</t>
+  </si>
+  <si>
+    <t>ERICA</t>
+  </si>
+  <si>
+    <t>ZAYRA JOSELIN</t>
+  </si>
+  <si>
+    <t>JAVIER FERNANDO</t>
+  </si>
+  <si>
+    <t>ALEXIS</t>
+  </si>
+  <si>
     <t>DIEGO ABDEL JARIN</t>
   </si>
   <si>
+    <t>WENDY</t>
+  </si>
+  <si>
+    <t>AIDA</t>
+  </si>
+  <si>
+    <t>CESAR</t>
+  </si>
+  <si>
+    <t>JUAN CARLOS</t>
+  </si>
+  <si>
+    <t>KARLA</t>
+  </si>
+  <si>
+    <t>LETICIA</t>
+  </si>
+  <si>
+    <t>VALENTIN</t>
+  </si>
+  <si>
+    <t>ALFREDO</t>
+  </si>
+  <si>
+    <t>ANGEL GERARDO</t>
+  </si>
+  <si>
     <t>EDUARDO ULISES</t>
   </si>
   <si>
+    <t>JELIN JANET</t>
+  </si>
+  <si>
+    <t>CESAR JOVANI</t>
+  </si>
+  <si>
+    <t>KARLA DENISSE</t>
+  </si>
+  <si>
+    <t>MONSERRAT</t>
+  </si>
+  <si>
+    <t>RICARDO ISIDRO</t>
+  </si>
+  <si>
+    <t>CESAR JAHIR</t>
+  </si>
+  <si>
     <t>CESAR GAEL</t>
-  </si>
-  <si>
-    <t>ALCANTARA</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>CISNEROS</t>
-  </si>
-  <si>
-    <t>CORDOVA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>LLAME</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MANI</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>MIXCOHUA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>MONSALVO</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>ROMAN</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>TREJO</t>
-  </si>
-  <si>
-    <t>LEYVA</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>PALMA</t>
-  </si>
-  <si>
-    <t>GUIZA</t>
-  </si>
-  <si>
-    <t>SERRANO</t>
-  </si>
-  <si>
-    <t>CUAHUA</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>GALEOTE</t>
-  </si>
-  <si>
-    <t>TZOMPAXTLE</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>ZAPATA</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>CASTELLANOS</t>
-  </si>
-  <si>
-    <t>QUINTERO</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>PINO</t>
-  </si>
-  <si>
-    <t>LUENGAS</t>
-  </si>
-  <si>
-    <t>MOISES EFRAIN</t>
-  </si>
-  <si>
-    <t>JOSE EMMANUEL</t>
-  </si>
-  <si>
-    <t>BRANDON AXEL</t>
-  </si>
-  <si>
-    <t>GABRIEL MARTIN</t>
-  </si>
-  <si>
-    <t>ANGELA ALESSANDRA</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
-  </si>
-  <si>
-    <t>CRISTIAN</t>
-  </si>
-  <si>
-    <t>ERICA</t>
-  </si>
-  <si>
-    <t>ZAYRA JOSELIN</t>
-  </si>
-  <si>
-    <t>JAVIER FERNANDO</t>
-  </si>
-  <si>
-    <t>ALEXIS</t>
-  </si>
-  <si>
-    <t>WENDY</t>
-  </si>
-  <si>
-    <t>AIDA</t>
-  </si>
-  <si>
-    <t>CESAR</t>
-  </si>
-  <si>
-    <t>JUAN CARLOS</t>
-  </si>
-  <si>
-    <t>KARLA</t>
-  </si>
-  <si>
-    <t>LETICIA</t>
-  </si>
-  <si>
-    <t>VALENTIN</t>
-  </si>
-  <si>
-    <t>ALFREDO</t>
-  </si>
-  <si>
-    <t>ANGEL GERARDO</t>
-  </si>
-  <si>
-    <t>JELIN JANET</t>
-  </si>
-  <si>
-    <t>CESAR JOVANI</t>
-  </si>
-  <si>
-    <t>KARLA DENISSE</t>
-  </si>
-  <si>
-    <t>MONSERRAT</t>
-  </si>
-  <si>
-    <t>RICARDO ISIDRO</t>
-  </si>
-  <si>
-    <t>CESAR JAHIR</t>
   </si>
   <si>
     <t>ELIZABETH</t>
@@ -965,7 +965,7 @@
         <v>5</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O4">
         <v>6</v>
@@ -974,16 +974,16 @@
         <v>8</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R4">
         <v>9</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U4">
         <v>6</v>
@@ -998,7 +998,7 @@
         <v>8</v>
       </c>
       <c r="Y4">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1033,16 +1033,16 @@
         <v>8</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L5">
         <v>5</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O5">
         <v>5</v>
@@ -1051,16 +1051,16 @@
         <v>6</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R5">
         <v>5</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U5">
         <v>5</v>
@@ -1069,13 +1069,13 @@
         <v>7</v>
       </c>
       <c r="W5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X5">
         <v>5</v>
       </c>
       <c r="Y5">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1119,7 +1119,7 @@
         <v>5</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O6">
         <v>7</v>
@@ -1128,16 +1128,16 @@
         <v>9</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
         <v>10</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U6">
         <v>6</v>
@@ -1152,7 +1152,7 @@
         <v>9</v>
       </c>
       <c r="Y6">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1196,7 +1196,7 @@
         <v>6</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O7">
         <v>7</v>
@@ -1205,13 +1205,13 @@
         <v>9</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R7">
         <v>9</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T7">
         <v>10</v>
@@ -1229,7 +1229,7 @@
         <v>10</v>
       </c>
       <c r="Y7">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1273,7 +1273,7 @@
         <v>5</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O8">
         <v>5</v>
@@ -1282,13 +1282,13 @@
         <v>10</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
         <v>7</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T8">
         <v>9</v>
@@ -1306,7 +1306,7 @@
         <v>7</v>
       </c>
       <c r="Y8">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1350,7 +1350,7 @@
         <v>7</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O9">
         <v>7</v>
@@ -1359,16 +1359,16 @@
         <v>8</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
         <v>10</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U9">
         <v>6</v>
@@ -1383,7 +1383,7 @@
         <v>5</v>
       </c>
       <c r="Y9">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1400,7 +1400,7 @@
         <v>8</v>
       </c>
       <c r="E10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -1418,7 +1418,7 @@
         <v>8</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L10">
         <v>5</v>
@@ -1427,7 +1427,7 @@
         <v>5</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O10">
         <v>5</v>
@@ -1436,16 +1436,16 @@
         <v>8</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R10">
         <v>5</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U10">
         <v>5</v>
@@ -1454,7 +1454,7 @@
         <v>8</v>
       </c>
       <c r="W10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X10">
         <v>5</v>
@@ -1504,7 +1504,7 @@
         <v>6</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O11">
         <v>6</v>
@@ -1513,16 +1513,16 @@
         <v>8</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R11">
         <v>10</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U11">
         <v>6</v>
@@ -1581,7 +1581,7 @@
         <v>7</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O12">
         <v>7</v>
@@ -1590,13 +1590,13 @@
         <v>8</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R12">
         <v>10</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T12">
         <v>8</v>
@@ -1614,7 +1614,7 @@
         <v>8</v>
       </c>
       <c r="Y12">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1658,7 +1658,7 @@
         <v>5</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O13">
         <v>6</v>
@@ -1667,16 +1667,16 @@
         <v>10</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R13">
         <v>7</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U13">
         <v>6</v>
@@ -1685,13 +1685,13 @@
         <v>10</v>
       </c>
       <c r="W13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X13">
         <v>6</v>
       </c>
       <c r="Y13">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1735,7 +1735,7 @@
         <v>10</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O14">
         <v>7</v>
@@ -1744,13 +1744,13 @@
         <v>10</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R14">
         <v>10</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T14">
         <v>8</v>
@@ -1812,7 +1812,7 @@
         <v>5</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O15">
         <v>7</v>
@@ -1821,16 +1821,16 @@
         <v>8</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R15">
         <v>9</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U15">
         <v>6</v>
@@ -1845,7 +1845,7 @@
         <v>7</v>
       </c>
       <c r="Y15">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1889,7 +1889,7 @@
         <v>8</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O16">
         <v>7</v>
@@ -1898,13 +1898,13 @@
         <v>9</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R16">
         <v>9</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T16">
         <v>8</v>
@@ -1966,7 +1966,7 @@
         <v>8</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O17">
         <v>7</v>
@@ -1975,13 +1975,13 @@
         <v>9</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R17">
         <v>9</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T17">
         <v>8</v>
@@ -2016,7 +2016,7 @@
         <v>5</v>
       </c>
       <c r="E18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F18">
         <v>5</v>
@@ -2034,7 +2034,7 @@
         <v>7</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L18">
         <v>5</v>
@@ -2043,7 +2043,7 @@
         <v>5</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O18">
         <v>5</v>
@@ -2052,16 +2052,16 @@
         <v>7</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R18">
         <v>9</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U18">
         <v>5</v>
@@ -2070,13 +2070,13 @@
         <v>6</v>
       </c>
       <c r="W18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X18">
         <v>5</v>
       </c>
       <c r="Y18">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2120,7 +2120,7 @@
         <v>6</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O19">
         <v>6</v>
@@ -2129,16 +2129,16 @@
         <v>9</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R19">
         <v>10</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U19">
         <v>7</v>
@@ -2188,7 +2188,7 @@
         <v>9</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L20">
         <v>8</v>
@@ -2197,7 +2197,7 @@
         <v>6</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O20">
         <v>5</v>
@@ -2206,16 +2206,16 @@
         <v>8</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R20">
         <v>9</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U20">
         <v>6</v>
@@ -2224,7 +2224,7 @@
         <v>8</v>
       </c>
       <c r="W20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X20">
         <v>8</v>
@@ -2274,7 +2274,7 @@
         <v>6</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O21">
         <v>7</v>
@@ -2283,13 +2283,13 @@
         <v>9</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R21">
         <v>9</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T21">
         <v>9</v>
@@ -2307,7 +2307,7 @@
         <v>8</v>
       </c>
       <c r="Y21">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2351,7 +2351,7 @@
         <v>5</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O22">
         <v>5</v>
@@ -2360,13 +2360,13 @@
         <v>9</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R22">
         <v>6</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T22">
         <v>9</v>
@@ -2384,7 +2384,7 @@
         <v>6</v>
       </c>
       <c r="Y22">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2428,7 +2428,7 @@
         <v>10</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O23">
         <v>9</v>
@@ -2437,13 +2437,13 @@
         <v>9</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R23">
         <v>9</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T23">
         <v>9</v>
@@ -2505,7 +2505,7 @@
         <v>10</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O24">
         <v>9</v>
@@ -2514,13 +2514,13 @@
         <v>9</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R24">
         <v>10</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T24">
         <v>9</v>
@@ -2582,7 +2582,7 @@
         <v>5</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O25">
         <v>7</v>
@@ -2591,16 +2591,16 @@
         <v>9</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R25">
         <v>9</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U25">
         <v>6</v>
@@ -2609,13 +2609,13 @@
         <v>9</v>
       </c>
       <c r="W25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X25">
         <v>7</v>
       </c>
       <c r="Y25">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2659,7 +2659,7 @@
         <v>5</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O26">
         <v>6</v>
@@ -2668,13 +2668,13 @@
         <v>9</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R26">
         <v>9</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T26">
         <v>8</v>
@@ -2692,7 +2692,7 @@
         <v>10</v>
       </c>
       <c r="Y26">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2709,7 +2709,7 @@
         <v>6</v>
       </c>
       <c r="E27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F27">
         <v>5</v>
@@ -2727,7 +2727,7 @@
         <v>6</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L27">
         <v>8</v>
@@ -2736,7 +2736,7 @@
         <v>5</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O27">
         <v>7</v>
@@ -2745,16 +2745,16 @@
         <v>6</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R27">
         <v>8</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U27">
         <v>6</v>
@@ -2763,13 +2763,13 @@
         <v>6</v>
       </c>
       <c r="W27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X27">
         <v>5</v>
       </c>
       <c r="Y27">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2813,7 +2813,7 @@
         <v>6</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O28">
         <v>7</v>
@@ -2822,13 +2822,13 @@
         <v>10</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R28">
         <v>9</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T28">
         <v>10</v>
@@ -2846,7 +2846,7 @@
         <v>8</v>
       </c>
       <c r="Y28">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2890,7 +2890,7 @@
         <v>6</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O29">
         <v>7</v>
@@ -2899,13 +2899,13 @@
         <v>9</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R29">
         <v>9</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T29">
         <v>8</v>
@@ -2923,7 +2923,7 @@
         <v>9</v>
       </c>
       <c r="Y29">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2967,7 +2967,7 @@
         <v>8</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O30">
         <v>8</v>
@@ -2976,13 +2976,13 @@
         <v>10</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R30">
         <v>10</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T30">
         <v>9</v>
@@ -3000,7 +3000,7 @@
         <v>10</v>
       </c>
       <c r="Y30">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -3044,7 +3044,7 @@
         <v>5</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O31">
         <v>6</v>
@@ -3053,13 +3053,13 @@
         <v>9</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R31">
         <v>9</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T31">
         <v>9</v>
@@ -3077,7 +3077,7 @@
         <v>7</v>
       </c>
       <c r="Y31">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -3121,7 +3121,7 @@
         <v>5</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O32">
         <v>7</v>
@@ -3130,13 +3130,13 @@
         <v>9</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R32">
         <v>7</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T32">
         <v>8</v>
@@ -3148,13 +3148,13 @@
         <v>9</v>
       </c>
       <c r="W32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X32">
         <v>6</v>
       </c>
       <c r="Y32">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3189,16 +3189,16 @@
         <v>9</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L33">
         <v>6</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O33">
         <v>7</v>
@@ -3207,13 +3207,13 @@
         <v>9</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R33">
         <v>7</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T33">
         <v>8</v>
@@ -3225,13 +3225,13 @@
         <v>9</v>
       </c>
       <c r="W33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X33">
         <v>6</v>
       </c>
       <c r="Y33">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3248,7 +3248,7 @@
         <v>8</v>
       </c>
       <c r="E34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F34">
         <v>5</v>
@@ -3266,7 +3266,7 @@
         <v>9</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L34">
         <v>6</v>
@@ -3275,7 +3275,7 @@
         <v>5</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O34">
         <v>5</v>
@@ -3284,16 +3284,16 @@
         <v>8</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R34">
         <v>5</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T34">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U34">
         <v>5</v>
@@ -3302,13 +3302,13 @@
         <v>8</v>
       </c>
       <c r="W34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X34">
         <v>5</v>
       </c>
       <c r="Y34">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3352,7 +3352,7 @@
         <v>5</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O35">
         <v>6</v>
@@ -3361,13 +3361,13 @@
         <v>9</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R35">
         <v>8</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T35">
         <v>9</v>
@@ -3385,7 +3385,7 @@
         <v>8</v>
       </c>
       <c r="Y35">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -3441,7 +3441,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
         <v>53</v>
@@ -3450,19 +3450,19 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E2">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>53.13</v>
+        <v>81.25</v>
       </c>
       <c r="G2">
-        <v>46.88</v>
+        <v>18.75</v>
       </c>
       <c r="H2">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3473,7 +3473,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>54</v>
@@ -3482,19 +3482,19 @@
         <v>32</v>
       </c>
       <c r="D3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>81.25</v>
+        <v>84.38</v>
       </c>
       <c r="G3">
-        <v>18.75</v>
+        <v>15.63</v>
       </c>
       <c r="H3">
-        <v>7.5</v>
+        <v>6.3</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3505,7 +3505,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>55</v>
@@ -3514,19 +3514,19 @@
         <v>32</v>
       </c>
       <c r="D4">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>84.38</v>
+        <v>90.63</v>
       </c>
       <c r="G4">
-        <v>15.63</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="H4">
-        <v>6.3</v>
+        <v>6.6</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3546,25 +3546,25 @@
         <v>32</v>
       </c>
       <c r="D5">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>87.5</v>
+        <v>93.75</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="H5">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="I5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>12.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -3590,7 +3590,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>8.6</v>
+        <v>8.1</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3638,7 +3638,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3663,86 +3663,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>19330051920252</v>
-      </c>
-      <c r="B2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D2" t="s">
-        <v>71</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>19330051920259</v>
-      </c>
-      <c r="B3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D3" t="s">
-        <v>72</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>19330051920403</v>
-      </c>
-      <c r="B4" t="s">
-        <v>65</v>
-      </c>
-      <c r="C4" t="s">
-        <v>69</v>
-      </c>
-      <c r="D4" t="s">
-        <v>73</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>19330051920412</v>
-      </c>
-      <c r="B5" t="s">
-        <v>66</v>
-      </c>
-      <c r="C5" t="s">
-        <v>70</v>
-      </c>
-      <c r="D5" t="s">
-        <v>74</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -3778,81 +3698,81 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>19330051920252</v>
+        <v>19330051920246</v>
       </c>
       <c r="B2" t="s">
         <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="D2" t="s">
-        <v>71</v>
+        <v>110</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>19330051920259</v>
+        <v>19330051920247</v>
       </c>
       <c r="B3" t="s">
         <v>64</v>
       </c>
       <c r="C3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D3" t="s">
-        <v>72</v>
+        <v>111</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>19330051920403</v>
+        <v>19330051920248</v>
       </c>
       <c r="B4" t="s">
         <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="D4" t="s">
-        <v>73</v>
+        <v>112</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>19330051920412</v>
+        <v>19330051920249</v>
       </c>
       <c r="B5" t="s">
         <v>66</v>
       </c>
       <c r="C5" t="s">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="D5" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>19330051920246</v>
+        <v>19330051920250</v>
       </c>
       <c r="B6" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="C6" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D6" t="s">
         <v>114</v>
@@ -3863,13 +3783,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>19330051920247</v>
+        <v>19330051920251</v>
       </c>
       <c r="B7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="D7" t="s">
         <v>115</v>
@@ -3880,13 +3800,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>19330051920248</v>
+        <v>19330051920252</v>
       </c>
       <c r="B8" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D8" t="s">
         <v>116</v>
@@ -3897,13 +3817,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>19330051920249</v>
+        <v>19330051920253</v>
       </c>
       <c r="B9" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="C9" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="D9" t="s">
         <v>117</v>
@@ -3914,13 +3834,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>19330051920250</v>
+        <v>19330051920433</v>
       </c>
       <c r="B10" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="C10" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D10" t="s">
         <v>118</v>
@@ -3931,13 +3851,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>19330051920251</v>
+        <v>19330051920256</v>
       </c>
       <c r="B11" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C11" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D11" t="s">
         <v>119</v>
@@ -3948,13 +3868,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>19330051920253</v>
+        <v>19330051920254</v>
       </c>
       <c r="B12" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="C12" t="s">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="D12" t="s">
         <v>120</v>
@@ -3965,13 +3885,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>19330051920433</v>
+        <v>19330051920258</v>
       </c>
       <c r="B13" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="C13" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D13" t="s">
         <v>121</v>
@@ -3982,13 +3902,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>19330051920256</v>
+        <v>19330051920257</v>
       </c>
       <c r="B14" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="C14" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D14" t="s">
         <v>122</v>
@@ -3999,13 +3919,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>19330051920254</v>
+        <v>19330051920259</v>
       </c>
       <c r="B15" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="C15" t="s">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="D15" t="s">
         <v>123</v>
@@ -4016,13 +3936,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>19330051920258</v>
+        <v>19330051920255</v>
       </c>
       <c r="B16" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="C16" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D16" t="s">
         <v>124</v>
@@ -4033,13 +3953,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>19330051920257</v>
+        <v>19330051920260</v>
       </c>
       <c r="B17" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="C17" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D17" t="s">
         <v>125</v>
@@ -4050,13 +3970,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>19330051920255</v>
+        <v>19330051920263</v>
       </c>
       <c r="B18" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="C18" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D18" t="s">
         <v>126</v>
@@ -4067,13 +3987,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>19330051920260</v>
+        <v>19330051920261</v>
       </c>
       <c r="B19" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="C19" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D19" t="s">
         <v>127</v>
@@ -4084,13 +4004,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>19330051920263</v>
+        <v>19330051920265</v>
       </c>
       <c r="B20" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="C20" t="s">
-        <v>94</v>
+        <v>71</v>
       </c>
       <c r="D20" t="s">
         <v>128</v>
@@ -4101,13 +4021,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>19330051920261</v>
+        <v>19330051920267</v>
       </c>
       <c r="B21" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="C21" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D21" t="s">
         <v>129</v>
@@ -4118,13 +4038,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>19330051920265</v>
+        <v>19330051920266</v>
       </c>
       <c r="B22" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="C22" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="D22" t="s">
         <v>130</v>
@@ -4135,13 +4055,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>19330051920267</v>
+        <v>19330051920402</v>
       </c>
       <c r="B23" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="C23" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D23" t="s">
         <v>131</v>
@@ -4152,13 +4072,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>19330051920266</v>
+        <v>19330051920400</v>
       </c>
       <c r="B24" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="C24" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D24" t="s">
         <v>132</v>
@@ -4169,13 +4089,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>19330051920402</v>
+        <v>19330051920403</v>
       </c>
       <c r="B25" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="C25" t="s">
-        <v>107</v>
+        <v>64</v>
       </c>
       <c r="D25" t="s">
         <v>133</v>
@@ -4186,13 +4106,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>19330051920400</v>
+        <v>19330051920348</v>
       </c>
       <c r="B26" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C26" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D26" t="s">
         <v>134</v>
@@ -4203,13 +4123,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>19330051920348</v>
+        <v>19330051920405</v>
       </c>
       <c r="B27" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="C27" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D27" t="s">
         <v>135</v>
@@ -4220,13 +4140,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>19330051920405</v>
+        <v>19330051920406</v>
       </c>
       <c r="B28" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="C28" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D28" t="s">
         <v>136</v>
@@ -4237,13 +4157,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>19330051920406</v>
+        <v>19330051920407</v>
       </c>
       <c r="B29" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="C29" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="D29" t="s">
         <v>137</v>
@@ -4254,13 +4174,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>19330051920407</v>
+        <v>19330051920409</v>
       </c>
       <c r="B30" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="C30" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="D30" t="s">
         <v>138</v>
@@ -4271,13 +4191,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>19330051920409</v>
+        <v>19330051920411</v>
       </c>
       <c r="B31" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="C31" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="D31" t="s">
         <v>139</v>
@@ -4288,13 +4208,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>19330051920411</v>
+        <v>19330051920412</v>
       </c>
       <c r="B32" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="C32" t="s">
-        <v>112</v>
+        <v>86</v>
       </c>
       <c r="D32" t="s">
         <v>140</v>
@@ -4308,10 +4228,10 @@
         <v>19330051920414</v>
       </c>
       <c r="B33" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C33" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D33" t="s">
         <v>141</v>
@@ -4327,7 +4247,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4359,22 +4279,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920247</v>
+        <v>19330051920259</v>
       </c>
       <c r="B2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C2" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="D2" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4382,22 +4302,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920247</v>
+        <v>19330051920259</v>
       </c>
       <c r="B3" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C3" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="D3" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4405,22 +4325,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920265</v>
+        <v>19330051920412</v>
       </c>
       <c r="B4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C4" t="s">
         <v>86</v>
       </c>
-      <c r="C4" t="s">
-        <v>81</v>
-      </c>
       <c r="D4" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4428,19 +4348,19 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920265</v>
+        <v>19330051920412</v>
       </c>
       <c r="B5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C5" t="s">
         <v>86</v>
       </c>
-      <c r="C5" t="s">
-        <v>81</v>
-      </c>
       <c r="D5" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
         <v>53</v>
@@ -4451,19 +4371,19 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920246</v>
+        <v>19330051920251</v>
       </c>
       <c r="B6" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
         <v>53</v>
@@ -4474,22 +4394,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920248</v>
+        <v>19330051920265</v>
       </c>
       <c r="B7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C7" t="s">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="D7" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -4497,19 +4417,19 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920250</v>
+        <v>19330051920403</v>
       </c>
       <c r="B8" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C8" t="s">
-        <v>98</v>
+        <v>64</v>
       </c>
       <c r="D8" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
         <v>53</v>
@@ -4520,185 +4440,24 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330051920251</v>
+        <v>19330051920411</v>
       </c>
       <c r="B9" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="C9" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="D9" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>19330051920254</v>
-      </c>
-      <c r="B10" t="s">
-        <v>82</v>
-      </c>
-      <c r="C10" t="s">
-        <v>79</v>
-      </c>
-      <c r="D10" t="s">
-        <v>123</v>
-      </c>
-      <c r="E10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" t="s">
-        <v>53</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>19330051920258</v>
-      </c>
-      <c r="B11" t="s">
-        <v>82</v>
-      </c>
-      <c r="C11" t="s">
-        <v>101</v>
-      </c>
-      <c r="D11" t="s">
-        <v>124</v>
-      </c>
-      <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" t="s">
-        <v>53</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>19330051920402</v>
-      </c>
-      <c r="B12" t="s">
-        <v>88</v>
-      </c>
-      <c r="C12" t="s">
-        <v>107</v>
-      </c>
-      <c r="D12" t="s">
-        <v>133</v>
-      </c>
-      <c r="E12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" t="s">
-        <v>53</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>19330051920400</v>
-      </c>
-      <c r="B13" t="s">
-        <v>89</v>
-      </c>
-      <c r="C13" t="s">
-        <v>108</v>
-      </c>
-      <c r="D13" t="s">
-        <v>134</v>
-      </c>
-      <c r="E13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" t="s">
-        <v>53</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>19330051920407</v>
-      </c>
-      <c r="B14" t="s">
-        <v>93</v>
-      </c>
-      <c r="C14" t="s">
-        <v>70</v>
-      </c>
-      <c r="D14" t="s">
-        <v>138</v>
-      </c>
-      <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" t="s">
-        <v>53</v>
-      </c>
-      <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>19330051920409</v>
-      </c>
-      <c r="B15" t="s">
-        <v>70</v>
-      </c>
-      <c r="C15" t="s">
-        <v>96</v>
-      </c>
-      <c r="D15" t="s">
-        <v>139</v>
-      </c>
-      <c r="E15" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" t="s">
-        <v>53</v>
-      </c>
-      <c r="G15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>19330051920414</v>
-      </c>
-      <c r="B16" t="s">
-        <v>94</v>
-      </c>
-      <c r="C16" t="s">
-        <v>113</v>
-      </c>
-      <c r="D16" t="s">
-        <v>141</v>
-      </c>
-      <c r="E16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" t="s">
-        <v>53</v>
-      </c>
-      <c r="G16">
         <v>5</v>
       </c>
     </row>
